--- a/design/角色表.xlsx
+++ b/design/角色表.xlsx
@@ -749,7 +749,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1659,7 +1659,7 @@
         <v>1600</v>
       </c>
       <c r="E6" s="9">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F6" s="9">
         <v>100</v>
@@ -9143,35 +9143,36 @@
     </row>
   </sheetData>
   <dataValidations count="6">
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="玩家配置ID" prompt="整数 1～2147483647。本表内唯一的正整数；不复用已发布 ID。" sqref="A5:A6 A7:A503">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～2147483647。跨表引用及组合条件请对照填表说明。" promptTitle="玩家配置ID" prompt="整数 1～2147483647。本表内唯一的正整数；不复用已发布 ID。" sqref="A5:A503">
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 2～10000。跨表引用及组合条件请对照填表说明。" promptTitle="碰撞宽度（毫米）" prompt="整数 2～10000。必须为偶数；以脚底中心向左右各延伸半宽。" sqref="C5:C6 C7:C503">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 2～10000。跨表引用及组合条件请对照填表说明。" promptTitle="碰撞宽度（毫米）" prompt="整数 2～10000。必须为偶数；以脚底中心向左右各延伸半宽。" sqref="C5:C503">
       <formula1>2</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 2～10000。跨表引用及组合条件请对照填表说明。" promptTitle="碰撞高度（毫米）" prompt="整数 2～10000。必须为偶数；从脚底向上延伸。" sqref="D5:D6 D7:D503">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 2～10000。跨表引用及组合条件请对照填表说明。" promptTitle="碰撞高度（毫米）" prompt="整数 2～10000。必须为偶数；从脚底向上延伸。" sqref="D5:D503">
       <formula1>2</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～1000000。跨表引用及组合条件请对照填表说明。" promptTitle="最大生命" prompt="整数 1～1000000。出生时的最大生命；非运行时当前生命。" sqref="E5:E6 E7:E503">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～1000000。跨表引用及组合条件请对照填表说明。" promptTitle="最大生命" prompt="整数 1～1000000。出生时的最大生命；非运行时当前生命。" sqref="E5:E503">
       <formula1>1</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～1000。跨表引用及组合条件请对照填表说明。" promptTitle="移速（毫米/Tick）" prompt="整数 1～1000。固定 60 Hz 下每 Tick 的水平移动速度。" sqref="F5:F6 F7:F503">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～1000。跨表引用及组合条件请对照填表说明。" promptTitle="移速（毫米/Tick）" prompt="整数 1～1000。固定 60 Hz 下每 Tick 的水平移动速度。" sqref="F5:F503">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～1000。跨表引用及组合条件请对照填表说明。" promptTitle="跳跃速度（毫米/Tick）" prompt="整数 1～1000。起跳时的向上速度。" sqref="G5:G6 G7:G503">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～1000。跨表引用及组合条件请对照填表说明。" promptTitle="跳跃速度（毫米/Tick）" prompt="整数 1～1000。起跳时的向上速度。" sqref="G5:G503">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="L5:L6 J2:J503 M7:O503 M1:O1 A1:G1 A2:H4 A5:A6 C5:H6 N6:O6 A7:H503" numberStoredAsText="1"/>
+    <ignoredError sqref="A7:H503 N6:O6 C5:H5 C6:D6 F6:H6 A5:A6 A2:H4 A1:G1 M1:O1 M7:O503 J2:J503 L5:L6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12300,6 +12301,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/design/角色表.xlsx
+++ b/design/角色表.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="51">
   <si>
     <t>玩家配置ID</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>移速（毫米/Tick）</t>
+  </si>
+  <si>
+    <t>奔跑速度（毫米/Tick）</t>
   </si>
   <si>
     <t>跳跃速度（毫米/Tick）</t>
@@ -97,6 +100,9 @@
   </si>
   <si>
     <t>Speed</t>
+  </si>
+  <si>
+    <t>Run</t>
   </si>
   <si>
     <t>JumpSpeed</t>
@@ -1417,7 +1423,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:O503"/>
+  <dimension ref="A1:P503"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" style="1" customWidth="1"/>
@@ -1425,13 +1431,13 @@
     <col min="3" max="4" width="18" style="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23" style="1" customWidth="1"/>
-    <col min="8" max="10" width="24" style="11" customWidth="1"/>
-    <col min="11" max="13" width="24" style="1" customWidth="1"/>
-    <col min="15" max="15" width="55" customWidth="1"/>
+    <col min="7" max="8" width="23" style="1" customWidth="1"/>
+    <col min="9" max="11" width="24" style="11" customWidth="1"/>
+    <col min="12" max="14" width="24" style="1" customWidth="1"/>
+    <col min="16" max="16" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:15">
+    <row r="1" ht="40" customHeight="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1453,7 +1459,7 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="12" t="s">
@@ -1462,7 +1468,7 @@
       <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -1471,144 +1477,156 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" ht="25" customHeight="1" spans="1:15">
-      <c r="A2" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="6" t="s">
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:16">
+      <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="B2" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="C2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>14</v>
+      <c r="H2" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="6" t="s">
+      <c r="K2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="29" customHeight="1" spans="1:15">
-      <c r="A3" s="5" t="s">
+      <c r="M2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="6" t="s">
+    </row>
+    <row r="3" ht="29" customHeight="1" spans="1:16">
+      <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="G3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="H3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="I3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="J3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="K3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="7"/>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:15">
-      <c r="A4" s="5" t="s">
+      <c r="M3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>31</v>
       </c>
+      <c r="P3" s="7"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:16">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="C4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
-      <c r="H4" s="13" t="s">
-        <v>31</v>
+      <c r="H4" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
-      <c r="M4" s="6" t="s">
-        <v>32</v>
+      <c r="M4" s="13" t="s">
+        <v>33</v>
       </c>
-      <c r="O4" s="7"/>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="1:15">
+      <c r="N4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="7"/>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="1:16">
       <c r="A5" s="8">
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="8">
         <v>600</v>
@@ -1623,34 +1641,37 @@
         <v>100</v>
       </c>
       <c r="G5" s="8">
+        <v>150</v>
+      </c>
+      <c r="H5" s="8">
         <v>240</v>
       </c>
-      <c r="H5" s="14" t="s">
-        <v>34</v>
-      </c>
       <c r="I5" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="14"/>
-      <c r="O5" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" ht="26" customHeight="1" spans="1:15">
+      <c r="M5" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" s="14"/>
+      <c r="P5" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1" spans="1:16">
       <c r="A6" s="9">
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C6" s="9">
         <v>600</v>
@@ -1665,28 +1686,31 @@
         <v>100</v>
       </c>
       <c r="G6" s="9">
+        <v>150</v>
+      </c>
+      <c r="H6" s="9">
         <v>240</v>
       </c>
-      <c r="H6" s="15" t="s">
-        <v>34</v>
-      </c>
       <c r="I6" s="15" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="10"/>
       <c r="B7" s="16"/>
       <c r="C7" s="10"/>
@@ -1694,14 +1718,15 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="16"/>
+      <c r="H7" s="10"/>
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
       <c r="M7" s="16"/>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" s="16"/>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="10"/>
       <c r="B8" s="16"/>
       <c r="C8" s="10"/>
@@ -1709,14 +1734,15 @@
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="16"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" s="16"/>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="10"/>
       <c r="B9" s="16"/>
       <c r="C9" s="10"/>
@@ -1724,14 +1750,15 @@
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="16"/>
+      <c r="H9" s="10"/>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" s="16"/>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="10"/>
       <c r="B10" s="16"/>
       <c r="C10" s="10"/>
@@ -1739,14 +1766,15 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="16"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" s="16"/>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="10"/>
       <c r="B11" s="16"/>
       <c r="C11" s="10"/>
@@ -1754,14 +1782,15 @@
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="16"/>
+      <c r="H11" s="10"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" s="16"/>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="10"/>
       <c r="B12" s="16"/>
       <c r="C12" s="10"/>
@@ -1769,14 +1798,15 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="16"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
       <c r="K12" s="16"/>
       <c r="L12" s="16"/>
       <c r="M12" s="16"/>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="10"/>
       <c r="B13" s="16"/>
       <c r="C13" s="10"/>
@@ -1784,14 +1814,15 @@
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="16"/>
+      <c r="H13" s="10"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" s="16"/>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" s="10"/>
       <c r="B14" s="16"/>
       <c r="C14" s="10"/>
@@ -1799,14 +1830,15 @@
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="16"/>
+      <c r="H14" s="10"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" s="16"/>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="10"/>
       <c r="B15" s="16"/>
       <c r="C15" s="10"/>
@@ -1814,14 +1846,15 @@
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="16"/>
+      <c r="H15" s="10"/>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
       <c r="K15" s="16"/>
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" s="16"/>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="10"/>
       <c r="B16" s="16"/>
       <c r="C16" s="10"/>
@@ -1829,14 +1862,15 @@
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
-      <c r="H16" s="16"/>
+      <c r="H16" s="10"/>
       <c r="I16" s="16"/>
       <c r="J16" s="16"/>
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16" s="16"/>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="10"/>
       <c r="B17" s="16"/>
       <c r="C17" s="10"/>
@@ -1844,14 +1878,15 @@
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="16"/>
+      <c r="H17" s="10"/>
       <c r="I17" s="16"/>
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17" s="16"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="10"/>
       <c r="B18" s="16"/>
       <c r="C18" s="10"/>
@@ -1859,14 +1894,15 @@
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="16"/>
+      <c r="H18" s="10"/>
       <c r="I18" s="16"/>
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18" s="16"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="10"/>
       <c r="B19" s="16"/>
       <c r="C19" s="10"/>
@@ -1874,14 +1910,15 @@
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
-      <c r="H19" s="16"/>
+      <c r="H19" s="10"/>
       <c r="I19" s="16"/>
       <c r="J19" s="16"/>
       <c r="K19" s="16"/>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="16"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="10"/>
       <c r="B20" s="16"/>
       <c r="C20" s="10"/>
@@ -1889,14 +1926,15 @@
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
-      <c r="H20" s="16"/>
+      <c r="H20" s="10"/>
       <c r="I20" s="16"/>
       <c r="J20" s="16"/>
       <c r="K20" s="16"/>
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20" s="16"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="10"/>
       <c r="B21" s="16"/>
       <c r="C21" s="10"/>
@@ -1904,14 +1942,15 @@
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
-      <c r="H21" s="16"/>
+      <c r="H21" s="10"/>
       <c r="I21" s="16"/>
       <c r="J21" s="16"/>
       <c r="K21" s="16"/>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21" s="16"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="10"/>
       <c r="B22" s="16"/>
       <c r="C22" s="10"/>
@@ -1919,14 +1958,15 @@
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
-      <c r="H22" s="16"/>
+      <c r="H22" s="10"/>
       <c r="I22" s="16"/>
       <c r="J22" s="16"/>
       <c r="K22" s="16"/>
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22" s="16"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="10"/>
       <c r="B23" s="16"/>
       <c r="C23" s="10"/>
@@ -1934,14 +1974,15 @@
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="16"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="16"/>
       <c r="J23" s="16"/>
       <c r="K23" s="16"/>
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23" s="16"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="10"/>
       <c r="B24" s="16"/>
       <c r="C24" s="10"/>
@@ -1949,14 +1990,15 @@
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
-      <c r="H24" s="16"/>
+      <c r="H24" s="10"/>
       <c r="I24" s="16"/>
       <c r="J24" s="16"/>
       <c r="K24" s="16"/>
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" s="16"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="10"/>
       <c r="B25" s="16"/>
       <c r="C25" s="10"/>
@@ -1964,14 +2006,15 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
-      <c r="H25" s="16"/>
+      <c r="H25" s="10"/>
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="N25" s="16"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="10"/>
       <c r="B26" s="16"/>
       <c r="C26" s="10"/>
@@ -1979,14 +2022,15 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
-      <c r="H26" s="16"/>
+      <c r="H26" s="10"/>
       <c r="I26" s="16"/>
       <c r="J26" s="16"/>
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="N26" s="16"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="10"/>
       <c r="B27" s="16"/>
       <c r="C27" s="10"/>
@@ -1994,14 +2038,15 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="16"/>
+      <c r="H27" s="10"/>
       <c r="I27" s="16"/>
       <c r="J27" s="16"/>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="N27" s="16"/>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="10"/>
       <c r="B28" s="16"/>
       <c r="C28" s="10"/>
@@ -2009,14 +2054,15 @@
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
-      <c r="H28" s="16"/>
+      <c r="H28" s="10"/>
       <c r="I28" s="16"/>
       <c r="J28" s="16"/>
       <c r="K28" s="16"/>
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="N28" s="16"/>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="10"/>
       <c r="B29" s="16"/>
       <c r="C29" s="10"/>
@@ -2024,14 +2070,15 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="16"/>
+      <c r="H29" s="10"/>
       <c r="I29" s="16"/>
       <c r="J29" s="16"/>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
-    </row>
-    <row r="30" spans="1:13">
+      <c r="N29" s="16"/>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="10"/>
       <c r="B30" s="16"/>
       <c r="C30" s="10"/>
@@ -2039,14 +2086,15 @@
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
-      <c r="H30" s="16"/>
+      <c r="H30" s="10"/>
       <c r="I30" s="16"/>
       <c r="J30" s="16"/>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
-    </row>
-    <row r="31" spans="1:13">
+      <c r="N30" s="16"/>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="10"/>
       <c r="B31" s="16"/>
       <c r="C31" s="10"/>
@@ -2054,14 +2102,15 @@
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="16"/>
+      <c r="H31" s="10"/>
       <c r="I31" s="16"/>
       <c r="J31" s="16"/>
       <c r="K31" s="16"/>
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
-    </row>
-    <row r="32" spans="1:13">
+      <c r="N31" s="16"/>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="10"/>
       <c r="B32" s="16"/>
       <c r="C32" s="10"/>
@@ -2069,14 +2118,15 @@
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
-      <c r="H32" s="16"/>
+      <c r="H32" s="10"/>
       <c r="I32" s="16"/>
       <c r="J32" s="16"/>
       <c r="K32" s="16"/>
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32" s="16"/>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="10"/>
       <c r="B33" s="16"/>
       <c r="C33" s="10"/>
@@ -2084,14 +2134,15 @@
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
-      <c r="H33" s="16"/>
+      <c r="H33" s="10"/>
       <c r="I33" s="16"/>
       <c r="J33" s="16"/>
       <c r="K33" s="16"/>
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="N33" s="16"/>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="10"/>
       <c r="B34" s="16"/>
       <c r="C34" s="10"/>
@@ -2099,14 +2150,15 @@
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
       <c r="G34" s="10"/>
-      <c r="H34" s="16"/>
+      <c r="H34" s="10"/>
       <c r="I34" s="16"/>
       <c r="J34" s="16"/>
       <c r="K34" s="16"/>
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="N34" s="16"/>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="10"/>
       <c r="B35" s="16"/>
       <c r="C35" s="10"/>
@@ -2114,14 +2166,15 @@
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="16"/>
+      <c r="H35" s="10"/>
       <c r="I35" s="16"/>
       <c r="J35" s="16"/>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="N35" s="16"/>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="10"/>
       <c r="B36" s="16"/>
       <c r="C36" s="10"/>
@@ -2129,14 +2182,15 @@
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="G36" s="10"/>
-      <c r="H36" s="16"/>
+      <c r="H36" s="10"/>
       <c r="I36" s="16"/>
       <c r="J36" s="16"/>
       <c r="K36" s="16"/>
       <c r="L36" s="16"/>
       <c r="M36" s="16"/>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="N36" s="16"/>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="10"/>
       <c r="B37" s="16"/>
       <c r="C37" s="10"/>
@@ -2144,14 +2198,15 @@
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
-      <c r="H37" s="16"/>
+      <c r="H37" s="10"/>
       <c r="I37" s="16"/>
       <c r="J37" s="16"/>
       <c r="K37" s="16"/>
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
-    </row>
-    <row r="38" spans="1:13">
+      <c r="N37" s="16"/>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="10"/>
       <c r="B38" s="16"/>
       <c r="C38" s="10"/>
@@ -2159,14 +2214,15 @@
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
       <c r="G38" s="10"/>
-      <c r="H38" s="16"/>
+      <c r="H38" s="10"/>
       <c r="I38" s="16"/>
       <c r="J38" s="16"/>
       <c r="K38" s="16"/>
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
-    </row>
-    <row r="39" spans="1:13">
+      <c r="N38" s="16"/>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="10"/>
       <c r="B39" s="16"/>
       <c r="C39" s="10"/>
@@ -2174,14 +2230,15 @@
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
       <c r="G39" s="10"/>
-      <c r="H39" s="16"/>
+      <c r="H39" s="10"/>
       <c r="I39" s="16"/>
       <c r="J39" s="16"/>
       <c r="K39" s="16"/>
       <c r="L39" s="16"/>
       <c r="M39" s="16"/>
-    </row>
-    <row r="40" spans="1:13">
+      <c r="N39" s="16"/>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="10"/>
       <c r="B40" s="16"/>
       <c r="C40" s="10"/>
@@ -2189,14 +2246,15 @@
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
       <c r="G40" s="10"/>
-      <c r="H40" s="16"/>
+      <c r="H40" s="10"/>
       <c r="I40" s="16"/>
       <c r="J40" s="16"/>
       <c r="K40" s="16"/>
       <c r="L40" s="16"/>
       <c r="M40" s="16"/>
-    </row>
-    <row r="41" spans="1:13">
+      <c r="N40" s="16"/>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="10"/>
       <c r="B41" s="16"/>
       <c r="C41" s="10"/>
@@ -2204,14 +2262,15 @@
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
       <c r="G41" s="10"/>
-      <c r="H41" s="16"/>
+      <c r="H41" s="10"/>
       <c r="I41" s="16"/>
       <c r="J41" s="16"/>
       <c r="K41" s="16"/>
       <c r="L41" s="16"/>
       <c r="M41" s="16"/>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41" s="16"/>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="10"/>
       <c r="B42" s="16"/>
       <c r="C42" s="10"/>
@@ -2219,14 +2278,15 @@
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
-      <c r="H42" s="16"/>
+      <c r="H42" s="10"/>
       <c r="I42" s="16"/>
       <c r="J42" s="16"/>
       <c r="K42" s="16"/>
       <c r="L42" s="16"/>
       <c r="M42" s="16"/>
-    </row>
-    <row r="43" spans="1:13">
+      <c r="N42" s="16"/>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="10"/>
       <c r="B43" s="16"/>
       <c r="C43" s="10"/>
@@ -2234,14 +2294,15 @@
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
-      <c r="H43" s="16"/>
+      <c r="H43" s="10"/>
       <c r="I43" s="16"/>
       <c r="J43" s="16"/>
       <c r="K43" s="16"/>
       <c r="L43" s="16"/>
       <c r="M43" s="16"/>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="N43" s="16"/>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="10"/>
       <c r="B44" s="16"/>
       <c r="C44" s="10"/>
@@ -2249,14 +2310,15 @@
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
-      <c r="H44" s="16"/>
+      <c r="H44" s="10"/>
       <c r="I44" s="16"/>
       <c r="J44" s="16"/>
       <c r="K44" s="16"/>
       <c r="L44" s="16"/>
       <c r="M44" s="16"/>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="N44" s="16"/>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="10"/>
       <c r="B45" s="16"/>
       <c r="C45" s="10"/>
@@ -2264,14 +2326,15 @@
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
       <c r="G45" s="10"/>
-      <c r="H45" s="16"/>
+      <c r="H45" s="10"/>
       <c r="I45" s="16"/>
       <c r="J45" s="16"/>
       <c r="K45" s="16"/>
       <c r="L45" s="16"/>
       <c r="M45" s="16"/>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="N45" s="16"/>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="10"/>
       <c r="B46" s="16"/>
       <c r="C46" s="10"/>
@@ -2279,14 +2342,15 @@
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="10"/>
-      <c r="H46" s="16"/>
+      <c r="H46" s="10"/>
       <c r="I46" s="16"/>
       <c r="J46" s="16"/>
       <c r="K46" s="16"/>
       <c r="L46" s="16"/>
       <c r="M46" s="16"/>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="N46" s="16"/>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="10"/>
       <c r="B47" s="16"/>
       <c r="C47" s="10"/>
@@ -2294,14 +2358,15 @@
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
       <c r="G47" s="10"/>
-      <c r="H47" s="16"/>
+      <c r="H47" s="10"/>
       <c r="I47" s="16"/>
       <c r="J47" s="16"/>
       <c r="K47" s="16"/>
       <c r="L47" s="16"/>
       <c r="M47" s="16"/>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="N47" s="16"/>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" s="10"/>
       <c r="B48" s="16"/>
       <c r="C48" s="10"/>
@@ -2309,14 +2374,15 @@
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
       <c r="G48" s="10"/>
-      <c r="H48" s="16"/>
+      <c r="H48" s="10"/>
       <c r="I48" s="16"/>
       <c r="J48" s="16"/>
       <c r="K48" s="16"/>
       <c r="L48" s="16"/>
       <c r="M48" s="16"/>
-    </row>
-    <row r="49" spans="1:13">
+      <c r="N48" s="16"/>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" s="10"/>
       <c r="B49" s="16"/>
       <c r="C49" s="10"/>
@@ -2324,14 +2390,15 @@
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
       <c r="G49" s="10"/>
-      <c r="H49" s="16"/>
+      <c r="H49" s="10"/>
       <c r="I49" s="16"/>
       <c r="J49" s="16"/>
       <c r="K49" s="16"/>
       <c r="L49" s="16"/>
       <c r="M49" s="16"/>
-    </row>
-    <row r="50" spans="1:13">
+      <c r="N49" s="16"/>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" s="10"/>
       <c r="B50" s="16"/>
       <c r="C50" s="10"/>
@@ -2339,14 +2406,15 @@
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
       <c r="G50" s="10"/>
-      <c r="H50" s="16"/>
+      <c r="H50" s="10"/>
       <c r="I50" s="16"/>
       <c r="J50" s="16"/>
       <c r="K50" s="16"/>
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>
-    </row>
-    <row r="51" spans="1:13">
+      <c r="N50" s="16"/>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" s="10"/>
       <c r="B51" s="16"/>
       <c r="C51" s="10"/>
@@ -2354,14 +2422,15 @@
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
       <c r="G51" s="10"/>
-      <c r="H51" s="16"/>
+      <c r="H51" s="10"/>
       <c r="I51" s="16"/>
       <c r="J51" s="16"/>
       <c r="K51" s="16"/>
       <c r="L51" s="16"/>
       <c r="M51" s="16"/>
-    </row>
-    <row r="52" spans="1:13">
+      <c r="N51" s="16"/>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" s="10"/>
       <c r="B52" s="16"/>
       <c r="C52" s="10"/>
@@ -2369,14 +2438,15 @@
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="10"/>
-      <c r="H52" s="16"/>
+      <c r="H52" s="10"/>
       <c r="I52" s="16"/>
       <c r="J52" s="16"/>
       <c r="K52" s="16"/>
       <c r="L52" s="16"/>
       <c r="M52" s="16"/>
-    </row>
-    <row r="53" spans="1:13">
+      <c r="N52" s="16"/>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" s="10"/>
       <c r="B53" s="16"/>
       <c r="C53" s="10"/>
@@ -2384,14 +2454,15 @@
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
       <c r="G53" s="10"/>
-      <c r="H53" s="16"/>
+      <c r="H53" s="10"/>
       <c r="I53" s="16"/>
       <c r="J53" s="16"/>
       <c r="K53" s="16"/>
       <c r="L53" s="16"/>
       <c r="M53" s="16"/>
-    </row>
-    <row r="54" spans="1:13">
+      <c r="N53" s="16"/>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" s="10"/>
       <c r="B54" s="16"/>
       <c r="C54" s="10"/>
@@ -2399,14 +2470,15 @@
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
       <c r="G54" s="10"/>
-      <c r="H54" s="16"/>
+      <c r="H54" s="10"/>
       <c r="I54" s="16"/>
       <c r="J54" s="16"/>
       <c r="K54" s="16"/>
       <c r="L54" s="16"/>
       <c r="M54" s="16"/>
-    </row>
-    <row r="55" spans="1:13">
+      <c r="N54" s="16"/>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" s="10"/>
       <c r="B55" s="16"/>
       <c r="C55" s="10"/>
@@ -2414,14 +2486,15 @@
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
       <c r="G55" s="10"/>
-      <c r="H55" s="16"/>
+      <c r="H55" s="10"/>
       <c r="I55" s="16"/>
       <c r="J55" s="16"/>
       <c r="K55" s="16"/>
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
-    </row>
-    <row r="56" spans="1:13">
+      <c r="N55" s="16"/>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" s="10"/>
       <c r="B56" s="16"/>
       <c r="C56" s="10"/>
@@ -2429,14 +2502,15 @@
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="G56" s="10"/>
-      <c r="H56" s="16"/>
+      <c r="H56" s="10"/>
       <c r="I56" s="16"/>
       <c r="J56" s="16"/>
       <c r="K56" s="16"/>
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
-    </row>
-    <row r="57" spans="1:13">
+      <c r="N56" s="16"/>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" s="10"/>
       <c r="B57" s="16"/>
       <c r="C57" s="10"/>
@@ -2444,14 +2518,15 @@
       <c r="E57" s="10"/>
       <c r="F57" s="10"/>
       <c r="G57" s="10"/>
-      <c r="H57" s="16"/>
+      <c r="H57" s="10"/>
       <c r="I57" s="16"/>
       <c r="J57" s="16"/>
       <c r="K57" s="16"/>
       <c r="L57" s="16"/>
       <c r="M57" s="16"/>
-    </row>
-    <row r="58" spans="1:13">
+      <c r="N57" s="16"/>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" s="10"/>
       <c r="B58" s="16"/>
       <c r="C58" s="10"/>
@@ -2459,14 +2534,15 @@
       <c r="E58" s="10"/>
       <c r="F58" s="10"/>
       <c r="G58" s="10"/>
-      <c r="H58" s="16"/>
+      <c r="H58" s="10"/>
       <c r="I58" s="16"/>
       <c r="J58" s="16"/>
       <c r="K58" s="16"/>
       <c r="L58" s="16"/>
       <c r="M58" s="16"/>
-    </row>
-    <row r="59" spans="1:13">
+      <c r="N58" s="16"/>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" s="10"/>
       <c r="B59" s="16"/>
       <c r="C59" s="10"/>
@@ -2474,14 +2550,15 @@
       <c r="E59" s="10"/>
       <c r="F59" s="10"/>
       <c r="G59" s="10"/>
-      <c r="H59" s="16"/>
+      <c r="H59" s="10"/>
       <c r="I59" s="16"/>
       <c r="J59" s="16"/>
       <c r="K59" s="16"/>
       <c r="L59" s="16"/>
       <c r="M59" s="16"/>
-    </row>
-    <row r="60" spans="1:13">
+      <c r="N59" s="16"/>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" s="10"/>
       <c r="B60" s="16"/>
       <c r="C60" s="10"/>
@@ -2489,14 +2566,15 @@
       <c r="E60" s="10"/>
       <c r="F60" s="10"/>
       <c r="G60" s="10"/>
-      <c r="H60" s="16"/>
+      <c r="H60" s="10"/>
       <c r="I60" s="16"/>
       <c r="J60" s="16"/>
       <c r="K60" s="16"/>
       <c r="L60" s="16"/>
       <c r="M60" s="16"/>
-    </row>
-    <row r="61" spans="1:13">
+      <c r="N60" s="16"/>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" s="10"/>
       <c r="B61" s="16"/>
       <c r="C61" s="10"/>
@@ -2504,14 +2582,15 @@
       <c r="E61" s="10"/>
       <c r="F61" s="10"/>
       <c r="G61" s="10"/>
-      <c r="H61" s="16"/>
+      <c r="H61" s="10"/>
       <c r="I61" s="16"/>
       <c r="J61" s="16"/>
       <c r="K61" s="16"/>
       <c r="L61" s="16"/>
       <c r="M61" s="16"/>
-    </row>
-    <row r="62" spans="1:13">
+      <c r="N61" s="16"/>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" s="10"/>
       <c r="B62" s="16"/>
       <c r="C62" s="10"/>
@@ -2519,14 +2598,15 @@
       <c r="E62" s="10"/>
       <c r="F62" s="10"/>
       <c r="G62" s="10"/>
-      <c r="H62" s="16"/>
+      <c r="H62" s="10"/>
       <c r="I62" s="16"/>
       <c r="J62" s="16"/>
       <c r="K62" s="16"/>
       <c r="L62" s="16"/>
       <c r="M62" s="16"/>
-    </row>
-    <row r="63" spans="1:13">
+      <c r="N62" s="16"/>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" s="10"/>
       <c r="B63" s="16"/>
       <c r="C63" s="10"/>
@@ -2534,14 +2614,15 @@
       <c r="E63" s="10"/>
       <c r="F63" s="10"/>
       <c r="G63" s="10"/>
-      <c r="H63" s="16"/>
+      <c r="H63" s="10"/>
       <c r="I63" s="16"/>
       <c r="J63" s="16"/>
       <c r="K63" s="16"/>
       <c r="L63" s="16"/>
       <c r="M63" s="16"/>
-    </row>
-    <row r="64" spans="1:13">
+      <c r="N63" s="16"/>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" s="10"/>
       <c r="B64" s="16"/>
       <c r="C64" s="10"/>
@@ -2549,14 +2630,15 @@
       <c r="E64" s="10"/>
       <c r="F64" s="10"/>
       <c r="G64" s="10"/>
-      <c r="H64" s="16"/>
+      <c r="H64" s="10"/>
       <c r="I64" s="16"/>
       <c r="J64" s="16"/>
       <c r="K64" s="16"/>
       <c r="L64" s="16"/>
       <c r="M64" s="16"/>
-    </row>
-    <row r="65" spans="1:13">
+      <c r="N64" s="16"/>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" s="10"/>
       <c r="B65" s="16"/>
       <c r="C65" s="10"/>
@@ -2564,14 +2646,15 @@
       <c r="E65" s="10"/>
       <c r="F65" s="10"/>
       <c r="G65" s="10"/>
-      <c r="H65" s="16"/>
+      <c r="H65" s="10"/>
       <c r="I65" s="16"/>
       <c r="J65" s="16"/>
       <c r="K65" s="16"/>
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
-    </row>
-    <row r="66" spans="1:13">
+      <c r="N65" s="16"/>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" s="10"/>
       <c r="B66" s="16"/>
       <c r="C66" s="10"/>
@@ -2579,14 +2662,15 @@
       <c r="E66" s="10"/>
       <c r="F66" s="10"/>
       <c r="G66" s="10"/>
-      <c r="H66" s="16"/>
+      <c r="H66" s="10"/>
       <c r="I66" s="16"/>
       <c r="J66" s="16"/>
       <c r="K66" s="16"/>
       <c r="L66" s="16"/>
       <c r="M66" s="16"/>
-    </row>
-    <row r="67" spans="1:13">
+      <c r="N66" s="16"/>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67" s="10"/>
       <c r="B67" s="16"/>
       <c r="C67" s="10"/>
@@ -2594,14 +2678,15 @@
       <c r="E67" s="10"/>
       <c r="F67" s="10"/>
       <c r="G67" s="10"/>
-      <c r="H67" s="16"/>
+      <c r="H67" s="10"/>
       <c r="I67" s="16"/>
       <c r="J67" s="16"/>
       <c r="K67" s="16"/>
       <c r="L67" s="16"/>
       <c r="M67" s="16"/>
-    </row>
-    <row r="68" spans="1:13">
+      <c r="N67" s="16"/>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" s="10"/>
       <c r="B68" s="16"/>
       <c r="C68" s="10"/>
@@ -2609,14 +2694,15 @@
       <c r="E68" s="10"/>
       <c r="F68" s="10"/>
       <c r="G68" s="10"/>
-      <c r="H68" s="16"/>
+      <c r="H68" s="10"/>
       <c r="I68" s="16"/>
       <c r="J68" s="16"/>
       <c r="K68" s="16"/>
       <c r="L68" s="16"/>
       <c r="M68" s="16"/>
-    </row>
-    <row r="69" spans="1:13">
+      <c r="N68" s="16"/>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" s="10"/>
       <c r="B69" s="16"/>
       <c r="C69" s="10"/>
@@ -2624,14 +2710,15 @@
       <c r="E69" s="10"/>
       <c r="F69" s="10"/>
       <c r="G69" s="10"/>
-      <c r="H69" s="16"/>
+      <c r="H69" s="10"/>
       <c r="I69" s="16"/>
       <c r="J69" s="16"/>
       <c r="K69" s="16"/>
       <c r="L69" s="16"/>
       <c r="M69" s="16"/>
-    </row>
-    <row r="70" spans="1:13">
+      <c r="N69" s="16"/>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" s="10"/>
       <c r="B70" s="16"/>
       <c r="C70" s="10"/>
@@ -2639,14 +2726,15 @@
       <c r="E70" s="10"/>
       <c r="F70" s="10"/>
       <c r="G70" s="10"/>
-      <c r="H70" s="16"/>
+      <c r="H70" s="10"/>
       <c r="I70" s="16"/>
       <c r="J70" s="16"/>
       <c r="K70" s="16"/>
       <c r="L70" s="16"/>
       <c r="M70" s="16"/>
-    </row>
-    <row r="71" spans="1:13">
+      <c r="N70" s="16"/>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" s="10"/>
       <c r="B71" s="16"/>
       <c r="C71" s="10"/>
@@ -2654,14 +2742,15 @@
       <c r="E71" s="10"/>
       <c r="F71" s="10"/>
       <c r="G71" s="10"/>
-      <c r="H71" s="16"/>
+      <c r="H71" s="10"/>
       <c r="I71" s="16"/>
       <c r="J71" s="16"/>
       <c r="K71" s="16"/>
       <c r="L71" s="16"/>
       <c r="M71" s="16"/>
-    </row>
-    <row r="72" spans="1:13">
+      <c r="N71" s="16"/>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72" s="10"/>
       <c r="B72" s="16"/>
       <c r="C72" s="10"/>
@@ -2669,14 +2758,15 @@
       <c r="E72" s="10"/>
       <c r="F72" s="10"/>
       <c r="G72" s="10"/>
-      <c r="H72" s="16"/>
+      <c r="H72" s="10"/>
       <c r="I72" s="16"/>
       <c r="J72" s="16"/>
       <c r="K72" s="16"/>
       <c r="L72" s="16"/>
       <c r="M72" s="16"/>
-    </row>
-    <row r="73" spans="1:13">
+      <c r="N72" s="16"/>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" s="10"/>
       <c r="B73" s="16"/>
       <c r="C73" s="10"/>
@@ -2684,14 +2774,15 @@
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
       <c r="G73" s="10"/>
-      <c r="H73" s="16"/>
+      <c r="H73" s="10"/>
       <c r="I73" s="16"/>
       <c r="J73" s="16"/>
       <c r="K73" s="16"/>
       <c r="L73" s="16"/>
       <c r="M73" s="16"/>
-    </row>
-    <row r="74" spans="1:13">
+      <c r="N73" s="16"/>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" s="10"/>
       <c r="B74" s="16"/>
       <c r="C74" s="10"/>
@@ -2699,14 +2790,15 @@
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
       <c r="G74" s="10"/>
-      <c r="H74" s="16"/>
+      <c r="H74" s="10"/>
       <c r="I74" s="16"/>
       <c r="J74" s="16"/>
       <c r="K74" s="16"/>
       <c r="L74" s="16"/>
       <c r="M74" s="16"/>
-    </row>
-    <row r="75" spans="1:13">
+      <c r="N74" s="16"/>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75" s="10"/>
       <c r="B75" s="16"/>
       <c r="C75" s="10"/>
@@ -2714,14 +2806,15 @@
       <c r="E75" s="10"/>
       <c r="F75" s="10"/>
       <c r="G75" s="10"/>
-      <c r="H75" s="16"/>
+      <c r="H75" s="10"/>
       <c r="I75" s="16"/>
       <c r="J75" s="16"/>
       <c r="K75" s="16"/>
       <c r="L75" s="16"/>
       <c r="M75" s="16"/>
-    </row>
-    <row r="76" spans="1:13">
+      <c r="N75" s="16"/>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76" s="10"/>
       <c r="B76" s="16"/>
       <c r="C76" s="10"/>
@@ -2729,14 +2822,15 @@
       <c r="E76" s="10"/>
       <c r="F76" s="10"/>
       <c r="G76" s="10"/>
-      <c r="H76" s="16"/>
+      <c r="H76" s="10"/>
       <c r="I76" s="16"/>
       <c r="J76" s="16"/>
       <c r="K76" s="16"/>
       <c r="L76" s="16"/>
       <c r="M76" s="16"/>
-    </row>
-    <row r="77" spans="1:13">
+      <c r="N76" s="16"/>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77" s="10"/>
       <c r="B77" s="16"/>
       <c r="C77" s="10"/>
@@ -2744,14 +2838,15 @@
       <c r="E77" s="10"/>
       <c r="F77" s="10"/>
       <c r="G77" s="10"/>
-      <c r="H77" s="16"/>
+      <c r="H77" s="10"/>
       <c r="I77" s="16"/>
       <c r="J77" s="16"/>
       <c r="K77" s="16"/>
       <c r="L77" s="16"/>
       <c r="M77" s="16"/>
-    </row>
-    <row r="78" spans="1:13">
+      <c r="N77" s="16"/>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78" s="10"/>
       <c r="B78" s="16"/>
       <c r="C78" s="10"/>
@@ -2759,14 +2854,15 @@
       <c r="E78" s="10"/>
       <c r="F78" s="10"/>
       <c r="G78" s="10"/>
-      <c r="H78" s="16"/>
+      <c r="H78" s="10"/>
       <c r="I78" s="16"/>
       <c r="J78" s="16"/>
       <c r="K78" s="16"/>
       <c r="L78" s="16"/>
       <c r="M78" s="16"/>
-    </row>
-    <row r="79" spans="1:13">
+      <c r="N78" s="16"/>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79" s="10"/>
       <c r="B79" s="16"/>
       <c r="C79" s="10"/>
@@ -2774,14 +2870,15 @@
       <c r="E79" s="10"/>
       <c r="F79" s="10"/>
       <c r="G79" s="10"/>
-      <c r="H79" s="16"/>
+      <c r="H79" s="10"/>
       <c r="I79" s="16"/>
       <c r="J79" s="16"/>
       <c r="K79" s="16"/>
       <c r="L79" s="16"/>
       <c r="M79" s="16"/>
-    </row>
-    <row r="80" spans="1:13">
+      <c r="N79" s="16"/>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80" s="10"/>
       <c r="B80" s="16"/>
       <c r="C80" s="10"/>
@@ -2789,14 +2886,15 @@
       <c r="E80" s="10"/>
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
-      <c r="H80" s="16"/>
+      <c r="H80" s="10"/>
       <c r="I80" s="16"/>
       <c r="J80" s="16"/>
       <c r="K80" s="16"/>
       <c r="L80" s="16"/>
       <c r="M80" s="16"/>
-    </row>
-    <row r="81" spans="1:13">
+      <c r="N80" s="16"/>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" s="10"/>
       <c r="B81" s="16"/>
       <c r="C81" s="10"/>
@@ -2804,14 +2902,15 @@
       <c r="E81" s="10"/>
       <c r="F81" s="10"/>
       <c r="G81" s="10"/>
-      <c r="H81" s="16"/>
+      <c r="H81" s="10"/>
       <c r="I81" s="16"/>
       <c r="J81" s="16"/>
       <c r="K81" s="16"/>
       <c r="L81" s="16"/>
       <c r="M81" s="16"/>
-    </row>
-    <row r="82" spans="1:13">
+      <c r="N81" s="16"/>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82" s="10"/>
       <c r="B82" s="16"/>
       <c r="C82" s="10"/>
@@ -2819,14 +2918,15 @@
       <c r="E82" s="10"/>
       <c r="F82" s="10"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="16"/>
+      <c r="H82" s="10"/>
       <c r="I82" s="16"/>
       <c r="J82" s="16"/>
       <c r="K82" s="16"/>
       <c r="L82" s="16"/>
       <c r="M82" s="16"/>
-    </row>
-    <row r="83" spans="1:13">
+      <c r="N82" s="16"/>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83" s="10"/>
       <c r="B83" s="16"/>
       <c r="C83" s="10"/>
@@ -2834,14 +2934,15 @@
       <c r="E83" s="10"/>
       <c r="F83" s="10"/>
       <c r="G83" s="10"/>
-      <c r="H83" s="16"/>
+      <c r="H83" s="10"/>
       <c r="I83" s="16"/>
       <c r="J83" s="16"/>
       <c r="K83" s="16"/>
       <c r="L83" s="16"/>
       <c r="M83" s="16"/>
-    </row>
-    <row r="84" spans="1:13">
+      <c r="N83" s="16"/>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84" s="10"/>
       <c r="B84" s="16"/>
       <c r="C84" s="10"/>
@@ -2849,14 +2950,15 @@
       <c r="E84" s="10"/>
       <c r="F84" s="10"/>
       <c r="G84" s="10"/>
-      <c r="H84" s="16"/>
+      <c r="H84" s="10"/>
       <c r="I84" s="16"/>
       <c r="J84" s="16"/>
       <c r="K84" s="16"/>
       <c r="L84" s="16"/>
       <c r="M84" s="16"/>
-    </row>
-    <row r="85" spans="1:13">
+      <c r="N84" s="16"/>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85" s="10"/>
       <c r="B85" s="16"/>
       <c r="C85" s="10"/>
@@ -2864,14 +2966,15 @@
       <c r="E85" s="10"/>
       <c r="F85" s="10"/>
       <c r="G85" s="10"/>
-      <c r="H85" s="16"/>
+      <c r="H85" s="10"/>
       <c r="I85" s="16"/>
       <c r="J85" s="16"/>
       <c r="K85" s="16"/>
       <c r="L85" s="16"/>
       <c r="M85" s="16"/>
-    </row>
-    <row r="86" spans="1:13">
+      <c r="N85" s="16"/>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86" s="10"/>
       <c r="B86" s="16"/>
       <c r="C86" s="10"/>
@@ -2879,14 +2982,15 @@
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
       <c r="G86" s="10"/>
-      <c r="H86" s="16"/>
+      <c r="H86" s="10"/>
       <c r="I86" s="16"/>
       <c r="J86" s="16"/>
       <c r="K86" s="16"/>
       <c r="L86" s="16"/>
       <c r="M86" s="16"/>
-    </row>
-    <row r="87" spans="1:13">
+      <c r="N86" s="16"/>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87" s="10"/>
       <c r="B87" s="16"/>
       <c r="C87" s="10"/>
@@ -2894,14 +2998,15 @@
       <c r="E87" s="10"/>
       <c r="F87" s="10"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="16"/>
+      <c r="H87" s="10"/>
       <c r="I87" s="16"/>
       <c r="J87" s="16"/>
       <c r="K87" s="16"/>
       <c r="L87" s="16"/>
       <c r="M87" s="16"/>
-    </row>
-    <row r="88" spans="1:13">
+      <c r="N87" s="16"/>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88" s="10"/>
       <c r="B88" s="16"/>
       <c r="C88" s="10"/>
@@ -2909,14 +3014,15 @@
       <c r="E88" s="10"/>
       <c r="F88" s="10"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="16"/>
+      <c r="H88" s="10"/>
       <c r="I88" s="16"/>
       <c r="J88" s="16"/>
       <c r="K88" s="16"/>
       <c r="L88" s="16"/>
       <c r="M88" s="16"/>
-    </row>
-    <row r="89" spans="1:13">
+      <c r="N88" s="16"/>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89" s="10"/>
       <c r="B89" s="16"/>
       <c r="C89" s="10"/>
@@ -2924,14 +3030,15 @@
       <c r="E89" s="10"/>
       <c r="F89" s="10"/>
       <c r="G89" s="10"/>
-      <c r="H89" s="16"/>
+      <c r="H89" s="10"/>
       <c r="I89" s="16"/>
       <c r="J89" s="16"/>
       <c r="K89" s="16"/>
       <c r="L89" s="16"/>
       <c r="M89" s="16"/>
-    </row>
-    <row r="90" spans="1:13">
+      <c r="N89" s="16"/>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90" s="10"/>
       <c r="B90" s="16"/>
       <c r="C90" s="10"/>
@@ -2939,14 +3046,15 @@
       <c r="E90" s="10"/>
       <c r="F90" s="10"/>
       <c r="G90" s="10"/>
-      <c r="H90" s="16"/>
+      <c r="H90" s="10"/>
       <c r="I90" s="16"/>
       <c r="J90" s="16"/>
       <c r="K90" s="16"/>
       <c r="L90" s="16"/>
       <c r="M90" s="16"/>
-    </row>
-    <row r="91" spans="1:13">
+      <c r="N90" s="16"/>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91" s="10"/>
       <c r="B91" s="16"/>
       <c r="C91" s="10"/>
@@ -2954,14 +3062,15 @@
       <c r="E91" s="10"/>
       <c r="F91" s="10"/>
       <c r="G91" s="10"/>
-      <c r="H91" s="16"/>
+      <c r="H91" s="10"/>
       <c r="I91" s="16"/>
       <c r="J91" s="16"/>
       <c r="K91" s="16"/>
       <c r="L91" s="16"/>
       <c r="M91" s="16"/>
-    </row>
-    <row r="92" spans="1:13">
+      <c r="N91" s="16"/>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92" s="10"/>
       <c r="B92" s="16"/>
       <c r="C92" s="10"/>
@@ -2969,14 +3078,15 @@
       <c r="E92" s="10"/>
       <c r="F92" s="10"/>
       <c r="G92" s="10"/>
-      <c r="H92" s="16"/>
+      <c r="H92" s="10"/>
       <c r="I92" s="16"/>
       <c r="J92" s="16"/>
       <c r="K92" s="16"/>
       <c r="L92" s="16"/>
       <c r="M92" s="16"/>
-    </row>
-    <row r="93" spans="1:13">
+      <c r="N92" s="16"/>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93" s="10"/>
       <c r="B93" s="16"/>
       <c r="C93" s="10"/>
@@ -2984,14 +3094,15 @@
       <c r="E93" s="10"/>
       <c r="F93" s="10"/>
       <c r="G93" s="10"/>
-      <c r="H93" s="16"/>
+      <c r="H93" s="10"/>
       <c r="I93" s="16"/>
       <c r="J93" s="16"/>
       <c r="K93" s="16"/>
       <c r="L93" s="16"/>
       <c r="M93" s="16"/>
-    </row>
-    <row r="94" spans="1:13">
+      <c r="N93" s="16"/>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94" s="10"/>
       <c r="B94" s="16"/>
       <c r="C94" s="10"/>
@@ -2999,14 +3110,15 @@
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
       <c r="G94" s="10"/>
-      <c r="H94" s="16"/>
+      <c r="H94" s="10"/>
       <c r="I94" s="16"/>
       <c r="J94" s="16"/>
       <c r="K94" s="16"/>
       <c r="L94" s="16"/>
       <c r="M94" s="16"/>
-    </row>
-    <row r="95" spans="1:13">
+      <c r="N94" s="16"/>
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95" s="10"/>
       <c r="B95" s="16"/>
       <c r="C95" s="10"/>
@@ -3014,14 +3126,15 @@
       <c r="E95" s="10"/>
       <c r="F95" s="10"/>
       <c r="G95" s="10"/>
-      <c r="H95" s="16"/>
+      <c r="H95" s="10"/>
       <c r="I95" s="16"/>
       <c r="J95" s="16"/>
       <c r="K95" s="16"/>
       <c r="L95" s="16"/>
       <c r="M95" s="16"/>
-    </row>
-    <row r="96" spans="1:13">
+      <c r="N95" s="16"/>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96" s="10"/>
       <c r="B96" s="16"/>
       <c r="C96" s="10"/>
@@ -3029,14 +3142,15 @@
       <c r="E96" s="10"/>
       <c r="F96" s="10"/>
       <c r="G96" s="10"/>
-      <c r="H96" s="16"/>
+      <c r="H96" s="10"/>
       <c r="I96" s="16"/>
       <c r="J96" s="16"/>
       <c r="K96" s="16"/>
       <c r="L96" s="16"/>
       <c r="M96" s="16"/>
-    </row>
-    <row r="97" spans="1:13">
+      <c r="N96" s="16"/>
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97" s="10"/>
       <c r="B97" s="16"/>
       <c r="C97" s="10"/>
@@ -3044,14 +3158,15 @@
       <c r="E97" s="10"/>
       <c r="F97" s="10"/>
       <c r="G97" s="10"/>
-      <c r="H97" s="16"/>
+      <c r="H97" s="10"/>
       <c r="I97" s="16"/>
       <c r="J97" s="16"/>
       <c r="K97" s="16"/>
       <c r="L97" s="16"/>
       <c r="M97" s="16"/>
-    </row>
-    <row r="98" spans="1:13">
+      <c r="N97" s="16"/>
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98" s="10"/>
       <c r="B98" s="16"/>
       <c r="C98" s="10"/>
@@ -3059,14 +3174,15 @@
       <c r="E98" s="10"/>
       <c r="F98" s="10"/>
       <c r="G98" s="10"/>
-      <c r="H98" s="16"/>
+      <c r="H98" s="10"/>
       <c r="I98" s="16"/>
       <c r="J98" s="16"/>
       <c r="K98" s="16"/>
       <c r="L98" s="16"/>
       <c r="M98" s="16"/>
-    </row>
-    <row r="99" spans="1:13">
+      <c r="N98" s="16"/>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99" s="10"/>
       <c r="B99" s="16"/>
       <c r="C99" s="10"/>
@@ -3074,14 +3190,15 @@
       <c r="E99" s="10"/>
       <c r="F99" s="10"/>
       <c r="G99" s="10"/>
-      <c r="H99" s="16"/>
+      <c r="H99" s="10"/>
       <c r="I99" s="16"/>
       <c r="J99" s="16"/>
       <c r="K99" s="16"/>
       <c r="L99" s="16"/>
       <c r="M99" s="16"/>
-    </row>
-    <row r="100" spans="1:13">
+      <c r="N99" s="16"/>
+    </row>
+    <row r="100" spans="1:14">
       <c r="A100" s="10"/>
       <c r="B100" s="16"/>
       <c r="C100" s="10"/>
@@ -3089,14 +3206,15 @@
       <c r="E100" s="10"/>
       <c r="F100" s="10"/>
       <c r="G100" s="10"/>
-      <c r="H100" s="16"/>
+      <c r="H100" s="10"/>
       <c r="I100" s="16"/>
       <c r="J100" s="16"/>
       <c r="K100" s="16"/>
       <c r="L100" s="16"/>
       <c r="M100" s="16"/>
-    </row>
-    <row r="101" spans="1:13">
+      <c r="N100" s="16"/>
+    </row>
+    <row r="101" spans="1:14">
       <c r="A101" s="10"/>
       <c r="B101" s="16"/>
       <c r="C101" s="10"/>
@@ -3104,14 +3222,15 @@
       <c r="E101" s="10"/>
       <c r="F101" s="10"/>
       <c r="G101" s="10"/>
-      <c r="H101" s="16"/>
+      <c r="H101" s="10"/>
       <c r="I101" s="16"/>
       <c r="J101" s="16"/>
       <c r="K101" s="16"/>
       <c r="L101" s="16"/>
       <c r="M101" s="16"/>
-    </row>
-    <row r="102" spans="1:13">
+      <c r="N101" s="16"/>
+    </row>
+    <row r="102" spans="1:14">
       <c r="A102" s="10"/>
       <c r="B102" s="16"/>
       <c r="C102" s="10"/>
@@ -3119,14 +3238,15 @@
       <c r="E102" s="10"/>
       <c r="F102" s="10"/>
       <c r="G102" s="10"/>
-      <c r="H102" s="16"/>
+      <c r="H102" s="10"/>
       <c r="I102" s="16"/>
       <c r="J102" s="16"/>
       <c r="K102" s="16"/>
       <c r="L102" s="16"/>
       <c r="M102" s="16"/>
-    </row>
-    <row r="103" spans="1:13">
+      <c r="N102" s="16"/>
+    </row>
+    <row r="103" spans="1:14">
       <c r="A103" s="10"/>
       <c r="B103" s="16"/>
       <c r="C103" s="10"/>
@@ -3134,14 +3254,15 @@
       <c r="E103" s="10"/>
       <c r="F103" s="10"/>
       <c r="G103" s="10"/>
-      <c r="H103" s="16"/>
+      <c r="H103" s="10"/>
       <c r="I103" s="16"/>
       <c r="J103" s="16"/>
       <c r="K103" s="16"/>
       <c r="L103" s="16"/>
       <c r="M103" s="16"/>
-    </row>
-    <row r="104" spans="1:13">
+      <c r="N103" s="16"/>
+    </row>
+    <row r="104" spans="1:14">
       <c r="A104" s="10"/>
       <c r="B104" s="16"/>
       <c r="C104" s="10"/>
@@ -3149,14 +3270,15 @@
       <c r="E104" s="10"/>
       <c r="F104" s="10"/>
       <c r="G104" s="10"/>
-      <c r="H104" s="16"/>
+      <c r="H104" s="10"/>
       <c r="I104" s="16"/>
       <c r="J104" s="16"/>
       <c r="K104" s="16"/>
       <c r="L104" s="16"/>
       <c r="M104" s="16"/>
-    </row>
-    <row r="105" spans="1:13">
+      <c r="N104" s="16"/>
+    </row>
+    <row r="105" spans="1:14">
       <c r="A105" s="10"/>
       <c r="B105" s="16"/>
       <c r="C105" s="10"/>
@@ -3164,14 +3286,15 @@
       <c r="E105" s="10"/>
       <c r="F105" s="10"/>
       <c r="G105" s="10"/>
-      <c r="H105" s="16"/>
+      <c r="H105" s="10"/>
       <c r="I105" s="16"/>
       <c r="J105" s="16"/>
       <c r="K105" s="16"/>
       <c r="L105" s="16"/>
       <c r="M105" s="16"/>
-    </row>
-    <row r="106" spans="1:13">
+      <c r="N105" s="16"/>
+    </row>
+    <row r="106" spans="1:14">
       <c r="A106" s="10"/>
       <c r="B106" s="16"/>
       <c r="C106" s="10"/>
@@ -3179,14 +3302,15 @@
       <c r="E106" s="10"/>
       <c r="F106" s="10"/>
       <c r="G106" s="10"/>
-      <c r="H106" s="16"/>
+      <c r="H106" s="10"/>
       <c r="I106" s="16"/>
       <c r="J106" s="16"/>
       <c r="K106" s="16"/>
       <c r="L106" s="16"/>
       <c r="M106" s="16"/>
-    </row>
-    <row r="107" spans="1:13">
+      <c r="N106" s="16"/>
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107" s="10"/>
       <c r="B107" s="16"/>
       <c r="C107" s="10"/>
@@ -3194,14 +3318,15 @@
       <c r="E107" s="10"/>
       <c r="F107" s="10"/>
       <c r="G107" s="10"/>
-      <c r="H107" s="16"/>
+      <c r="H107" s="10"/>
       <c r="I107" s="16"/>
       <c r="J107" s="16"/>
       <c r="K107" s="16"/>
       <c r="L107" s="16"/>
       <c r="M107" s="16"/>
-    </row>
-    <row r="108" spans="1:13">
+      <c r="N107" s="16"/>
+    </row>
+    <row r="108" spans="1:14">
       <c r="A108" s="10"/>
       <c r="B108" s="16"/>
       <c r="C108" s="10"/>
@@ -3209,14 +3334,15 @@
       <c r="E108" s="10"/>
       <c r="F108" s="10"/>
       <c r="G108" s="10"/>
-      <c r="H108" s="16"/>
+      <c r="H108" s="10"/>
       <c r="I108" s="16"/>
       <c r="J108" s="16"/>
       <c r="K108" s="16"/>
       <c r="L108" s="16"/>
       <c r="M108" s="16"/>
-    </row>
-    <row r="109" spans="1:13">
+      <c r="N108" s="16"/>
+    </row>
+    <row r="109" spans="1:14">
       <c r="A109" s="10"/>
       <c r="B109" s="16"/>
       <c r="C109" s="10"/>
@@ -3224,14 +3350,15 @@
       <c r="E109" s="10"/>
       <c r="F109" s="10"/>
       <c r="G109" s="10"/>
-      <c r="H109" s="16"/>
+      <c r="H109" s="10"/>
       <c r="I109" s="16"/>
       <c r="J109" s="16"/>
       <c r="K109" s="16"/>
       <c r="L109" s="16"/>
       <c r="M109" s="16"/>
-    </row>
-    <row r="110" spans="1:13">
+      <c r="N109" s="16"/>
+    </row>
+    <row r="110" spans="1:14">
       <c r="A110" s="10"/>
       <c r="B110" s="16"/>
       <c r="C110" s="10"/>
@@ -3239,14 +3366,15 @@
       <c r="E110" s="10"/>
       <c r="F110" s="10"/>
       <c r="G110" s="10"/>
-      <c r="H110" s="16"/>
+      <c r="H110" s="10"/>
       <c r="I110" s="16"/>
       <c r="J110" s="16"/>
       <c r="K110" s="16"/>
       <c r="L110" s="16"/>
       <c r="M110" s="16"/>
-    </row>
-    <row r="111" spans="1:13">
+      <c r="N110" s="16"/>
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111" s="10"/>
       <c r="B111" s="16"/>
       <c r="C111" s="10"/>
@@ -3254,14 +3382,15 @@
       <c r="E111" s="10"/>
       <c r="F111" s="10"/>
       <c r="G111" s="10"/>
-      <c r="H111" s="16"/>
+      <c r="H111" s="10"/>
       <c r="I111" s="16"/>
       <c r="J111" s="16"/>
       <c r="K111" s="16"/>
       <c r="L111" s="16"/>
       <c r="M111" s="16"/>
-    </row>
-    <row r="112" spans="1:13">
+      <c r="N111" s="16"/>
+    </row>
+    <row r="112" spans="1:14">
       <c r="A112" s="10"/>
       <c r="B112" s="16"/>
       <c r="C112" s="10"/>
@@ -3269,14 +3398,15 @@
       <c r="E112" s="10"/>
       <c r="F112" s="10"/>
       <c r="G112" s="10"/>
-      <c r="H112" s="16"/>
+      <c r="H112" s="10"/>
       <c r="I112" s="16"/>
       <c r="J112" s="16"/>
       <c r="K112" s="16"/>
       <c r="L112" s="16"/>
       <c r="M112" s="16"/>
-    </row>
-    <row r="113" spans="1:13">
+      <c r="N112" s="16"/>
+    </row>
+    <row r="113" spans="1:14">
       <c r="A113" s="10"/>
       <c r="B113" s="16"/>
       <c r="C113" s="10"/>
@@ -3284,14 +3414,15 @@
       <c r="E113" s="10"/>
       <c r="F113" s="10"/>
       <c r="G113" s="10"/>
-      <c r="H113" s="16"/>
+      <c r="H113" s="10"/>
       <c r="I113" s="16"/>
       <c r="J113" s="16"/>
       <c r="K113" s="16"/>
       <c r="L113" s="16"/>
       <c r="M113" s="16"/>
-    </row>
-    <row r="114" spans="1:13">
+      <c r="N113" s="16"/>
+    </row>
+    <row r="114" spans="1:14">
       <c r="A114" s="10"/>
       <c r="B114" s="16"/>
       <c r="C114" s="10"/>
@@ -3299,14 +3430,15 @@
       <c r="E114" s="10"/>
       <c r="F114" s="10"/>
       <c r="G114" s="10"/>
-      <c r="H114" s="16"/>
+      <c r="H114" s="10"/>
       <c r="I114" s="16"/>
       <c r="J114" s="16"/>
       <c r="K114" s="16"/>
       <c r="L114" s="16"/>
       <c r="M114" s="16"/>
-    </row>
-    <row r="115" spans="1:13">
+      <c r="N114" s="16"/>
+    </row>
+    <row r="115" spans="1:14">
       <c r="A115" s="10"/>
       <c r="B115" s="16"/>
       <c r="C115" s="10"/>
@@ -3314,14 +3446,15 @@
       <c r="E115" s="10"/>
       <c r="F115" s="10"/>
       <c r="G115" s="10"/>
-      <c r="H115" s="16"/>
+      <c r="H115" s="10"/>
       <c r="I115" s="16"/>
       <c r="J115" s="16"/>
       <c r="K115" s="16"/>
       <c r="L115" s="16"/>
       <c r="M115" s="16"/>
-    </row>
-    <row r="116" spans="1:13">
+      <c r="N115" s="16"/>
+    </row>
+    <row r="116" spans="1:14">
       <c r="A116" s="10"/>
       <c r="B116" s="16"/>
       <c r="C116" s="10"/>
@@ -3329,14 +3462,15 @@
       <c r="E116" s="10"/>
       <c r="F116" s="10"/>
       <c r="G116" s="10"/>
-      <c r="H116" s="16"/>
+      <c r="H116" s="10"/>
       <c r="I116" s="16"/>
       <c r="J116" s="16"/>
       <c r="K116" s="16"/>
       <c r="L116" s="16"/>
       <c r="M116" s="16"/>
-    </row>
-    <row r="117" spans="1:13">
+      <c r="N116" s="16"/>
+    </row>
+    <row r="117" spans="1:14">
       <c r="A117" s="10"/>
       <c r="B117" s="16"/>
       <c r="C117" s="10"/>
@@ -3344,14 +3478,15 @@
       <c r="E117" s="10"/>
       <c r="F117" s="10"/>
       <c r="G117" s="10"/>
-      <c r="H117" s="16"/>
+      <c r="H117" s="10"/>
       <c r="I117" s="16"/>
       <c r="J117" s="16"/>
       <c r="K117" s="16"/>
       <c r="L117" s="16"/>
       <c r="M117" s="16"/>
-    </row>
-    <row r="118" spans="1:13">
+      <c r="N117" s="16"/>
+    </row>
+    <row r="118" spans="1:14">
       <c r="A118" s="10"/>
       <c r="B118" s="16"/>
       <c r="C118" s="10"/>
@@ -3359,14 +3494,15 @@
       <c r="E118" s="10"/>
       <c r="F118" s="10"/>
       <c r="G118" s="10"/>
-      <c r="H118" s="16"/>
+      <c r="H118" s="10"/>
       <c r="I118" s="16"/>
       <c r="J118" s="16"/>
       <c r="K118" s="16"/>
       <c r="L118" s="16"/>
       <c r="M118" s="16"/>
-    </row>
-    <row r="119" spans="1:13">
+      <c r="N118" s="16"/>
+    </row>
+    <row r="119" spans="1:14">
       <c r="A119" s="10"/>
       <c r="B119" s="16"/>
       <c r="C119" s="10"/>
@@ -3374,14 +3510,15 @@
       <c r="E119" s="10"/>
       <c r="F119" s="10"/>
       <c r="G119" s="10"/>
-      <c r="H119" s="16"/>
+      <c r="H119" s="10"/>
       <c r="I119" s="16"/>
       <c r="J119" s="16"/>
       <c r="K119" s="16"/>
       <c r="L119" s="16"/>
       <c r="M119" s="16"/>
-    </row>
-    <row r="120" spans="1:13">
+      <c r="N119" s="16"/>
+    </row>
+    <row r="120" spans="1:14">
       <c r="A120" s="10"/>
       <c r="B120" s="16"/>
       <c r="C120" s="10"/>
@@ -3389,14 +3526,15 @@
       <c r="E120" s="10"/>
       <c r="F120" s="10"/>
       <c r="G120" s="10"/>
-      <c r="H120" s="16"/>
+      <c r="H120" s="10"/>
       <c r="I120" s="16"/>
       <c r="J120" s="16"/>
       <c r="K120" s="16"/>
       <c r="L120" s="16"/>
       <c r="M120" s="16"/>
-    </row>
-    <row r="121" spans="1:13">
+      <c r="N120" s="16"/>
+    </row>
+    <row r="121" spans="1:14">
       <c r="A121" s="10"/>
       <c r="B121" s="16"/>
       <c r="C121" s="10"/>
@@ -3404,14 +3542,15 @@
       <c r="E121" s="10"/>
       <c r="F121" s="10"/>
       <c r="G121" s="10"/>
-      <c r="H121" s="16"/>
+      <c r="H121" s="10"/>
       <c r="I121" s="16"/>
       <c r="J121" s="16"/>
       <c r="K121" s="16"/>
       <c r="L121" s="16"/>
       <c r="M121" s="16"/>
-    </row>
-    <row r="122" spans="1:13">
+      <c r="N121" s="16"/>
+    </row>
+    <row r="122" spans="1:14">
       <c r="A122" s="10"/>
       <c r="B122" s="16"/>
       <c r="C122" s="10"/>
@@ -3419,14 +3558,15 @@
       <c r="E122" s="10"/>
       <c r="F122" s="10"/>
       <c r="G122" s="10"/>
-      <c r="H122" s="16"/>
+      <c r="H122" s="10"/>
       <c r="I122" s="16"/>
       <c r="J122" s="16"/>
       <c r="K122" s="16"/>
       <c r="L122" s="16"/>
       <c r="M122" s="16"/>
-    </row>
-    <row r="123" spans="1:13">
+      <c r="N122" s="16"/>
+    </row>
+    <row r="123" spans="1:14">
       <c r="A123" s="10"/>
       <c r="B123" s="16"/>
       <c r="C123" s="10"/>
@@ -3434,14 +3574,15 @@
       <c r="E123" s="10"/>
       <c r="F123" s="10"/>
       <c r="G123" s="10"/>
-      <c r="H123" s="16"/>
+      <c r="H123" s="10"/>
       <c r="I123" s="16"/>
       <c r="J123" s="16"/>
       <c r="K123" s="16"/>
       <c r="L123" s="16"/>
       <c r="M123" s="16"/>
-    </row>
-    <row r="124" spans="1:13">
+      <c r="N123" s="16"/>
+    </row>
+    <row r="124" spans="1:14">
       <c r="A124" s="10"/>
       <c r="B124" s="16"/>
       <c r="C124" s="10"/>
@@ -3449,14 +3590,15 @@
       <c r="E124" s="10"/>
       <c r="F124" s="10"/>
       <c r="G124" s="10"/>
-      <c r="H124" s="16"/>
+      <c r="H124" s="10"/>
       <c r="I124" s="16"/>
       <c r="J124" s="16"/>
       <c r="K124" s="16"/>
       <c r="L124" s="16"/>
       <c r="M124" s="16"/>
-    </row>
-    <row r="125" spans="1:13">
+      <c r="N124" s="16"/>
+    </row>
+    <row r="125" spans="1:14">
       <c r="A125" s="10"/>
       <c r="B125" s="16"/>
       <c r="C125" s="10"/>
@@ -3464,14 +3606,15 @@
       <c r="E125" s="10"/>
       <c r="F125" s="10"/>
       <c r="G125" s="10"/>
-      <c r="H125" s="16"/>
+      <c r="H125" s="10"/>
       <c r="I125" s="16"/>
       <c r="J125" s="16"/>
       <c r="K125" s="16"/>
       <c r="L125" s="16"/>
       <c r="M125" s="16"/>
-    </row>
-    <row r="126" spans="1:13">
+      <c r="N125" s="16"/>
+    </row>
+    <row r="126" spans="1:14">
       <c r="A126" s="10"/>
       <c r="B126" s="16"/>
       <c r="C126" s="10"/>
@@ -3479,14 +3622,15 @@
       <c r="E126" s="10"/>
       <c r="F126" s="10"/>
       <c r="G126" s="10"/>
-      <c r="H126" s="16"/>
+      <c r="H126" s="10"/>
       <c r="I126" s="16"/>
       <c r="J126" s="16"/>
       <c r="K126" s="16"/>
       <c r="L126" s="16"/>
       <c r="M126" s="16"/>
-    </row>
-    <row r="127" spans="1:13">
+      <c r="N126" s="16"/>
+    </row>
+    <row r="127" spans="1:14">
       <c r="A127" s="10"/>
       <c r="B127" s="16"/>
       <c r="C127" s="10"/>
@@ -3494,14 +3638,15 @@
       <c r="E127" s="10"/>
       <c r="F127" s="10"/>
       <c r="G127" s="10"/>
-      <c r="H127" s="16"/>
+      <c r="H127" s="10"/>
       <c r="I127" s="16"/>
       <c r="J127" s="16"/>
       <c r="K127" s="16"/>
       <c r="L127" s="16"/>
       <c r="M127" s="16"/>
-    </row>
-    <row r="128" spans="1:13">
+      <c r="N127" s="16"/>
+    </row>
+    <row r="128" spans="1:14">
       <c r="A128" s="10"/>
       <c r="B128" s="16"/>
       <c r="C128" s="10"/>
@@ -3509,14 +3654,15 @@
       <c r="E128" s="10"/>
       <c r="F128" s="10"/>
       <c r="G128" s="10"/>
-      <c r="H128" s="16"/>
+      <c r="H128" s="10"/>
       <c r="I128" s="16"/>
       <c r="J128" s="16"/>
       <c r="K128" s="16"/>
       <c r="L128" s="16"/>
       <c r="M128" s="16"/>
-    </row>
-    <row r="129" spans="1:13">
+      <c r="N128" s="16"/>
+    </row>
+    <row r="129" spans="1:14">
       <c r="A129" s="10"/>
       <c r="B129" s="16"/>
       <c r="C129" s="10"/>
@@ -3524,14 +3670,15 @@
       <c r="E129" s="10"/>
       <c r="F129" s="10"/>
       <c r="G129" s="10"/>
-      <c r="H129" s="16"/>
+      <c r="H129" s="10"/>
       <c r="I129" s="16"/>
       <c r="J129" s="16"/>
       <c r="K129" s="16"/>
       <c r="L129" s="16"/>
       <c r="M129" s="16"/>
-    </row>
-    <row r="130" spans="1:13">
+      <c r="N129" s="16"/>
+    </row>
+    <row r="130" spans="1:14">
       <c r="A130" s="10"/>
       <c r="B130" s="16"/>
       <c r="C130" s="10"/>
@@ -3539,14 +3686,15 @@
       <c r="E130" s="10"/>
       <c r="F130" s="10"/>
       <c r="G130" s="10"/>
-      <c r="H130" s="16"/>
+      <c r="H130" s="10"/>
       <c r="I130" s="16"/>
       <c r="J130" s="16"/>
       <c r="K130" s="16"/>
       <c r="L130" s="16"/>
       <c r="M130" s="16"/>
-    </row>
-    <row r="131" spans="1:13">
+      <c r="N130" s="16"/>
+    </row>
+    <row r="131" spans="1:14">
       <c r="A131" s="10"/>
       <c r="B131" s="16"/>
       <c r="C131" s="10"/>
@@ -3554,14 +3702,15 @@
       <c r="E131" s="10"/>
       <c r="F131" s="10"/>
       <c r="G131" s="10"/>
-      <c r="H131" s="16"/>
+      <c r="H131" s="10"/>
       <c r="I131" s="16"/>
       <c r="J131" s="16"/>
       <c r="K131" s="16"/>
       <c r="L131" s="16"/>
       <c r="M131" s="16"/>
-    </row>
-    <row r="132" spans="1:13">
+      <c r="N131" s="16"/>
+    </row>
+    <row r="132" spans="1:14">
       <c r="A132" s="10"/>
       <c r="B132" s="16"/>
       <c r="C132" s="10"/>
@@ -3569,14 +3718,15 @@
       <c r="E132" s="10"/>
       <c r="F132" s="10"/>
       <c r="G132" s="10"/>
-      <c r="H132" s="16"/>
+      <c r="H132" s="10"/>
       <c r="I132" s="16"/>
       <c r="J132" s="16"/>
       <c r="K132" s="16"/>
       <c r="L132" s="16"/>
       <c r="M132" s="16"/>
-    </row>
-    <row r="133" spans="1:13">
+      <c r="N132" s="16"/>
+    </row>
+    <row r="133" spans="1:14">
       <c r="A133" s="10"/>
       <c r="B133" s="16"/>
       <c r="C133" s="10"/>
@@ -3584,14 +3734,15 @@
       <c r="E133" s="10"/>
       <c r="F133" s="10"/>
       <c r="G133" s="10"/>
-      <c r="H133" s="16"/>
+      <c r="H133" s="10"/>
       <c r="I133" s="16"/>
       <c r="J133" s="16"/>
       <c r="K133" s="16"/>
       <c r="L133" s="16"/>
       <c r="M133" s="16"/>
-    </row>
-    <row r="134" spans="1:13">
+      <c r="N133" s="16"/>
+    </row>
+    <row r="134" spans="1:14">
       <c r="A134" s="10"/>
       <c r="B134" s="16"/>
       <c r="C134" s="10"/>
@@ -3599,14 +3750,15 @@
       <c r="E134" s="10"/>
       <c r="F134" s="10"/>
       <c r="G134" s="10"/>
-      <c r="H134" s="16"/>
+      <c r="H134" s="10"/>
       <c r="I134" s="16"/>
       <c r="J134" s="16"/>
       <c r="K134" s="16"/>
       <c r="L134" s="16"/>
       <c r="M134" s="16"/>
-    </row>
-    <row r="135" spans="1:13">
+      <c r="N134" s="16"/>
+    </row>
+    <row r="135" spans="1:14">
       <c r="A135" s="10"/>
       <c r="B135" s="16"/>
       <c r="C135" s="10"/>
@@ -3614,14 +3766,15 @@
       <c r="E135" s="10"/>
       <c r="F135" s="10"/>
       <c r="G135" s="10"/>
-      <c r="H135" s="16"/>
+      <c r="H135" s="10"/>
       <c r="I135" s="16"/>
       <c r="J135" s="16"/>
       <c r="K135" s="16"/>
       <c r="L135" s="16"/>
       <c r="M135" s="16"/>
-    </row>
-    <row r="136" spans="1:13">
+      <c r="N135" s="16"/>
+    </row>
+    <row r="136" spans="1:14">
       <c r="A136" s="10"/>
       <c r="B136" s="16"/>
       <c r="C136" s="10"/>
@@ -3629,14 +3782,15 @@
       <c r="E136" s="10"/>
       <c r="F136" s="10"/>
       <c r="G136" s="10"/>
-      <c r="H136" s="16"/>
+      <c r="H136" s="10"/>
       <c r="I136" s="16"/>
       <c r="J136" s="16"/>
       <c r="K136" s="16"/>
       <c r="L136" s="16"/>
       <c r="M136" s="16"/>
-    </row>
-    <row r="137" spans="1:13">
+      <c r="N136" s="16"/>
+    </row>
+    <row r="137" spans="1:14">
       <c r="A137" s="10"/>
       <c r="B137" s="16"/>
       <c r="C137" s="10"/>
@@ -3644,14 +3798,15 @@
       <c r="E137" s="10"/>
       <c r="F137" s="10"/>
       <c r="G137" s="10"/>
-      <c r="H137" s="16"/>
+      <c r="H137" s="10"/>
       <c r="I137" s="16"/>
       <c r="J137" s="16"/>
       <c r="K137" s="16"/>
       <c r="L137" s="16"/>
       <c r="M137" s="16"/>
-    </row>
-    <row r="138" spans="1:13">
+      <c r="N137" s="16"/>
+    </row>
+    <row r="138" spans="1:14">
       <c r="A138" s="10"/>
       <c r="B138" s="16"/>
       <c r="C138" s="10"/>
@@ -3659,14 +3814,15 @@
       <c r="E138" s="10"/>
       <c r="F138" s="10"/>
       <c r="G138" s="10"/>
-      <c r="H138" s="16"/>
+      <c r="H138" s="10"/>
       <c r="I138" s="16"/>
       <c r="J138" s="16"/>
       <c r="K138" s="16"/>
       <c r="L138" s="16"/>
       <c r="M138" s="16"/>
-    </row>
-    <row r="139" spans="1:13">
+      <c r="N138" s="16"/>
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139" s="10"/>
       <c r="B139" s="16"/>
       <c r="C139" s="10"/>
@@ -3674,14 +3830,15 @@
       <c r="E139" s="10"/>
       <c r="F139" s="10"/>
       <c r="G139" s="10"/>
-      <c r="H139" s="16"/>
+      <c r="H139" s="10"/>
       <c r="I139" s="16"/>
       <c r="J139" s="16"/>
       <c r="K139" s="16"/>
       <c r="L139" s="16"/>
       <c r="M139" s="16"/>
-    </row>
-    <row r="140" spans="1:13">
+      <c r="N139" s="16"/>
+    </row>
+    <row r="140" spans="1:14">
       <c r="A140" s="10"/>
       <c r="B140" s="16"/>
       <c r="C140" s="10"/>
@@ -3689,14 +3846,15 @@
       <c r="E140" s="10"/>
       <c r="F140" s="10"/>
       <c r="G140" s="10"/>
-      <c r="H140" s="16"/>
+      <c r="H140" s="10"/>
       <c r="I140" s="16"/>
       <c r="J140" s="16"/>
       <c r="K140" s="16"/>
       <c r="L140" s="16"/>
       <c r="M140" s="16"/>
-    </row>
-    <row r="141" spans="1:13">
+      <c r="N140" s="16"/>
+    </row>
+    <row r="141" spans="1:14">
       <c r="A141" s="10"/>
       <c r="B141" s="16"/>
       <c r="C141" s="10"/>
@@ -3704,14 +3862,15 @@
       <c r="E141" s="10"/>
       <c r="F141" s="10"/>
       <c r="G141" s="10"/>
-      <c r="H141" s="16"/>
+      <c r="H141" s="10"/>
       <c r="I141" s="16"/>
       <c r="J141" s="16"/>
       <c r="K141" s="16"/>
       <c r="L141" s="16"/>
       <c r="M141" s="16"/>
-    </row>
-    <row r="142" spans="1:13">
+      <c r="N141" s="16"/>
+    </row>
+    <row r="142" spans="1:14">
       <c r="A142" s="10"/>
       <c r="B142" s="16"/>
       <c r="C142" s="10"/>
@@ -3719,14 +3878,15 @@
       <c r="E142" s="10"/>
       <c r="F142" s="10"/>
       <c r="G142" s="10"/>
-      <c r="H142" s="16"/>
+      <c r="H142" s="10"/>
       <c r="I142" s="16"/>
       <c r="J142" s="16"/>
       <c r="K142" s="16"/>
       <c r="L142" s="16"/>
       <c r="M142" s="16"/>
-    </row>
-    <row r="143" spans="1:13">
+      <c r="N142" s="16"/>
+    </row>
+    <row r="143" spans="1:14">
       <c r="A143" s="10"/>
       <c r="B143" s="16"/>
       <c r="C143" s="10"/>
@@ -3734,14 +3894,15 @@
       <c r="E143" s="10"/>
       <c r="F143" s="10"/>
       <c r="G143" s="10"/>
-      <c r="H143" s="16"/>
+      <c r="H143" s="10"/>
       <c r="I143" s="16"/>
       <c r="J143" s="16"/>
       <c r="K143" s="16"/>
       <c r="L143" s="16"/>
       <c r="M143" s="16"/>
-    </row>
-    <row r="144" spans="1:13">
+      <c r="N143" s="16"/>
+    </row>
+    <row r="144" spans="1:14">
       <c r="A144" s="10"/>
       <c r="B144" s="16"/>
       <c r="C144" s="10"/>
@@ -3749,14 +3910,15 @@
       <c r="E144" s="10"/>
       <c r="F144" s="10"/>
       <c r="G144" s="10"/>
-      <c r="H144" s="16"/>
+      <c r="H144" s="10"/>
       <c r="I144" s="16"/>
       <c r="J144" s="16"/>
       <c r="K144" s="16"/>
       <c r="L144" s="16"/>
       <c r="M144" s="16"/>
-    </row>
-    <row r="145" spans="1:13">
+      <c r="N144" s="16"/>
+    </row>
+    <row r="145" spans="1:14">
       <c r="A145" s="10"/>
       <c r="B145" s="16"/>
       <c r="C145" s="10"/>
@@ -3764,14 +3926,15 @@
       <c r="E145" s="10"/>
       <c r="F145" s="10"/>
       <c r="G145" s="10"/>
-      <c r="H145" s="16"/>
+      <c r="H145" s="10"/>
       <c r="I145" s="16"/>
       <c r="J145" s="16"/>
       <c r="K145" s="16"/>
       <c r="L145" s="16"/>
       <c r="M145" s="16"/>
-    </row>
-    <row r="146" spans="1:13">
+      <c r="N145" s="16"/>
+    </row>
+    <row r="146" spans="1:14">
       <c r="A146" s="10"/>
       <c r="B146" s="16"/>
       <c r="C146" s="10"/>
@@ -3779,14 +3942,15 @@
       <c r="E146" s="10"/>
       <c r="F146" s="10"/>
       <c r="G146" s="10"/>
-      <c r="H146" s="16"/>
+      <c r="H146" s="10"/>
       <c r="I146" s="16"/>
       <c r="J146" s="16"/>
       <c r="K146" s="16"/>
       <c r="L146" s="16"/>
       <c r="M146" s="16"/>
-    </row>
-    <row r="147" spans="1:13">
+      <c r="N146" s="16"/>
+    </row>
+    <row r="147" spans="1:14">
       <c r="A147" s="10"/>
       <c r="B147" s="16"/>
       <c r="C147" s="10"/>
@@ -3794,14 +3958,15 @@
       <c r="E147" s="10"/>
       <c r="F147" s="10"/>
       <c r="G147" s="10"/>
-      <c r="H147" s="16"/>
+      <c r="H147" s="10"/>
       <c r="I147" s="16"/>
       <c r="J147" s="16"/>
       <c r="K147" s="16"/>
       <c r="L147" s="16"/>
       <c r="M147" s="16"/>
-    </row>
-    <row r="148" spans="1:13">
+      <c r="N147" s="16"/>
+    </row>
+    <row r="148" spans="1:14">
       <c r="A148" s="10"/>
       <c r="B148" s="16"/>
       <c r="C148" s="10"/>
@@ -3809,14 +3974,15 @@
       <c r="E148" s="10"/>
       <c r="F148" s="10"/>
       <c r="G148" s="10"/>
-      <c r="H148" s="16"/>
+      <c r="H148" s="10"/>
       <c r="I148" s="16"/>
       <c r="J148" s="16"/>
       <c r="K148" s="16"/>
       <c r="L148" s="16"/>
       <c r="M148" s="16"/>
-    </row>
-    <row r="149" spans="1:13">
+      <c r="N148" s="16"/>
+    </row>
+    <row r="149" spans="1:14">
       <c r="A149" s="10"/>
       <c r="B149" s="16"/>
       <c r="C149" s="10"/>
@@ -3824,14 +3990,15 @@
       <c r="E149" s="10"/>
       <c r="F149" s="10"/>
       <c r="G149" s="10"/>
-      <c r="H149" s="16"/>
+      <c r="H149" s="10"/>
       <c r="I149" s="16"/>
       <c r="J149" s="16"/>
       <c r="K149" s="16"/>
       <c r="L149" s="16"/>
       <c r="M149" s="16"/>
-    </row>
-    <row r="150" spans="1:13">
+      <c r="N149" s="16"/>
+    </row>
+    <row r="150" spans="1:14">
       <c r="A150" s="10"/>
       <c r="B150" s="16"/>
       <c r="C150" s="10"/>
@@ -3839,14 +4006,15 @@
       <c r="E150" s="10"/>
       <c r="F150" s="10"/>
       <c r="G150" s="10"/>
-      <c r="H150" s="16"/>
+      <c r="H150" s="10"/>
       <c r="I150" s="16"/>
       <c r="J150" s="16"/>
       <c r="K150" s="16"/>
       <c r="L150" s="16"/>
       <c r="M150" s="16"/>
-    </row>
-    <row r="151" spans="1:13">
+      <c r="N150" s="16"/>
+    </row>
+    <row r="151" spans="1:14">
       <c r="A151" s="10"/>
       <c r="B151" s="16"/>
       <c r="C151" s="10"/>
@@ -3854,14 +4022,15 @@
       <c r="E151" s="10"/>
       <c r="F151" s="10"/>
       <c r="G151" s="10"/>
-      <c r="H151" s="16"/>
+      <c r="H151" s="10"/>
       <c r="I151" s="16"/>
       <c r="J151" s="16"/>
       <c r="K151" s="16"/>
       <c r="L151" s="16"/>
       <c r="M151" s="16"/>
-    </row>
-    <row r="152" spans="1:13">
+      <c r="N151" s="16"/>
+    </row>
+    <row r="152" spans="1:14">
       <c r="A152" s="10"/>
       <c r="B152" s="16"/>
       <c r="C152" s="10"/>
@@ -3869,14 +4038,15 @@
       <c r="E152" s="10"/>
       <c r="F152" s="10"/>
       <c r="G152" s="10"/>
-      <c r="H152" s="16"/>
+      <c r="H152" s="10"/>
       <c r="I152" s="16"/>
       <c r="J152" s="16"/>
       <c r="K152" s="16"/>
       <c r="L152" s="16"/>
       <c r="M152" s="16"/>
-    </row>
-    <row r="153" spans="1:13">
+      <c r="N152" s="16"/>
+    </row>
+    <row r="153" spans="1:14">
       <c r="A153" s="10"/>
       <c r="B153" s="16"/>
       <c r="C153" s="10"/>
@@ -3884,14 +4054,15 @@
       <c r="E153" s="10"/>
       <c r="F153" s="10"/>
       <c r="G153" s="10"/>
-      <c r="H153" s="16"/>
+      <c r="H153" s="10"/>
       <c r="I153" s="16"/>
       <c r="J153" s="16"/>
       <c r="K153" s="16"/>
       <c r="L153" s="16"/>
       <c r="M153" s="16"/>
-    </row>
-    <row r="154" spans="1:13">
+      <c r="N153" s="16"/>
+    </row>
+    <row r="154" spans="1:14">
       <c r="A154" s="10"/>
       <c r="B154" s="16"/>
       <c r="C154" s="10"/>
@@ -3899,14 +4070,15 @@
       <c r="E154" s="10"/>
       <c r="F154" s="10"/>
       <c r="G154" s="10"/>
-      <c r="H154" s="16"/>
+      <c r="H154" s="10"/>
       <c r="I154" s="16"/>
       <c r="J154" s="16"/>
       <c r="K154" s="16"/>
       <c r="L154" s="16"/>
       <c r="M154" s="16"/>
-    </row>
-    <row r="155" spans="1:13">
+      <c r="N154" s="16"/>
+    </row>
+    <row r="155" spans="1:14">
       <c r="A155" s="10"/>
       <c r="B155" s="16"/>
       <c r="C155" s="10"/>
@@ -3914,14 +4086,15 @@
       <c r="E155" s="10"/>
       <c r="F155" s="10"/>
       <c r="G155" s="10"/>
-      <c r="H155" s="16"/>
+      <c r="H155" s="10"/>
       <c r="I155" s="16"/>
       <c r="J155" s="16"/>
       <c r="K155" s="16"/>
       <c r="L155" s="16"/>
       <c r="M155" s="16"/>
-    </row>
-    <row r="156" spans="1:13">
+      <c r="N155" s="16"/>
+    </row>
+    <row r="156" spans="1:14">
       <c r="A156" s="10"/>
       <c r="B156" s="16"/>
       <c r="C156" s="10"/>
@@ -3929,14 +4102,15 @@
       <c r="E156" s="10"/>
       <c r="F156" s="10"/>
       <c r="G156" s="10"/>
-      <c r="H156" s="16"/>
+      <c r="H156" s="10"/>
       <c r="I156" s="16"/>
       <c r="J156" s="16"/>
       <c r="K156" s="16"/>
       <c r="L156" s="16"/>
       <c r="M156" s="16"/>
-    </row>
-    <row r="157" spans="1:13">
+      <c r="N156" s="16"/>
+    </row>
+    <row r="157" spans="1:14">
       <c r="A157" s="10"/>
       <c r="B157" s="16"/>
       <c r="C157" s="10"/>
@@ -3944,14 +4118,15 @@
       <c r="E157" s="10"/>
       <c r="F157" s="10"/>
       <c r="G157" s="10"/>
-      <c r="H157" s="16"/>
+      <c r="H157" s="10"/>
       <c r="I157" s="16"/>
       <c r="J157" s="16"/>
       <c r="K157" s="16"/>
       <c r="L157" s="16"/>
       <c r="M157" s="16"/>
-    </row>
-    <row r="158" spans="1:13">
+      <c r="N157" s="16"/>
+    </row>
+    <row r="158" spans="1:14">
       <c r="A158" s="10"/>
       <c r="B158" s="16"/>
       <c r="C158" s="10"/>
@@ -3959,14 +4134,15 @@
       <c r="E158" s="10"/>
       <c r="F158" s="10"/>
       <c r="G158" s="10"/>
-      <c r="H158" s="16"/>
+      <c r="H158" s="10"/>
       <c r="I158" s="16"/>
       <c r="J158" s="16"/>
       <c r="K158" s="16"/>
       <c r="L158" s="16"/>
       <c r="M158" s="16"/>
-    </row>
-    <row r="159" spans="1:13">
+      <c r="N158" s="16"/>
+    </row>
+    <row r="159" spans="1:14">
       <c r="A159" s="10"/>
       <c r="B159" s="16"/>
       <c r="C159" s="10"/>
@@ -3974,14 +4150,15 @@
       <c r="E159" s="10"/>
       <c r="F159" s="10"/>
       <c r="G159" s="10"/>
-      <c r="H159" s="16"/>
+      <c r="H159" s="10"/>
       <c r="I159" s="16"/>
       <c r="J159" s="16"/>
       <c r="K159" s="16"/>
       <c r="L159" s="16"/>
       <c r="M159" s="16"/>
-    </row>
-    <row r="160" spans="1:13">
+      <c r="N159" s="16"/>
+    </row>
+    <row r="160" spans="1:14">
       <c r="A160" s="10"/>
       <c r="B160" s="16"/>
       <c r="C160" s="10"/>
@@ -3989,14 +4166,15 @@
       <c r="E160" s="10"/>
       <c r="F160" s="10"/>
       <c r="G160" s="10"/>
-      <c r="H160" s="16"/>
+      <c r="H160" s="10"/>
       <c r="I160" s="16"/>
       <c r="J160" s="16"/>
       <c r="K160" s="16"/>
       <c r="L160" s="16"/>
       <c r="M160" s="16"/>
-    </row>
-    <row r="161" spans="1:13">
+      <c r="N160" s="16"/>
+    </row>
+    <row r="161" spans="1:14">
       <c r="A161" s="10"/>
       <c r="B161" s="16"/>
       <c r="C161" s="10"/>
@@ -4004,14 +4182,15 @@
       <c r="E161" s="10"/>
       <c r="F161" s="10"/>
       <c r="G161" s="10"/>
-      <c r="H161" s="16"/>
+      <c r="H161" s="10"/>
       <c r="I161" s="16"/>
       <c r="J161" s="16"/>
       <c r="K161" s="16"/>
       <c r="L161" s="16"/>
       <c r="M161" s="16"/>
-    </row>
-    <row r="162" spans="1:13">
+      <c r="N161" s="16"/>
+    </row>
+    <row r="162" spans="1:14">
       <c r="A162" s="10"/>
       <c r="B162" s="16"/>
       <c r="C162" s="10"/>
@@ -4019,14 +4198,15 @@
       <c r="E162" s="10"/>
       <c r="F162" s="10"/>
       <c r="G162" s="10"/>
-      <c r="H162" s="16"/>
+      <c r="H162" s="10"/>
       <c r="I162" s="16"/>
       <c r="J162" s="16"/>
       <c r="K162" s="16"/>
       <c r="L162" s="16"/>
       <c r="M162" s="16"/>
-    </row>
-    <row r="163" spans="1:13">
+      <c r="N162" s="16"/>
+    </row>
+    <row r="163" spans="1:14">
       <c r="A163" s="10"/>
       <c r="B163" s="16"/>
       <c r="C163" s="10"/>
@@ -4034,14 +4214,15 @@
       <c r="E163" s="10"/>
       <c r="F163" s="10"/>
       <c r="G163" s="10"/>
-      <c r="H163" s="16"/>
+      <c r="H163" s="10"/>
       <c r="I163" s="16"/>
       <c r="J163" s="16"/>
       <c r="K163" s="16"/>
       <c r="L163" s="16"/>
       <c r="M163" s="16"/>
-    </row>
-    <row r="164" spans="1:13">
+      <c r="N163" s="16"/>
+    </row>
+    <row r="164" spans="1:14">
       <c r="A164" s="10"/>
       <c r="B164" s="16"/>
       <c r="C164" s="10"/>
@@ -4049,14 +4230,15 @@
       <c r="E164" s="10"/>
       <c r="F164" s="10"/>
       <c r="G164" s="10"/>
-      <c r="H164" s="16"/>
+      <c r="H164" s="10"/>
       <c r="I164" s="16"/>
       <c r="J164" s="16"/>
       <c r="K164" s="16"/>
       <c r="L164" s="16"/>
       <c r="M164" s="16"/>
-    </row>
-    <row r="165" spans="1:13">
+      <c r="N164" s="16"/>
+    </row>
+    <row r="165" spans="1:14">
       <c r="A165" s="10"/>
       <c r="B165" s="16"/>
       <c r="C165" s="10"/>
@@ -4064,14 +4246,15 @@
       <c r="E165" s="10"/>
       <c r="F165" s="10"/>
       <c r="G165" s="10"/>
-      <c r="H165" s="16"/>
+      <c r="H165" s="10"/>
       <c r="I165" s="16"/>
       <c r="J165" s="16"/>
       <c r="K165" s="16"/>
       <c r="L165" s="16"/>
       <c r="M165" s="16"/>
-    </row>
-    <row r="166" spans="1:13">
+      <c r="N165" s="16"/>
+    </row>
+    <row r="166" spans="1:14">
       <c r="A166" s="10"/>
       <c r="B166" s="16"/>
       <c r="C166" s="10"/>
@@ -4079,14 +4262,15 @@
       <c r="E166" s="10"/>
       <c r="F166" s="10"/>
       <c r="G166" s="10"/>
-      <c r="H166" s="16"/>
+      <c r="H166" s="10"/>
       <c r="I166" s="16"/>
       <c r="J166" s="16"/>
       <c r="K166" s="16"/>
       <c r="L166" s="16"/>
       <c r="M166" s="16"/>
-    </row>
-    <row r="167" spans="1:13">
+      <c r="N166" s="16"/>
+    </row>
+    <row r="167" spans="1:14">
       <c r="A167" s="10"/>
       <c r="B167" s="16"/>
       <c r="C167" s="10"/>
@@ -4094,14 +4278,15 @@
       <c r="E167" s="10"/>
       <c r="F167" s="10"/>
       <c r="G167" s="10"/>
-      <c r="H167" s="16"/>
+      <c r="H167" s="10"/>
       <c r="I167" s="16"/>
       <c r="J167" s="16"/>
       <c r="K167" s="16"/>
       <c r="L167" s="16"/>
       <c r="M167" s="16"/>
-    </row>
-    <row r="168" spans="1:13">
+      <c r="N167" s="16"/>
+    </row>
+    <row r="168" spans="1:14">
       <c r="A168" s="10"/>
       <c r="B168" s="16"/>
       <c r="C168" s="10"/>
@@ -4109,14 +4294,15 @@
       <c r="E168" s="10"/>
       <c r="F168" s="10"/>
       <c r="G168" s="10"/>
-      <c r="H168" s="16"/>
+      <c r="H168" s="10"/>
       <c r="I168" s="16"/>
       <c r="J168" s="16"/>
       <c r="K168" s="16"/>
       <c r="L168" s="16"/>
       <c r="M168" s="16"/>
-    </row>
-    <row r="169" spans="1:13">
+      <c r="N168" s="16"/>
+    </row>
+    <row r="169" spans="1:14">
       <c r="A169" s="10"/>
       <c r="B169" s="16"/>
       <c r="C169" s="10"/>
@@ -4124,14 +4310,15 @@
       <c r="E169" s="10"/>
       <c r="F169" s="10"/>
       <c r="G169" s="10"/>
-      <c r="H169" s="16"/>
+      <c r="H169" s="10"/>
       <c r="I169" s="16"/>
       <c r="J169" s="16"/>
       <c r="K169" s="16"/>
       <c r="L169" s="16"/>
       <c r="M169" s="16"/>
-    </row>
-    <row r="170" spans="1:13">
+      <c r="N169" s="16"/>
+    </row>
+    <row r="170" spans="1:14">
       <c r="A170" s="10"/>
       <c r="B170" s="16"/>
       <c r="C170" s="10"/>
@@ -4139,14 +4326,15 @@
       <c r="E170" s="10"/>
       <c r="F170" s="10"/>
       <c r="G170" s="10"/>
-      <c r="H170" s="16"/>
+      <c r="H170" s="10"/>
       <c r="I170" s="16"/>
       <c r="J170" s="16"/>
       <c r="K170" s="16"/>
       <c r="L170" s="16"/>
       <c r="M170" s="16"/>
-    </row>
-    <row r="171" spans="1:13">
+      <c r="N170" s="16"/>
+    </row>
+    <row r="171" spans="1:14">
       <c r="A171" s="10"/>
       <c r="B171" s="16"/>
       <c r="C171" s="10"/>
@@ -4154,14 +4342,15 @@
       <c r="E171" s="10"/>
       <c r="F171" s="10"/>
       <c r="G171" s="10"/>
-      <c r="H171" s="16"/>
+      <c r="H171" s="10"/>
       <c r="I171" s="16"/>
       <c r="J171" s="16"/>
       <c r="K171" s="16"/>
       <c r="L171" s="16"/>
       <c r="M171" s="16"/>
-    </row>
-    <row r="172" spans="1:13">
+      <c r="N171" s="16"/>
+    </row>
+    <row r="172" spans="1:14">
       <c r="A172" s="10"/>
       <c r="B172" s="16"/>
       <c r="C172" s="10"/>
@@ -4169,14 +4358,15 @@
       <c r="E172" s="10"/>
       <c r="F172" s="10"/>
       <c r="G172" s="10"/>
-      <c r="H172" s="16"/>
+      <c r="H172" s="10"/>
       <c r="I172" s="16"/>
       <c r="J172" s="16"/>
       <c r="K172" s="16"/>
       <c r="L172" s="16"/>
       <c r="M172" s="16"/>
-    </row>
-    <row r="173" spans="1:13">
+      <c r="N172" s="16"/>
+    </row>
+    <row r="173" spans="1:14">
       <c r="A173" s="10"/>
       <c r="B173" s="16"/>
       <c r="C173" s="10"/>
@@ -4184,14 +4374,15 @@
       <c r="E173" s="10"/>
       <c r="F173" s="10"/>
       <c r="G173" s="10"/>
-      <c r="H173" s="16"/>
+      <c r="H173" s="10"/>
       <c r="I173" s="16"/>
       <c r="J173" s="16"/>
       <c r="K173" s="16"/>
       <c r="L173" s="16"/>
       <c r="M173" s="16"/>
-    </row>
-    <row r="174" spans="1:13">
+      <c r="N173" s="16"/>
+    </row>
+    <row r="174" spans="1:14">
       <c r="A174" s="10"/>
       <c r="B174" s="16"/>
       <c r="C174" s="10"/>
@@ -4199,14 +4390,15 @@
       <c r="E174" s="10"/>
       <c r="F174" s="10"/>
       <c r="G174" s="10"/>
-      <c r="H174" s="16"/>
+      <c r="H174" s="10"/>
       <c r="I174" s="16"/>
       <c r="J174" s="16"/>
       <c r="K174" s="16"/>
       <c r="L174" s="16"/>
       <c r="M174" s="16"/>
-    </row>
-    <row r="175" spans="1:13">
+      <c r="N174" s="16"/>
+    </row>
+    <row r="175" spans="1:14">
       <c r="A175" s="10"/>
       <c r="B175" s="16"/>
       <c r="C175" s="10"/>
@@ -4214,14 +4406,15 @@
       <c r="E175" s="10"/>
       <c r="F175" s="10"/>
       <c r="G175" s="10"/>
-      <c r="H175" s="16"/>
+      <c r="H175" s="10"/>
       <c r="I175" s="16"/>
       <c r="J175" s="16"/>
       <c r="K175" s="16"/>
       <c r="L175" s="16"/>
       <c r="M175" s="16"/>
-    </row>
-    <row r="176" spans="1:13">
+      <c r="N175" s="16"/>
+    </row>
+    <row r="176" spans="1:14">
       <c r="A176" s="10"/>
       <c r="B176" s="16"/>
       <c r="C176" s="10"/>
@@ -4229,14 +4422,15 @@
       <c r="E176" s="10"/>
       <c r="F176" s="10"/>
       <c r="G176" s="10"/>
-      <c r="H176" s="16"/>
+      <c r="H176" s="10"/>
       <c r="I176" s="16"/>
       <c r="J176" s="16"/>
       <c r="K176" s="16"/>
       <c r="L176" s="16"/>
       <c r="M176" s="16"/>
-    </row>
-    <row r="177" spans="1:13">
+      <c r="N176" s="16"/>
+    </row>
+    <row r="177" spans="1:14">
       <c r="A177" s="10"/>
       <c r="B177" s="16"/>
       <c r="C177" s="10"/>
@@ -4244,14 +4438,15 @@
       <c r="E177" s="10"/>
       <c r="F177" s="10"/>
       <c r="G177" s="10"/>
-      <c r="H177" s="16"/>
+      <c r="H177" s="10"/>
       <c r="I177" s="16"/>
       <c r="J177" s="16"/>
       <c r="K177" s="16"/>
       <c r="L177" s="16"/>
       <c r="M177" s="16"/>
-    </row>
-    <row r="178" spans="1:13">
+      <c r="N177" s="16"/>
+    </row>
+    <row r="178" spans="1:14">
       <c r="A178" s="10"/>
       <c r="B178" s="16"/>
       <c r="C178" s="10"/>
@@ -4259,14 +4454,15 @@
       <c r="E178" s="10"/>
       <c r="F178" s="10"/>
       <c r="G178" s="10"/>
-      <c r="H178" s="16"/>
+      <c r="H178" s="10"/>
       <c r="I178" s="16"/>
       <c r="J178" s="16"/>
       <c r="K178" s="16"/>
       <c r="L178" s="16"/>
       <c r="M178" s="16"/>
-    </row>
-    <row r="179" spans="1:13">
+      <c r="N178" s="16"/>
+    </row>
+    <row r="179" spans="1:14">
       <c r="A179" s="10"/>
       <c r="B179" s="16"/>
       <c r="C179" s="10"/>
@@ -4274,14 +4470,15 @@
       <c r="E179" s="10"/>
       <c r="F179" s="10"/>
       <c r="G179" s="10"/>
-      <c r="H179" s="16"/>
+      <c r="H179" s="10"/>
       <c r="I179" s="16"/>
       <c r="J179" s="16"/>
       <c r="K179" s="16"/>
       <c r="L179" s="16"/>
       <c r="M179" s="16"/>
-    </row>
-    <row r="180" spans="1:13">
+      <c r="N179" s="16"/>
+    </row>
+    <row r="180" spans="1:14">
       <c r="A180" s="10"/>
       <c r="B180" s="16"/>
       <c r="C180" s="10"/>
@@ -4289,14 +4486,15 @@
       <c r="E180" s="10"/>
       <c r="F180" s="10"/>
       <c r="G180" s="10"/>
-      <c r="H180" s="16"/>
+      <c r="H180" s="10"/>
       <c r="I180" s="16"/>
       <c r="J180" s="16"/>
       <c r="K180" s="16"/>
       <c r="L180" s="16"/>
       <c r="M180" s="16"/>
-    </row>
-    <row r="181" spans="1:13">
+      <c r="N180" s="16"/>
+    </row>
+    <row r="181" spans="1:14">
       <c r="A181" s="10"/>
       <c r="B181" s="16"/>
       <c r="C181" s="10"/>
@@ -4304,14 +4502,15 @@
       <c r="E181" s="10"/>
       <c r="F181" s="10"/>
       <c r="G181" s="10"/>
-      <c r="H181" s="16"/>
+      <c r="H181" s="10"/>
       <c r="I181" s="16"/>
       <c r="J181" s="16"/>
       <c r="K181" s="16"/>
       <c r="L181" s="16"/>
       <c r="M181" s="16"/>
-    </row>
-    <row r="182" spans="1:13">
+      <c r="N181" s="16"/>
+    </row>
+    <row r="182" spans="1:14">
       <c r="A182" s="10"/>
       <c r="B182" s="16"/>
       <c r="C182" s="10"/>
@@ -4319,14 +4518,15 @@
       <c r="E182" s="10"/>
       <c r="F182" s="10"/>
       <c r="G182" s="10"/>
-      <c r="H182" s="16"/>
+      <c r="H182" s="10"/>
       <c r="I182" s="16"/>
       <c r="J182" s="16"/>
       <c r="K182" s="16"/>
       <c r="L182" s="16"/>
       <c r="M182" s="16"/>
-    </row>
-    <row r="183" spans="1:13">
+      <c r="N182" s="16"/>
+    </row>
+    <row r="183" spans="1:14">
       <c r="A183" s="10"/>
       <c r="B183" s="16"/>
       <c r="C183" s="10"/>
@@ -4334,14 +4534,15 @@
       <c r="E183" s="10"/>
       <c r="F183" s="10"/>
       <c r="G183" s="10"/>
-      <c r="H183" s="16"/>
+      <c r="H183" s="10"/>
       <c r="I183" s="16"/>
       <c r="J183" s="16"/>
       <c r="K183" s="16"/>
       <c r="L183" s="16"/>
       <c r="M183" s="16"/>
-    </row>
-    <row r="184" spans="1:13">
+      <c r="N183" s="16"/>
+    </row>
+    <row r="184" spans="1:14">
       <c r="A184" s="10"/>
       <c r="B184" s="16"/>
       <c r="C184" s="10"/>
@@ -4349,14 +4550,15 @@
       <c r="E184" s="10"/>
       <c r="F184" s="10"/>
       <c r="G184" s="10"/>
-      <c r="H184" s="16"/>
+      <c r="H184" s="10"/>
       <c r="I184" s="16"/>
       <c r="J184" s="16"/>
       <c r="K184" s="16"/>
       <c r="L184" s="16"/>
       <c r="M184" s="16"/>
-    </row>
-    <row r="185" spans="1:13">
+      <c r="N184" s="16"/>
+    </row>
+    <row r="185" spans="1:14">
       <c r="A185" s="10"/>
       <c r="B185" s="16"/>
       <c r="C185" s="10"/>
@@ -4364,14 +4566,15 @@
       <c r="E185" s="10"/>
       <c r="F185" s="10"/>
       <c r="G185" s="10"/>
-      <c r="H185" s="16"/>
+      <c r="H185" s="10"/>
       <c r="I185" s="16"/>
       <c r="J185" s="16"/>
       <c r="K185" s="16"/>
       <c r="L185" s="16"/>
       <c r="M185" s="16"/>
-    </row>
-    <row r="186" spans="1:13">
+      <c r="N185" s="16"/>
+    </row>
+    <row r="186" spans="1:14">
       <c r="A186" s="10"/>
       <c r="B186" s="16"/>
       <c r="C186" s="10"/>
@@ -4379,14 +4582,15 @@
       <c r="E186" s="10"/>
       <c r="F186" s="10"/>
       <c r="G186" s="10"/>
-      <c r="H186" s="16"/>
+      <c r="H186" s="10"/>
       <c r="I186" s="16"/>
       <c r="J186" s="16"/>
       <c r="K186" s="16"/>
       <c r="L186" s="16"/>
       <c r="M186" s="16"/>
-    </row>
-    <row r="187" spans="1:13">
+      <c r="N186" s="16"/>
+    </row>
+    <row r="187" spans="1:14">
       <c r="A187" s="10"/>
       <c r="B187" s="16"/>
       <c r="C187" s="10"/>
@@ -4394,14 +4598,15 @@
       <c r="E187" s="10"/>
       <c r="F187" s="10"/>
       <c r="G187" s="10"/>
-      <c r="H187" s="16"/>
+      <c r="H187" s="10"/>
       <c r="I187" s="16"/>
       <c r="J187" s="16"/>
       <c r="K187" s="16"/>
       <c r="L187" s="16"/>
       <c r="M187" s="16"/>
-    </row>
-    <row r="188" spans="1:13">
+      <c r="N187" s="16"/>
+    </row>
+    <row r="188" spans="1:14">
       <c r="A188" s="10"/>
       <c r="B188" s="16"/>
       <c r="C188" s="10"/>
@@ -4409,14 +4614,15 @@
       <c r="E188" s="10"/>
       <c r="F188" s="10"/>
       <c r="G188" s="10"/>
-      <c r="H188" s="16"/>
+      <c r="H188" s="10"/>
       <c r="I188" s="16"/>
       <c r="J188" s="16"/>
       <c r="K188" s="16"/>
       <c r="L188" s="16"/>
       <c r="M188" s="16"/>
-    </row>
-    <row r="189" spans="1:13">
+      <c r="N188" s="16"/>
+    </row>
+    <row r="189" spans="1:14">
       <c r="A189" s="10"/>
       <c r="B189" s="16"/>
       <c r="C189" s="10"/>
@@ -4424,14 +4630,15 @@
       <c r="E189" s="10"/>
       <c r="F189" s="10"/>
       <c r="G189" s="10"/>
-      <c r="H189" s="16"/>
+      <c r="H189" s="10"/>
       <c r="I189" s="16"/>
       <c r="J189" s="16"/>
       <c r="K189" s="16"/>
       <c r="L189" s="16"/>
       <c r="M189" s="16"/>
-    </row>
-    <row r="190" spans="1:13">
+      <c r="N189" s="16"/>
+    </row>
+    <row r="190" spans="1:14">
       <c r="A190" s="10"/>
       <c r="B190" s="16"/>
       <c r="C190" s="10"/>
@@ -4439,14 +4646,15 @@
       <c r="E190" s="10"/>
       <c r="F190" s="10"/>
       <c r="G190" s="10"/>
-      <c r="H190" s="16"/>
+      <c r="H190" s="10"/>
       <c r="I190" s="16"/>
       <c r="J190" s="16"/>
       <c r="K190" s="16"/>
       <c r="L190" s="16"/>
       <c r="M190" s="16"/>
-    </row>
-    <row r="191" spans="1:13">
+      <c r="N190" s="16"/>
+    </row>
+    <row r="191" spans="1:14">
       <c r="A191" s="10"/>
       <c r="B191" s="16"/>
       <c r="C191" s="10"/>
@@ -4454,14 +4662,15 @@
       <c r="E191" s="10"/>
       <c r="F191" s="10"/>
       <c r="G191" s="10"/>
-      <c r="H191" s="16"/>
+      <c r="H191" s="10"/>
       <c r="I191" s="16"/>
       <c r="J191" s="16"/>
       <c r="K191" s="16"/>
       <c r="L191" s="16"/>
       <c r="M191" s="16"/>
-    </row>
-    <row r="192" spans="1:13">
+      <c r="N191" s="16"/>
+    </row>
+    <row r="192" spans="1:14">
       <c r="A192" s="10"/>
       <c r="B192" s="16"/>
       <c r="C192" s="10"/>
@@ -4469,14 +4678,15 @@
       <c r="E192" s="10"/>
       <c r="F192" s="10"/>
       <c r="G192" s="10"/>
-      <c r="H192" s="16"/>
+      <c r="H192" s="10"/>
       <c r="I192" s="16"/>
       <c r="J192" s="16"/>
       <c r="K192" s="16"/>
       <c r="L192" s="16"/>
       <c r="M192" s="16"/>
-    </row>
-    <row r="193" spans="1:13">
+      <c r="N192" s="16"/>
+    </row>
+    <row r="193" spans="1:14">
       <c r="A193" s="10"/>
       <c r="B193" s="16"/>
       <c r="C193" s="10"/>
@@ -4484,14 +4694,15 @@
       <c r="E193" s="10"/>
       <c r="F193" s="10"/>
       <c r="G193" s="10"/>
-      <c r="H193" s="16"/>
+      <c r="H193" s="10"/>
       <c r="I193" s="16"/>
       <c r="J193" s="16"/>
       <c r="K193" s="16"/>
       <c r="L193" s="16"/>
       <c r="M193" s="16"/>
-    </row>
-    <row r="194" spans="1:13">
+      <c r="N193" s="16"/>
+    </row>
+    <row r="194" spans="1:14">
       <c r="A194" s="10"/>
       <c r="B194" s="16"/>
       <c r="C194" s="10"/>
@@ -4499,14 +4710,15 @@
       <c r="E194" s="10"/>
       <c r="F194" s="10"/>
       <c r="G194" s="10"/>
-      <c r="H194" s="16"/>
+      <c r="H194" s="10"/>
       <c r="I194" s="16"/>
       <c r="J194" s="16"/>
       <c r="K194" s="16"/>
       <c r="L194" s="16"/>
       <c r="M194" s="16"/>
-    </row>
-    <row r="195" spans="1:13">
+      <c r="N194" s="16"/>
+    </row>
+    <row r="195" spans="1:14">
       <c r="A195" s="10"/>
       <c r="B195" s="16"/>
       <c r="C195" s="10"/>
@@ -4514,14 +4726,15 @@
       <c r="E195" s="10"/>
       <c r="F195" s="10"/>
       <c r="G195" s="10"/>
-      <c r="H195" s="16"/>
+      <c r="H195" s="10"/>
       <c r="I195" s="16"/>
       <c r="J195" s="16"/>
       <c r="K195" s="16"/>
       <c r="L195" s="16"/>
       <c r="M195" s="16"/>
-    </row>
-    <row r="196" spans="1:13">
+      <c r="N195" s="16"/>
+    </row>
+    <row r="196" spans="1:14">
       <c r="A196" s="10"/>
       <c r="B196" s="16"/>
       <c r="C196" s="10"/>
@@ -4529,14 +4742,15 @@
       <c r="E196" s="10"/>
       <c r="F196" s="10"/>
       <c r="G196" s="10"/>
-      <c r="H196" s="16"/>
+      <c r="H196" s="10"/>
       <c r="I196" s="16"/>
       <c r="J196" s="16"/>
       <c r="K196" s="16"/>
       <c r="L196" s="16"/>
       <c r="M196" s="16"/>
-    </row>
-    <row r="197" spans="1:13">
+      <c r="N196" s="16"/>
+    </row>
+    <row r="197" spans="1:14">
       <c r="A197" s="10"/>
       <c r="B197" s="16"/>
       <c r="C197" s="10"/>
@@ -4544,14 +4758,15 @@
       <c r="E197" s="10"/>
       <c r="F197" s="10"/>
       <c r="G197" s="10"/>
-      <c r="H197" s="16"/>
+      <c r="H197" s="10"/>
       <c r="I197" s="16"/>
       <c r="J197" s="16"/>
       <c r="K197" s="16"/>
       <c r="L197" s="16"/>
       <c r="M197" s="16"/>
-    </row>
-    <row r="198" spans="1:13">
+      <c r="N197" s="16"/>
+    </row>
+    <row r="198" spans="1:14">
       <c r="A198" s="10"/>
       <c r="B198" s="16"/>
       <c r="C198" s="10"/>
@@ -4559,14 +4774,15 @@
       <c r="E198" s="10"/>
       <c r="F198" s="10"/>
       <c r="G198" s="10"/>
-      <c r="H198" s="16"/>
+      <c r="H198" s="10"/>
       <c r="I198" s="16"/>
       <c r="J198" s="16"/>
       <c r="K198" s="16"/>
       <c r="L198" s="16"/>
       <c r="M198" s="16"/>
-    </row>
-    <row r="199" spans="1:13">
+      <c r="N198" s="16"/>
+    </row>
+    <row r="199" spans="1:14">
       <c r="A199" s="10"/>
       <c r="B199" s="16"/>
       <c r="C199" s="10"/>
@@ -4574,14 +4790,15 @@
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
       <c r="G199" s="10"/>
-      <c r="H199" s="16"/>
+      <c r="H199" s="10"/>
       <c r="I199" s="16"/>
       <c r="J199" s="16"/>
       <c r="K199" s="16"/>
       <c r="L199" s="16"/>
       <c r="M199" s="16"/>
-    </row>
-    <row r="200" spans="1:13">
+      <c r="N199" s="16"/>
+    </row>
+    <row r="200" spans="1:14">
       <c r="A200" s="10"/>
       <c r="B200" s="16"/>
       <c r="C200" s="10"/>
@@ -4589,14 +4806,15 @@
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
       <c r="G200" s="10"/>
-      <c r="H200" s="16"/>
+      <c r="H200" s="10"/>
       <c r="I200" s="16"/>
       <c r="J200" s="16"/>
       <c r="K200" s="16"/>
       <c r="L200" s="16"/>
       <c r="M200" s="16"/>
-    </row>
-    <row r="201" spans="1:13">
+      <c r="N200" s="16"/>
+    </row>
+    <row r="201" spans="1:14">
       <c r="A201" s="10"/>
       <c r="B201" s="16"/>
       <c r="C201" s="10"/>
@@ -4604,14 +4822,15 @@
       <c r="E201" s="10"/>
       <c r="F201" s="10"/>
       <c r="G201" s="10"/>
-      <c r="H201" s="16"/>
+      <c r="H201" s="10"/>
       <c r="I201" s="16"/>
       <c r="J201" s="16"/>
       <c r="K201" s="16"/>
       <c r="L201" s="16"/>
       <c r="M201" s="16"/>
-    </row>
-    <row r="202" spans="1:13">
+      <c r="N201" s="16"/>
+    </row>
+    <row r="202" spans="1:14">
       <c r="A202" s="10"/>
       <c r="B202" s="16"/>
       <c r="C202" s="10"/>
@@ -4619,14 +4838,15 @@
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
       <c r="G202" s="10"/>
-      <c r="H202" s="16"/>
+      <c r="H202" s="10"/>
       <c r="I202" s="16"/>
       <c r="J202" s="16"/>
       <c r="K202" s="16"/>
       <c r="L202" s="16"/>
       <c r="M202" s="16"/>
-    </row>
-    <row r="203" spans="1:13">
+      <c r="N202" s="16"/>
+    </row>
+    <row r="203" spans="1:14">
       <c r="A203" s="10"/>
       <c r="B203" s="16"/>
       <c r="C203" s="10"/>
@@ -4634,14 +4854,15 @@
       <c r="E203" s="10"/>
       <c r="F203" s="10"/>
       <c r="G203" s="10"/>
-      <c r="H203" s="16"/>
+      <c r="H203" s="10"/>
       <c r="I203" s="16"/>
       <c r="J203" s="16"/>
       <c r="K203" s="16"/>
       <c r="L203" s="16"/>
       <c r="M203" s="16"/>
-    </row>
-    <row r="204" spans="1:13">
+      <c r="N203" s="16"/>
+    </row>
+    <row r="204" spans="1:14">
       <c r="A204" s="10"/>
       <c r="B204" s="16"/>
       <c r="C204" s="10"/>
@@ -4649,14 +4870,15 @@
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
       <c r="G204" s="10"/>
-      <c r="H204" s="16"/>
+      <c r="H204" s="10"/>
       <c r="I204" s="16"/>
       <c r="J204" s="16"/>
       <c r="K204" s="16"/>
       <c r="L204" s="16"/>
       <c r="M204" s="16"/>
-    </row>
-    <row r="205" spans="1:13">
+      <c r="N204" s="16"/>
+    </row>
+    <row r="205" spans="1:14">
       <c r="A205" s="10"/>
       <c r="B205" s="16"/>
       <c r="C205" s="10"/>
@@ -4664,14 +4886,15 @@
       <c r="E205" s="10"/>
       <c r="F205" s="10"/>
       <c r="G205" s="10"/>
-      <c r="H205" s="16"/>
+      <c r="H205" s="10"/>
       <c r="I205" s="16"/>
       <c r="J205" s="16"/>
       <c r="K205" s="16"/>
       <c r="L205" s="16"/>
       <c r="M205" s="16"/>
-    </row>
-    <row r="206" spans="1:13">
+      <c r="N205" s="16"/>
+    </row>
+    <row r="206" spans="1:14">
       <c r="A206" s="10"/>
       <c r="B206" s="16"/>
       <c r="C206" s="10"/>
@@ -4679,14 +4902,15 @@
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
       <c r="G206" s="10"/>
-      <c r="H206" s="16"/>
+      <c r="H206" s="10"/>
       <c r="I206" s="16"/>
       <c r="J206" s="16"/>
       <c r="K206" s="16"/>
       <c r="L206" s="16"/>
       <c r="M206" s="16"/>
-    </row>
-    <row r="207" spans="1:13">
+      <c r="N206" s="16"/>
+    </row>
+    <row r="207" spans="1:14">
       <c r="A207" s="10"/>
       <c r="B207" s="16"/>
       <c r="C207" s="10"/>
@@ -4694,14 +4918,15 @@
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
       <c r="G207" s="10"/>
-      <c r="H207" s="16"/>
+      <c r="H207" s="10"/>
       <c r="I207" s="16"/>
       <c r="J207" s="16"/>
       <c r="K207" s="16"/>
       <c r="L207" s="16"/>
       <c r="M207" s="16"/>
-    </row>
-    <row r="208" spans="1:13">
+      <c r="N207" s="16"/>
+    </row>
+    <row r="208" spans="1:14">
       <c r="A208" s="10"/>
       <c r="B208" s="16"/>
       <c r="C208" s="10"/>
@@ -4709,14 +4934,15 @@
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
       <c r="G208" s="10"/>
-      <c r="H208" s="16"/>
+      <c r="H208" s="10"/>
       <c r="I208" s="16"/>
       <c r="J208" s="16"/>
       <c r="K208" s="16"/>
       <c r="L208" s="16"/>
       <c r="M208" s="16"/>
-    </row>
-    <row r="209" spans="1:13">
+      <c r="N208" s="16"/>
+    </row>
+    <row r="209" spans="1:14">
       <c r="A209" s="10"/>
       <c r="B209" s="16"/>
       <c r="C209" s="10"/>
@@ -4724,14 +4950,15 @@
       <c r="E209" s="10"/>
       <c r="F209" s="10"/>
       <c r="G209" s="10"/>
-      <c r="H209" s="16"/>
+      <c r="H209" s="10"/>
       <c r="I209" s="16"/>
       <c r="J209" s="16"/>
       <c r="K209" s="16"/>
       <c r="L209" s="16"/>
       <c r="M209" s="16"/>
-    </row>
-    <row r="210" spans="1:13">
+      <c r="N209" s="16"/>
+    </row>
+    <row r="210" spans="1:14">
       <c r="A210" s="10"/>
       <c r="B210" s="16"/>
       <c r="C210" s="10"/>
@@ -4739,14 +4966,15 @@
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
       <c r="G210" s="10"/>
-      <c r="H210" s="16"/>
+      <c r="H210" s="10"/>
       <c r="I210" s="16"/>
       <c r="J210" s="16"/>
       <c r="K210" s="16"/>
       <c r="L210" s="16"/>
       <c r="M210" s="16"/>
-    </row>
-    <row r="211" spans="1:13">
+      <c r="N210" s="16"/>
+    </row>
+    <row r="211" spans="1:14">
       <c r="A211" s="10"/>
       <c r="B211" s="16"/>
       <c r="C211" s="10"/>
@@ -4754,14 +4982,15 @@
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
       <c r="G211" s="10"/>
-      <c r="H211" s="16"/>
+      <c r="H211" s="10"/>
       <c r="I211" s="16"/>
       <c r="J211" s="16"/>
       <c r="K211" s="16"/>
       <c r="L211" s="16"/>
       <c r="M211" s="16"/>
-    </row>
-    <row r="212" spans="1:13">
+      <c r="N211" s="16"/>
+    </row>
+    <row r="212" spans="1:14">
       <c r="A212" s="10"/>
       <c r="B212" s="16"/>
       <c r="C212" s="10"/>
@@ -4769,14 +4998,15 @@
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
       <c r="G212" s="10"/>
-      <c r="H212" s="16"/>
+      <c r="H212" s="10"/>
       <c r="I212" s="16"/>
       <c r="J212" s="16"/>
       <c r="K212" s="16"/>
       <c r="L212" s="16"/>
       <c r="M212" s="16"/>
-    </row>
-    <row r="213" spans="1:13">
+      <c r="N212" s="16"/>
+    </row>
+    <row r="213" spans="1:14">
       <c r="A213" s="10"/>
       <c r="B213" s="16"/>
       <c r="C213" s="10"/>
@@ -4784,14 +5014,15 @@
       <c r="E213" s="10"/>
       <c r="F213" s="10"/>
       <c r="G213" s="10"/>
-      <c r="H213" s="16"/>
+      <c r="H213" s="10"/>
       <c r="I213" s="16"/>
       <c r="J213" s="16"/>
       <c r="K213" s="16"/>
       <c r="L213" s="16"/>
       <c r="M213" s="16"/>
-    </row>
-    <row r="214" spans="1:13">
+      <c r="N213" s="16"/>
+    </row>
+    <row r="214" spans="1:14">
       <c r="A214" s="10"/>
       <c r="B214" s="16"/>
       <c r="C214" s="10"/>
@@ -4799,14 +5030,15 @@
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
       <c r="G214" s="10"/>
-      <c r="H214" s="16"/>
+      <c r="H214" s="10"/>
       <c r="I214" s="16"/>
       <c r="J214" s="16"/>
       <c r="K214" s="16"/>
       <c r="L214" s="16"/>
       <c r="M214" s="16"/>
-    </row>
-    <row r="215" spans="1:13">
+      <c r="N214" s="16"/>
+    </row>
+    <row r="215" spans="1:14">
       <c r="A215" s="10"/>
       <c r="B215" s="16"/>
       <c r="C215" s="10"/>
@@ -4814,14 +5046,15 @@
       <c r="E215" s="10"/>
       <c r="F215" s="10"/>
       <c r="G215" s="10"/>
-      <c r="H215" s="16"/>
+      <c r="H215" s="10"/>
       <c r="I215" s="16"/>
       <c r="J215" s="16"/>
       <c r="K215" s="16"/>
       <c r="L215" s="16"/>
       <c r="M215" s="16"/>
-    </row>
-    <row r="216" spans="1:13">
+      <c r="N215" s="16"/>
+    </row>
+    <row r="216" spans="1:14">
       <c r="A216" s="10"/>
       <c r="B216" s="16"/>
       <c r="C216" s="10"/>
@@ -4829,14 +5062,15 @@
       <c r="E216" s="10"/>
       <c r="F216" s="10"/>
       <c r="G216" s="10"/>
-      <c r="H216" s="16"/>
+      <c r="H216" s="10"/>
       <c r="I216" s="16"/>
       <c r="J216" s="16"/>
       <c r="K216" s="16"/>
       <c r="L216" s="16"/>
       <c r="M216" s="16"/>
-    </row>
-    <row r="217" spans="1:13">
+      <c r="N216" s="16"/>
+    </row>
+    <row r="217" spans="1:14">
       <c r="A217" s="10"/>
       <c r="B217" s="16"/>
       <c r="C217" s="10"/>
@@ -4844,14 +5078,15 @@
       <c r="E217" s="10"/>
       <c r="F217" s="10"/>
       <c r="G217" s="10"/>
-      <c r="H217" s="16"/>
+      <c r="H217" s="10"/>
       <c r="I217" s="16"/>
       <c r="J217" s="16"/>
       <c r="K217" s="16"/>
       <c r="L217" s="16"/>
       <c r="M217" s="16"/>
-    </row>
-    <row r="218" spans="1:13">
+      <c r="N217" s="16"/>
+    </row>
+    <row r="218" spans="1:14">
       <c r="A218" s="10"/>
       <c r="B218" s="16"/>
       <c r="C218" s="10"/>
@@ -4859,14 +5094,15 @@
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
       <c r="G218" s="10"/>
-      <c r="H218" s="16"/>
+      <c r="H218" s="10"/>
       <c r="I218" s="16"/>
       <c r="J218" s="16"/>
       <c r="K218" s="16"/>
       <c r="L218" s="16"/>
       <c r="M218" s="16"/>
-    </row>
-    <row r="219" spans="1:13">
+      <c r="N218" s="16"/>
+    </row>
+    <row r="219" spans="1:14">
       <c r="A219" s="10"/>
       <c r="B219" s="16"/>
       <c r="C219" s="10"/>
@@ -4874,14 +5110,15 @@
       <c r="E219" s="10"/>
       <c r="F219" s="10"/>
       <c r="G219" s="10"/>
-      <c r="H219" s="16"/>
+      <c r="H219" s="10"/>
       <c r="I219" s="16"/>
       <c r="J219" s="16"/>
       <c r="K219" s="16"/>
       <c r="L219" s="16"/>
       <c r="M219" s="16"/>
-    </row>
-    <row r="220" spans="1:13">
+      <c r="N219" s="16"/>
+    </row>
+    <row r="220" spans="1:14">
       <c r="A220" s="10"/>
       <c r="B220" s="16"/>
       <c r="C220" s="10"/>
@@ -4889,14 +5126,15 @@
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
       <c r="G220" s="10"/>
-      <c r="H220" s="16"/>
+      <c r="H220" s="10"/>
       <c r="I220" s="16"/>
       <c r="J220" s="16"/>
       <c r="K220" s="16"/>
       <c r="L220" s="16"/>
       <c r="M220" s="16"/>
-    </row>
-    <row r="221" spans="1:13">
+      <c r="N220" s="16"/>
+    </row>
+    <row r="221" spans="1:14">
       <c r="A221" s="10"/>
       <c r="B221" s="16"/>
       <c r="C221" s="10"/>
@@ -4904,14 +5142,15 @@
       <c r="E221" s="10"/>
       <c r="F221" s="10"/>
       <c r="G221" s="10"/>
-      <c r="H221" s="16"/>
+      <c r="H221" s="10"/>
       <c r="I221" s="16"/>
       <c r="J221" s="16"/>
       <c r="K221" s="16"/>
       <c r="L221" s="16"/>
       <c r="M221" s="16"/>
-    </row>
-    <row r="222" spans="1:13">
+      <c r="N221" s="16"/>
+    </row>
+    <row r="222" spans="1:14">
       <c r="A222" s="10"/>
       <c r="B222" s="16"/>
       <c r="C222" s="10"/>
@@ -4919,14 +5158,15 @@
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
       <c r="G222" s="10"/>
-      <c r="H222" s="16"/>
+      <c r="H222" s="10"/>
       <c r="I222" s="16"/>
       <c r="J222" s="16"/>
       <c r="K222" s="16"/>
       <c r="L222" s="16"/>
       <c r="M222" s="16"/>
-    </row>
-    <row r="223" spans="1:13">
+      <c r="N222" s="16"/>
+    </row>
+    <row r="223" spans="1:14">
       <c r="A223" s="10"/>
       <c r="B223" s="16"/>
       <c r="C223" s="10"/>
@@ -4934,14 +5174,15 @@
       <c r="E223" s="10"/>
       <c r="F223" s="10"/>
       <c r="G223" s="10"/>
-      <c r="H223" s="16"/>
+      <c r="H223" s="10"/>
       <c r="I223" s="16"/>
       <c r="J223" s="16"/>
       <c r="K223" s="16"/>
       <c r="L223" s="16"/>
       <c r="M223" s="16"/>
-    </row>
-    <row r="224" spans="1:13">
+      <c r="N223" s="16"/>
+    </row>
+    <row r="224" spans="1:14">
       <c r="A224" s="10"/>
       <c r="B224" s="16"/>
       <c r="C224" s="10"/>
@@ -4949,14 +5190,15 @@
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
       <c r="G224" s="10"/>
-      <c r="H224" s="16"/>
+      <c r="H224" s="10"/>
       <c r="I224" s="16"/>
       <c r="J224" s="16"/>
       <c r="K224" s="16"/>
       <c r="L224" s="16"/>
       <c r="M224" s="16"/>
-    </row>
-    <row r="225" spans="1:13">
+      <c r="N224" s="16"/>
+    </row>
+    <row r="225" spans="1:14">
       <c r="A225" s="10"/>
       <c r="B225" s="16"/>
       <c r="C225" s="10"/>
@@ -4964,14 +5206,15 @@
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
       <c r="G225" s="10"/>
-      <c r="H225" s="16"/>
+      <c r="H225" s="10"/>
       <c r="I225" s="16"/>
       <c r="J225" s="16"/>
       <c r="K225" s="16"/>
       <c r="L225" s="16"/>
       <c r="M225" s="16"/>
-    </row>
-    <row r="226" spans="1:13">
+      <c r="N225" s="16"/>
+    </row>
+    <row r="226" spans="1:14">
       <c r="A226" s="10"/>
       <c r="B226" s="16"/>
       <c r="C226" s="10"/>
@@ -4979,14 +5222,15 @@
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
       <c r="G226" s="10"/>
-      <c r="H226" s="16"/>
+      <c r="H226" s="10"/>
       <c r="I226" s="16"/>
       <c r="J226" s="16"/>
       <c r="K226" s="16"/>
       <c r="L226" s="16"/>
       <c r="M226" s="16"/>
-    </row>
-    <row r="227" spans="1:13">
+      <c r="N226" s="16"/>
+    </row>
+    <row r="227" spans="1:14">
       <c r="A227" s="10"/>
       <c r="B227" s="16"/>
       <c r="C227" s="10"/>
@@ -4994,14 +5238,15 @@
       <c r="E227" s="10"/>
       <c r="F227" s="10"/>
       <c r="G227" s="10"/>
-      <c r="H227" s="16"/>
+      <c r="H227" s="10"/>
       <c r="I227" s="16"/>
       <c r="J227" s="16"/>
       <c r="K227" s="16"/>
       <c r="L227" s="16"/>
       <c r="M227" s="16"/>
-    </row>
-    <row r="228" spans="1:13">
+      <c r="N227" s="16"/>
+    </row>
+    <row r="228" spans="1:14">
       <c r="A228" s="10"/>
       <c r="B228" s="16"/>
       <c r="C228" s="10"/>
@@ -5009,14 +5254,15 @@
       <c r="E228" s="10"/>
       <c r="F228" s="10"/>
       <c r="G228" s="10"/>
-      <c r="H228" s="16"/>
+      <c r="H228" s="10"/>
       <c r="I228" s="16"/>
       <c r="J228" s="16"/>
       <c r="K228" s="16"/>
       <c r="L228" s="16"/>
       <c r="M228" s="16"/>
-    </row>
-    <row r="229" spans="1:13">
+      <c r="N228" s="16"/>
+    </row>
+    <row r="229" spans="1:14">
       <c r="A229" s="10"/>
       <c r="B229" s="16"/>
       <c r="C229" s="10"/>
@@ -5024,14 +5270,15 @@
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
       <c r="G229" s="10"/>
-      <c r="H229" s="16"/>
+      <c r="H229" s="10"/>
       <c r="I229" s="16"/>
       <c r="J229" s="16"/>
       <c r="K229" s="16"/>
       <c r="L229" s="16"/>
       <c r="M229" s="16"/>
-    </row>
-    <row r="230" spans="1:13">
+      <c r="N229" s="16"/>
+    </row>
+    <row r="230" spans="1:14">
       <c r="A230" s="10"/>
       <c r="B230" s="16"/>
       <c r="C230" s="10"/>
@@ -5039,14 +5286,15 @@
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
       <c r="G230" s="10"/>
-      <c r="H230" s="16"/>
+      <c r="H230" s="10"/>
       <c r="I230" s="16"/>
       <c r="J230" s="16"/>
       <c r="K230" s="16"/>
       <c r="L230" s="16"/>
       <c r="M230" s="16"/>
-    </row>
-    <row r="231" spans="1:13">
+      <c r="N230" s="16"/>
+    </row>
+    <row r="231" spans="1:14">
       <c r="A231" s="10"/>
       <c r="B231" s="16"/>
       <c r="C231" s="10"/>
@@ -5054,14 +5302,15 @@
       <c r="E231" s="10"/>
       <c r="F231" s="10"/>
       <c r="G231" s="10"/>
-      <c r="H231" s="16"/>
+      <c r="H231" s="10"/>
       <c r="I231" s="16"/>
       <c r="J231" s="16"/>
       <c r="K231" s="16"/>
       <c r="L231" s="16"/>
       <c r="M231" s="16"/>
-    </row>
-    <row r="232" spans="1:13">
+      <c r="N231" s="16"/>
+    </row>
+    <row r="232" spans="1:14">
       <c r="A232" s="10"/>
       <c r="B232" s="16"/>
       <c r="C232" s="10"/>
@@ -5069,14 +5318,15 @@
       <c r="E232" s="10"/>
       <c r="F232" s="10"/>
       <c r="G232" s="10"/>
-      <c r="H232" s="16"/>
+      <c r="H232" s="10"/>
       <c r="I232" s="16"/>
       <c r="J232" s="16"/>
       <c r="K232" s="16"/>
       <c r="L232" s="16"/>
       <c r="M232" s="16"/>
-    </row>
-    <row r="233" spans="1:13">
+      <c r="N232" s="16"/>
+    </row>
+    <row r="233" spans="1:14">
       <c r="A233" s="10"/>
       <c r="B233" s="16"/>
       <c r="C233" s="10"/>
@@ -5084,14 +5334,15 @@
       <c r="E233" s="10"/>
       <c r="F233" s="10"/>
       <c r="G233" s="10"/>
-      <c r="H233" s="16"/>
+      <c r="H233" s="10"/>
       <c r="I233" s="16"/>
       <c r="J233" s="16"/>
       <c r="K233" s="16"/>
       <c r="L233" s="16"/>
       <c r="M233" s="16"/>
-    </row>
-    <row r="234" spans="1:13">
+      <c r="N233" s="16"/>
+    </row>
+    <row r="234" spans="1:14">
       <c r="A234" s="10"/>
       <c r="B234" s="16"/>
       <c r="C234" s="10"/>
@@ -5099,14 +5350,15 @@
       <c r="E234" s="10"/>
       <c r="F234" s="10"/>
       <c r="G234" s="10"/>
-      <c r="H234" s="16"/>
+      <c r="H234" s="10"/>
       <c r="I234" s="16"/>
       <c r="J234" s="16"/>
       <c r="K234" s="16"/>
       <c r="L234" s="16"/>
       <c r="M234" s="16"/>
-    </row>
-    <row r="235" spans="1:13">
+      <c r="N234" s="16"/>
+    </row>
+    <row r="235" spans="1:14">
       <c r="A235" s="10"/>
       <c r="B235" s="16"/>
       <c r="C235" s="10"/>
@@ -5114,14 +5366,15 @@
       <c r="E235" s="10"/>
       <c r="F235" s="10"/>
       <c r="G235" s="10"/>
-      <c r="H235" s="16"/>
+      <c r="H235" s="10"/>
       <c r="I235" s="16"/>
       <c r="J235" s="16"/>
       <c r="K235" s="16"/>
       <c r="L235" s="16"/>
       <c r="M235" s="16"/>
-    </row>
-    <row r="236" spans="1:13">
+      <c r="N235" s="16"/>
+    </row>
+    <row r="236" spans="1:14">
       <c r="A236" s="10"/>
       <c r="B236" s="16"/>
       <c r="C236" s="10"/>
@@ -5129,14 +5382,15 @@
       <c r="E236" s="10"/>
       <c r="F236" s="10"/>
       <c r="G236" s="10"/>
-      <c r="H236" s="16"/>
+      <c r="H236" s="10"/>
       <c r="I236" s="16"/>
       <c r="J236" s="16"/>
       <c r="K236" s="16"/>
       <c r="L236" s="16"/>
       <c r="M236" s="16"/>
-    </row>
-    <row r="237" spans="1:13">
+      <c r="N236" s="16"/>
+    </row>
+    <row r="237" spans="1:14">
       <c r="A237" s="10"/>
       <c r="B237" s="16"/>
       <c r="C237" s="10"/>
@@ -5144,14 +5398,15 @@
       <c r="E237" s="10"/>
       <c r="F237" s="10"/>
       <c r="G237" s="10"/>
-      <c r="H237" s="16"/>
+      <c r="H237" s="10"/>
       <c r="I237" s="16"/>
       <c r="J237" s="16"/>
       <c r="K237" s="16"/>
       <c r="L237" s="16"/>
       <c r="M237" s="16"/>
-    </row>
-    <row r="238" spans="1:13">
+      <c r="N237" s="16"/>
+    </row>
+    <row r="238" spans="1:14">
       <c r="A238" s="10"/>
       <c r="B238" s="16"/>
       <c r="C238" s="10"/>
@@ -5159,14 +5414,15 @@
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
       <c r="G238" s="10"/>
-      <c r="H238" s="16"/>
+      <c r="H238" s="10"/>
       <c r="I238" s="16"/>
       <c r="J238" s="16"/>
       <c r="K238" s="16"/>
       <c r="L238" s="16"/>
       <c r="M238" s="16"/>
-    </row>
-    <row r="239" spans="1:13">
+      <c r="N238" s="16"/>
+    </row>
+    <row r="239" spans="1:14">
       <c r="A239" s="10"/>
       <c r="B239" s="16"/>
       <c r="C239" s="10"/>
@@ -5174,14 +5430,15 @@
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
       <c r="G239" s="10"/>
-      <c r="H239" s="16"/>
+      <c r="H239" s="10"/>
       <c r="I239" s="16"/>
       <c r="J239" s="16"/>
       <c r="K239" s="16"/>
       <c r="L239" s="16"/>
       <c r="M239" s="16"/>
-    </row>
-    <row r="240" spans="1:13">
+      <c r="N239" s="16"/>
+    </row>
+    <row r="240" spans="1:14">
       <c r="A240" s="10"/>
       <c r="B240" s="16"/>
       <c r="C240" s="10"/>
@@ -5189,14 +5446,15 @@
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
       <c r="G240" s="10"/>
-      <c r="H240" s="16"/>
+      <c r="H240" s="10"/>
       <c r="I240" s="16"/>
       <c r="J240" s="16"/>
       <c r="K240" s="16"/>
       <c r="L240" s="16"/>
       <c r="M240" s="16"/>
-    </row>
-    <row r="241" spans="1:13">
+      <c r="N240" s="16"/>
+    </row>
+    <row r="241" spans="1:14">
       <c r="A241" s="10"/>
       <c r="B241" s="16"/>
       <c r="C241" s="10"/>
@@ -5204,14 +5462,15 @@
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
       <c r="G241" s="10"/>
-      <c r="H241" s="16"/>
+      <c r="H241" s="10"/>
       <c r="I241" s="16"/>
       <c r="J241" s="16"/>
       <c r="K241" s="16"/>
       <c r="L241" s="16"/>
       <c r="M241" s="16"/>
-    </row>
-    <row r="242" spans="1:13">
+      <c r="N241" s="16"/>
+    </row>
+    <row r="242" spans="1:14">
       <c r="A242" s="10"/>
       <c r="B242" s="16"/>
       <c r="C242" s="10"/>
@@ -5219,14 +5478,15 @@
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
       <c r="G242" s="10"/>
-      <c r="H242" s="16"/>
+      <c r="H242" s="10"/>
       <c r="I242" s="16"/>
       <c r="J242" s="16"/>
       <c r="K242" s="16"/>
       <c r="L242" s="16"/>
       <c r="M242" s="16"/>
-    </row>
-    <row r="243" spans="1:13">
+      <c r="N242" s="16"/>
+    </row>
+    <row r="243" spans="1:14">
       <c r="A243" s="10"/>
       <c r="B243" s="16"/>
       <c r="C243" s="10"/>
@@ -5234,14 +5494,15 @@
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
       <c r="G243" s="10"/>
-      <c r="H243" s="16"/>
+      <c r="H243" s="10"/>
       <c r="I243" s="16"/>
       <c r="J243" s="16"/>
       <c r="K243" s="16"/>
       <c r="L243" s="16"/>
       <c r="M243" s="16"/>
-    </row>
-    <row r="244" spans="1:13">
+      <c r="N243" s="16"/>
+    </row>
+    <row r="244" spans="1:14">
       <c r="A244" s="10"/>
       <c r="B244" s="16"/>
       <c r="C244" s="10"/>
@@ -5249,14 +5510,15 @@
       <c r="E244" s="10"/>
       <c r="F244" s="10"/>
       <c r="G244" s="10"/>
-      <c r="H244" s="16"/>
+      <c r="H244" s="10"/>
       <c r="I244" s="16"/>
       <c r="J244" s="16"/>
       <c r="K244" s="16"/>
       <c r="L244" s="16"/>
       <c r="M244" s="16"/>
-    </row>
-    <row r="245" spans="1:13">
+      <c r="N244" s="16"/>
+    </row>
+    <row r="245" spans="1:14">
       <c r="A245" s="10"/>
       <c r="B245" s="16"/>
       <c r="C245" s="10"/>
@@ -5264,14 +5526,15 @@
       <c r="E245" s="10"/>
       <c r="F245" s="10"/>
       <c r="G245" s="10"/>
-      <c r="H245" s="16"/>
+      <c r="H245" s="10"/>
       <c r="I245" s="16"/>
       <c r="J245" s="16"/>
       <c r="K245" s="16"/>
       <c r="L245" s="16"/>
       <c r="M245" s="16"/>
-    </row>
-    <row r="246" spans="1:13">
+      <c r="N245" s="16"/>
+    </row>
+    <row r="246" spans="1:14">
       <c r="A246" s="10"/>
       <c r="B246" s="16"/>
       <c r="C246" s="10"/>
@@ -5279,14 +5542,15 @@
       <c r="E246" s="10"/>
       <c r="F246" s="10"/>
       <c r="G246" s="10"/>
-      <c r="H246" s="16"/>
+      <c r="H246" s="10"/>
       <c r="I246" s="16"/>
       <c r="J246" s="16"/>
       <c r="K246" s="16"/>
       <c r="L246" s="16"/>
       <c r="M246" s="16"/>
-    </row>
-    <row r="247" spans="1:13">
+      <c r="N246" s="16"/>
+    </row>
+    <row r="247" spans="1:14">
       <c r="A247" s="10"/>
       <c r="B247" s="16"/>
       <c r="C247" s="10"/>
@@ -5294,14 +5558,15 @@
       <c r="E247" s="10"/>
       <c r="F247" s="10"/>
       <c r="G247" s="10"/>
-      <c r="H247" s="16"/>
+      <c r="H247" s="10"/>
       <c r="I247" s="16"/>
       <c r="J247" s="16"/>
       <c r="K247" s="16"/>
       <c r="L247" s="16"/>
       <c r="M247" s="16"/>
-    </row>
-    <row r="248" spans="1:13">
+      <c r="N247" s="16"/>
+    </row>
+    <row r="248" spans="1:14">
       <c r="A248" s="10"/>
       <c r="B248" s="16"/>
       <c r="C248" s="10"/>
@@ -5309,14 +5574,15 @@
       <c r="E248" s="10"/>
       <c r="F248" s="10"/>
       <c r="G248" s="10"/>
-      <c r="H248" s="16"/>
+      <c r="H248" s="10"/>
       <c r="I248" s="16"/>
       <c r="J248" s="16"/>
       <c r="K248" s="16"/>
       <c r="L248" s="16"/>
       <c r="M248" s="16"/>
-    </row>
-    <row r="249" spans="1:13">
+      <c r="N248" s="16"/>
+    </row>
+    <row r="249" spans="1:14">
       <c r="A249" s="10"/>
       <c r="B249" s="16"/>
       <c r="C249" s="10"/>
@@ -5324,14 +5590,15 @@
       <c r="E249" s="10"/>
       <c r="F249" s="10"/>
       <c r="G249" s="10"/>
-      <c r="H249" s="16"/>
+      <c r="H249" s="10"/>
       <c r="I249" s="16"/>
       <c r="J249" s="16"/>
       <c r="K249" s="16"/>
       <c r="L249" s="16"/>
       <c r="M249" s="16"/>
-    </row>
-    <row r="250" spans="1:13">
+      <c r="N249" s="16"/>
+    </row>
+    <row r="250" spans="1:14">
       <c r="A250" s="10"/>
       <c r="B250" s="16"/>
       <c r="C250" s="10"/>
@@ -5339,14 +5606,15 @@
       <c r="E250" s="10"/>
       <c r="F250" s="10"/>
       <c r="G250" s="10"/>
-      <c r="H250" s="16"/>
+      <c r="H250" s="10"/>
       <c r="I250" s="16"/>
       <c r="J250" s="16"/>
       <c r="K250" s="16"/>
       <c r="L250" s="16"/>
       <c r="M250" s="16"/>
-    </row>
-    <row r="251" spans="1:13">
+      <c r="N250" s="16"/>
+    </row>
+    <row r="251" spans="1:14">
       <c r="A251" s="10"/>
       <c r="B251" s="16"/>
       <c r="C251" s="10"/>
@@ -5354,14 +5622,15 @@
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
       <c r="G251" s="10"/>
-      <c r="H251" s="16"/>
+      <c r="H251" s="10"/>
       <c r="I251" s="16"/>
       <c r="J251" s="16"/>
       <c r="K251" s="16"/>
       <c r="L251" s="16"/>
       <c r="M251" s="16"/>
-    </row>
-    <row r="252" spans="1:13">
+      <c r="N251" s="16"/>
+    </row>
+    <row r="252" spans="1:14">
       <c r="A252" s="10"/>
       <c r="B252" s="16"/>
       <c r="C252" s="10"/>
@@ -5369,14 +5638,15 @@
       <c r="E252" s="10"/>
       <c r="F252" s="10"/>
       <c r="G252" s="10"/>
-      <c r="H252" s="16"/>
+      <c r="H252" s="10"/>
       <c r="I252" s="16"/>
       <c r="J252" s="16"/>
       <c r="K252" s="16"/>
       <c r="L252" s="16"/>
       <c r="M252" s="16"/>
-    </row>
-    <row r="253" spans="1:13">
+      <c r="N252" s="16"/>
+    </row>
+    <row r="253" spans="1:14">
       <c r="A253" s="10"/>
       <c r="B253" s="16"/>
       <c r="C253" s="10"/>
@@ -5384,14 +5654,15 @@
       <c r="E253" s="10"/>
       <c r="F253" s="10"/>
       <c r="G253" s="10"/>
-      <c r="H253" s="16"/>
+      <c r="H253" s="10"/>
       <c r="I253" s="16"/>
       <c r="J253" s="16"/>
       <c r="K253" s="16"/>
       <c r="L253" s="16"/>
       <c r="M253" s="16"/>
-    </row>
-    <row r="254" spans="1:13">
+      <c r="N253" s="16"/>
+    </row>
+    <row r="254" spans="1:14">
       <c r="A254" s="10"/>
       <c r="B254" s="16"/>
       <c r="C254" s="10"/>
@@ -5399,14 +5670,15 @@
       <c r="E254" s="10"/>
       <c r="F254" s="10"/>
       <c r="G254" s="10"/>
-      <c r="H254" s="16"/>
+      <c r="H254" s="10"/>
       <c r="I254" s="16"/>
       <c r="J254" s="16"/>
       <c r="K254" s="16"/>
       <c r="L254" s="16"/>
       <c r="M254" s="16"/>
-    </row>
-    <row r="255" spans="1:13">
+      <c r="N254" s="16"/>
+    </row>
+    <row r="255" spans="1:14">
       <c r="A255" s="10"/>
       <c r="B255" s="16"/>
       <c r="C255" s="10"/>
@@ -5414,14 +5686,15 @@
       <c r="E255" s="10"/>
       <c r="F255" s="10"/>
       <c r="G255" s="10"/>
-      <c r="H255" s="16"/>
+      <c r="H255" s="10"/>
       <c r="I255" s="16"/>
       <c r="J255" s="16"/>
       <c r="K255" s="16"/>
       <c r="L255" s="16"/>
       <c r="M255" s="16"/>
-    </row>
-    <row r="256" spans="1:13">
+      <c r="N255" s="16"/>
+    </row>
+    <row r="256" spans="1:14">
       <c r="A256" s="10"/>
       <c r="B256" s="16"/>
       <c r="C256" s="10"/>
@@ -5429,14 +5702,15 @@
       <c r="E256" s="10"/>
       <c r="F256" s="10"/>
       <c r="G256" s="10"/>
-      <c r="H256" s="16"/>
+      <c r="H256" s="10"/>
       <c r="I256" s="16"/>
       <c r="J256" s="16"/>
       <c r="K256" s="16"/>
       <c r="L256" s="16"/>
       <c r="M256" s="16"/>
-    </row>
-    <row r="257" spans="1:13">
+      <c r="N256" s="16"/>
+    </row>
+    <row r="257" spans="1:14">
       <c r="A257" s="10"/>
       <c r="B257" s="16"/>
       <c r="C257" s="10"/>
@@ -5444,14 +5718,15 @@
       <c r="E257" s="10"/>
       <c r="F257" s="10"/>
       <c r="G257" s="10"/>
-      <c r="H257" s="16"/>
+      <c r="H257" s="10"/>
       <c r="I257" s="16"/>
       <c r="J257" s="16"/>
       <c r="K257" s="16"/>
       <c r="L257" s="16"/>
       <c r="M257" s="16"/>
-    </row>
-    <row r="258" spans="1:13">
+      <c r="N257" s="16"/>
+    </row>
+    <row r="258" spans="1:14">
       <c r="A258" s="10"/>
       <c r="B258" s="16"/>
       <c r="C258" s="10"/>
@@ -5459,14 +5734,15 @@
       <c r="E258" s="10"/>
       <c r="F258" s="10"/>
       <c r="G258" s="10"/>
-      <c r="H258" s="16"/>
+      <c r="H258" s="10"/>
       <c r="I258" s="16"/>
       <c r="J258" s="16"/>
       <c r="K258" s="16"/>
       <c r="L258" s="16"/>
       <c r="M258" s="16"/>
-    </row>
-    <row r="259" spans="1:13">
+      <c r="N258" s="16"/>
+    </row>
+    <row r="259" spans="1:14">
       <c r="A259" s="10"/>
       <c r="B259" s="16"/>
       <c r="C259" s="10"/>
@@ -5474,14 +5750,15 @@
       <c r="E259" s="10"/>
       <c r="F259" s="10"/>
       <c r="G259" s="10"/>
-      <c r="H259" s="16"/>
+      <c r="H259" s="10"/>
       <c r="I259" s="16"/>
       <c r="J259" s="16"/>
       <c r="K259" s="16"/>
       <c r="L259" s="16"/>
       <c r="M259" s="16"/>
-    </row>
-    <row r="260" spans="1:13">
+      <c r="N259" s="16"/>
+    </row>
+    <row r="260" spans="1:14">
       <c r="A260" s="10"/>
       <c r="B260" s="16"/>
       <c r="C260" s="10"/>
@@ -5489,14 +5766,15 @@
       <c r="E260" s="10"/>
       <c r="F260" s="10"/>
       <c r="G260" s="10"/>
-      <c r="H260" s="16"/>
+      <c r="H260" s="10"/>
       <c r="I260" s="16"/>
       <c r="J260" s="16"/>
       <c r="K260" s="16"/>
       <c r="L260" s="16"/>
       <c r="M260" s="16"/>
-    </row>
-    <row r="261" spans="1:13">
+      <c r="N260" s="16"/>
+    </row>
+    <row r="261" spans="1:14">
       <c r="A261" s="10"/>
       <c r="B261" s="16"/>
       <c r="C261" s="10"/>
@@ -5504,14 +5782,15 @@
       <c r="E261" s="10"/>
       <c r="F261" s="10"/>
       <c r="G261" s="10"/>
-      <c r="H261" s="16"/>
+      <c r="H261" s="10"/>
       <c r="I261" s="16"/>
       <c r="J261" s="16"/>
       <c r="K261" s="16"/>
       <c r="L261" s="16"/>
       <c r="M261" s="16"/>
-    </row>
-    <row r="262" spans="1:13">
+      <c r="N261" s="16"/>
+    </row>
+    <row r="262" spans="1:14">
       <c r="A262" s="10"/>
       <c r="B262" s="16"/>
       <c r="C262" s="10"/>
@@ -5519,14 +5798,15 @@
       <c r="E262" s="10"/>
       <c r="F262" s="10"/>
       <c r="G262" s="10"/>
-      <c r="H262" s="16"/>
+      <c r="H262" s="10"/>
       <c r="I262" s="16"/>
       <c r="J262" s="16"/>
       <c r="K262" s="16"/>
       <c r="L262" s="16"/>
       <c r="M262" s="16"/>
-    </row>
-    <row r="263" spans="1:13">
+      <c r="N262" s="16"/>
+    </row>
+    <row r="263" spans="1:14">
       <c r="A263" s="10"/>
       <c r="B263" s="16"/>
       <c r="C263" s="10"/>
@@ -5534,14 +5814,15 @@
       <c r="E263" s="10"/>
       <c r="F263" s="10"/>
       <c r="G263" s="10"/>
-      <c r="H263" s="16"/>
+      <c r="H263" s="10"/>
       <c r="I263" s="16"/>
       <c r="J263" s="16"/>
       <c r="K263" s="16"/>
       <c r="L263" s="16"/>
       <c r="M263" s="16"/>
-    </row>
-    <row r="264" spans="1:13">
+      <c r="N263" s="16"/>
+    </row>
+    <row r="264" spans="1:14">
       <c r="A264" s="10"/>
       <c r="B264" s="16"/>
       <c r="C264" s="10"/>
@@ -5549,14 +5830,15 @@
       <c r="E264" s="10"/>
       <c r="F264" s="10"/>
       <c r="G264" s="10"/>
-      <c r="H264" s="16"/>
+      <c r="H264" s="10"/>
       <c r="I264" s="16"/>
       <c r="J264" s="16"/>
       <c r="K264" s="16"/>
       <c r="L264" s="16"/>
       <c r="M264" s="16"/>
-    </row>
-    <row r="265" spans="1:13">
+      <c r="N264" s="16"/>
+    </row>
+    <row r="265" spans="1:14">
       <c r="A265" s="10"/>
       <c r="B265" s="16"/>
       <c r="C265" s="10"/>
@@ -5564,14 +5846,15 @@
       <c r="E265" s="10"/>
       <c r="F265" s="10"/>
       <c r="G265" s="10"/>
-      <c r="H265" s="16"/>
+      <c r="H265" s="10"/>
       <c r="I265" s="16"/>
       <c r="J265" s="16"/>
       <c r="K265" s="16"/>
       <c r="L265" s="16"/>
       <c r="M265" s="16"/>
-    </row>
-    <row r="266" spans="1:13">
+      <c r="N265" s="16"/>
+    </row>
+    <row r="266" spans="1:14">
       <c r="A266" s="10"/>
       <c r="B266" s="16"/>
       <c r="C266" s="10"/>
@@ -5579,14 +5862,15 @@
       <c r="E266" s="10"/>
       <c r="F266" s="10"/>
       <c r="G266" s="10"/>
-      <c r="H266" s="16"/>
+      <c r="H266" s="10"/>
       <c r="I266" s="16"/>
       <c r="J266" s="16"/>
       <c r="K266" s="16"/>
       <c r="L266" s="16"/>
       <c r="M266" s="16"/>
-    </row>
-    <row r="267" spans="1:13">
+      <c r="N266" s="16"/>
+    </row>
+    <row r="267" spans="1:14">
       <c r="A267" s="10"/>
       <c r="B267" s="16"/>
       <c r="C267" s="10"/>
@@ -5594,14 +5878,15 @@
       <c r="E267" s="10"/>
       <c r="F267" s="10"/>
       <c r="G267" s="10"/>
-      <c r="H267" s="16"/>
+      <c r="H267" s="10"/>
       <c r="I267" s="16"/>
       <c r="J267" s="16"/>
       <c r="K267" s="16"/>
       <c r="L267" s="16"/>
       <c r="M267" s="16"/>
-    </row>
-    <row r="268" spans="1:13">
+      <c r="N267" s="16"/>
+    </row>
+    <row r="268" spans="1:14">
       <c r="A268" s="10"/>
       <c r="B268" s="16"/>
       <c r="C268" s="10"/>
@@ -5609,14 +5894,15 @@
       <c r="E268" s="10"/>
       <c r="F268" s="10"/>
       <c r="G268" s="10"/>
-      <c r="H268" s="16"/>
+      <c r="H268" s="10"/>
       <c r="I268" s="16"/>
       <c r="J268" s="16"/>
       <c r="K268" s="16"/>
       <c r="L268" s="16"/>
       <c r="M268" s="16"/>
-    </row>
-    <row r="269" spans="1:13">
+      <c r="N268" s="16"/>
+    </row>
+    <row r="269" spans="1:14">
       <c r="A269" s="10"/>
       <c r="B269" s="16"/>
       <c r="C269" s="10"/>
@@ -5624,14 +5910,15 @@
       <c r="E269" s="10"/>
       <c r="F269" s="10"/>
       <c r="G269" s="10"/>
-      <c r="H269" s="16"/>
+      <c r="H269" s="10"/>
       <c r="I269" s="16"/>
       <c r="J269" s="16"/>
       <c r="K269" s="16"/>
       <c r="L269" s="16"/>
       <c r="M269" s="16"/>
-    </row>
-    <row r="270" spans="1:13">
+      <c r="N269" s="16"/>
+    </row>
+    <row r="270" spans="1:14">
       <c r="A270" s="10"/>
       <c r="B270" s="16"/>
       <c r="C270" s="10"/>
@@ -5639,14 +5926,15 @@
       <c r="E270" s="10"/>
       <c r="F270" s="10"/>
       <c r="G270" s="10"/>
-      <c r="H270" s="16"/>
+      <c r="H270" s="10"/>
       <c r="I270" s="16"/>
       <c r="J270" s="16"/>
       <c r="K270" s="16"/>
       <c r="L270" s="16"/>
       <c r="M270" s="16"/>
-    </row>
-    <row r="271" spans="1:13">
+      <c r="N270" s="16"/>
+    </row>
+    <row r="271" spans="1:14">
       <c r="A271" s="10"/>
       <c r="B271" s="16"/>
       <c r="C271" s="10"/>
@@ -5654,14 +5942,15 @@
       <c r="E271" s="10"/>
       <c r="F271" s="10"/>
       <c r="G271" s="10"/>
-      <c r="H271" s="16"/>
+      <c r="H271" s="10"/>
       <c r="I271" s="16"/>
       <c r="J271" s="16"/>
       <c r="K271" s="16"/>
       <c r="L271" s="16"/>
       <c r="M271" s="16"/>
-    </row>
-    <row r="272" spans="1:13">
+      <c r="N271" s="16"/>
+    </row>
+    <row r="272" spans="1:14">
       <c r="A272" s="10"/>
       <c r="B272" s="16"/>
       <c r="C272" s="10"/>
@@ -5669,14 +5958,15 @@
       <c r="E272" s="10"/>
       <c r="F272" s="10"/>
       <c r="G272" s="10"/>
-      <c r="H272" s="16"/>
+      <c r="H272" s="10"/>
       <c r="I272" s="16"/>
       <c r="J272" s="16"/>
       <c r="K272" s="16"/>
       <c r="L272" s="16"/>
       <c r="M272" s="16"/>
-    </row>
-    <row r="273" spans="1:13">
+      <c r="N272" s="16"/>
+    </row>
+    <row r="273" spans="1:14">
       <c r="A273" s="10"/>
       <c r="B273" s="16"/>
       <c r="C273" s="10"/>
@@ -5684,14 +5974,15 @@
       <c r="E273" s="10"/>
       <c r="F273" s="10"/>
       <c r="G273" s="10"/>
-      <c r="H273" s="16"/>
+      <c r="H273" s="10"/>
       <c r="I273" s="16"/>
       <c r="J273" s="16"/>
       <c r="K273" s="16"/>
       <c r="L273" s="16"/>
       <c r="M273" s="16"/>
-    </row>
-    <row r="274" spans="1:13">
+      <c r="N273" s="16"/>
+    </row>
+    <row r="274" spans="1:14">
       <c r="A274" s="10"/>
       <c r="B274" s="16"/>
       <c r="C274" s="10"/>
@@ -5699,14 +5990,15 @@
       <c r="E274" s="10"/>
       <c r="F274" s="10"/>
       <c r="G274" s="10"/>
-      <c r="H274" s="16"/>
+      <c r="H274" s="10"/>
       <c r="I274" s="16"/>
       <c r="J274" s="16"/>
       <c r="K274" s="16"/>
       <c r="L274" s="16"/>
       <c r="M274" s="16"/>
-    </row>
-    <row r="275" spans="1:13">
+      <c r="N274" s="16"/>
+    </row>
+    <row r="275" spans="1:14">
       <c r="A275" s="10"/>
       <c r="B275" s="16"/>
       <c r="C275" s="10"/>
@@ -5714,14 +6006,15 @@
       <c r="E275" s="10"/>
       <c r="F275" s="10"/>
       <c r="G275" s="10"/>
-      <c r="H275" s="16"/>
+      <c r="H275" s="10"/>
       <c r="I275" s="16"/>
       <c r="J275" s="16"/>
       <c r="K275" s="16"/>
       <c r="L275" s="16"/>
       <c r="M275" s="16"/>
-    </row>
-    <row r="276" spans="1:13">
+      <c r="N275" s="16"/>
+    </row>
+    <row r="276" spans="1:14">
       <c r="A276" s="10"/>
       <c r="B276" s="16"/>
       <c r="C276" s="10"/>
@@ -5729,14 +6022,15 @@
       <c r="E276" s="10"/>
       <c r="F276" s="10"/>
       <c r="G276" s="10"/>
-      <c r="H276" s="16"/>
+      <c r="H276" s="10"/>
       <c r="I276" s="16"/>
       <c r="J276" s="16"/>
       <c r="K276" s="16"/>
       <c r="L276" s="16"/>
       <c r="M276" s="16"/>
-    </row>
-    <row r="277" spans="1:13">
+      <c r="N276" s="16"/>
+    </row>
+    <row r="277" spans="1:14">
       <c r="A277" s="10"/>
       <c r="B277" s="16"/>
       <c r="C277" s="10"/>
@@ -5744,14 +6038,15 @@
       <c r="E277" s="10"/>
       <c r="F277" s="10"/>
       <c r="G277" s="10"/>
-      <c r="H277" s="16"/>
+      <c r="H277" s="10"/>
       <c r="I277" s="16"/>
       <c r="J277" s="16"/>
       <c r="K277" s="16"/>
       <c r="L277" s="16"/>
       <c r="M277" s="16"/>
-    </row>
-    <row r="278" spans="1:13">
+      <c r="N277" s="16"/>
+    </row>
+    <row r="278" spans="1:14">
       <c r="A278" s="10"/>
       <c r="B278" s="16"/>
       <c r="C278" s="10"/>
@@ -5759,14 +6054,15 @@
       <c r="E278" s="10"/>
       <c r="F278" s="10"/>
       <c r="G278" s="10"/>
-      <c r="H278" s="16"/>
+      <c r="H278" s="10"/>
       <c r="I278" s="16"/>
       <c r="J278" s="16"/>
       <c r="K278" s="16"/>
       <c r="L278" s="16"/>
       <c r="M278" s="16"/>
-    </row>
-    <row r="279" spans="1:13">
+      <c r="N278" s="16"/>
+    </row>
+    <row r="279" spans="1:14">
       <c r="A279" s="10"/>
       <c r="B279" s="16"/>
       <c r="C279" s="10"/>
@@ -5774,14 +6070,15 @@
       <c r="E279" s="10"/>
       <c r="F279" s="10"/>
       <c r="G279" s="10"/>
-      <c r="H279" s="16"/>
+      <c r="H279" s="10"/>
       <c r="I279" s="16"/>
       <c r="J279" s="16"/>
       <c r="K279" s="16"/>
       <c r="L279" s="16"/>
       <c r="M279" s="16"/>
-    </row>
-    <row r="280" spans="1:13">
+      <c r="N279" s="16"/>
+    </row>
+    <row r="280" spans="1:14">
       <c r="A280" s="10"/>
       <c r="B280" s="16"/>
       <c r="C280" s="10"/>
@@ -5789,14 +6086,15 @@
       <c r="E280" s="10"/>
       <c r="F280" s="10"/>
       <c r="G280" s="10"/>
-      <c r="H280" s="16"/>
+      <c r="H280" s="10"/>
       <c r="I280" s="16"/>
       <c r="J280" s="16"/>
       <c r="K280" s="16"/>
       <c r="L280" s="16"/>
       <c r="M280" s="16"/>
-    </row>
-    <row r="281" spans="1:13">
+      <c r="N280" s="16"/>
+    </row>
+    <row r="281" spans="1:14">
       <c r="A281" s="10"/>
       <c r="B281" s="16"/>
       <c r="C281" s="10"/>
@@ -5804,14 +6102,15 @@
       <c r="E281" s="10"/>
       <c r="F281" s="10"/>
       <c r="G281" s="10"/>
-      <c r="H281" s="16"/>
+      <c r="H281" s="10"/>
       <c r="I281" s="16"/>
       <c r="J281" s="16"/>
       <c r="K281" s="16"/>
       <c r="L281" s="16"/>
       <c r="M281" s="16"/>
-    </row>
-    <row r="282" spans="1:13">
+      <c r="N281" s="16"/>
+    </row>
+    <row r="282" spans="1:14">
       <c r="A282" s="10"/>
       <c r="B282" s="16"/>
       <c r="C282" s="10"/>
@@ -5819,14 +6118,15 @@
       <c r="E282" s="10"/>
       <c r="F282" s="10"/>
       <c r="G282" s="10"/>
-      <c r="H282" s="16"/>
+      <c r="H282" s="10"/>
       <c r="I282" s="16"/>
       <c r="J282" s="16"/>
       <c r="K282" s="16"/>
       <c r="L282" s="16"/>
       <c r="M282" s="16"/>
-    </row>
-    <row r="283" spans="1:13">
+      <c r="N282" s="16"/>
+    </row>
+    <row r="283" spans="1:14">
       <c r="A283" s="10"/>
       <c r="B283" s="16"/>
       <c r="C283" s="10"/>
@@ -5834,14 +6134,15 @@
       <c r="E283" s="10"/>
       <c r="F283" s="10"/>
       <c r="G283" s="10"/>
-      <c r="H283" s="16"/>
+      <c r="H283" s="10"/>
       <c r="I283" s="16"/>
       <c r="J283" s="16"/>
       <c r="K283" s="16"/>
       <c r="L283" s="16"/>
       <c r="M283" s="16"/>
-    </row>
-    <row r="284" spans="1:13">
+      <c r="N283" s="16"/>
+    </row>
+    <row r="284" spans="1:14">
       <c r="A284" s="10"/>
       <c r="B284" s="16"/>
       <c r="C284" s="10"/>
@@ -5849,14 +6150,15 @@
       <c r="E284" s="10"/>
       <c r="F284" s="10"/>
       <c r="G284" s="10"/>
-      <c r="H284" s="16"/>
+      <c r="H284" s="10"/>
       <c r="I284" s="16"/>
       <c r="J284" s="16"/>
       <c r="K284" s="16"/>
       <c r="L284" s="16"/>
       <c r="M284" s="16"/>
-    </row>
-    <row r="285" spans="1:13">
+      <c r="N284" s="16"/>
+    </row>
+    <row r="285" spans="1:14">
       <c r="A285" s="10"/>
       <c r="B285" s="16"/>
       <c r="C285" s="10"/>
@@ -5864,14 +6166,15 @@
       <c r="E285" s="10"/>
       <c r="F285" s="10"/>
       <c r="G285" s="10"/>
-      <c r="H285" s="16"/>
+      <c r="H285" s="10"/>
       <c r="I285" s="16"/>
       <c r="J285" s="16"/>
       <c r="K285" s="16"/>
       <c r="L285" s="16"/>
       <c r="M285" s="16"/>
-    </row>
-    <row r="286" spans="1:13">
+      <c r="N285" s="16"/>
+    </row>
+    <row r="286" spans="1:14">
       <c r="A286" s="10"/>
       <c r="B286" s="16"/>
       <c r="C286" s="10"/>
@@ -5879,14 +6182,15 @@
       <c r="E286" s="10"/>
       <c r="F286" s="10"/>
       <c r="G286" s="10"/>
-      <c r="H286" s="16"/>
+      <c r="H286" s="10"/>
       <c r="I286" s="16"/>
       <c r="J286" s="16"/>
       <c r="K286" s="16"/>
       <c r="L286" s="16"/>
       <c r="M286" s="16"/>
-    </row>
-    <row r="287" spans="1:13">
+      <c r="N286" s="16"/>
+    </row>
+    <row r="287" spans="1:14">
       <c r="A287" s="10"/>
       <c r="B287" s="16"/>
       <c r="C287" s="10"/>
@@ -5894,14 +6198,15 @@
       <c r="E287" s="10"/>
       <c r="F287" s="10"/>
       <c r="G287" s="10"/>
-      <c r="H287" s="16"/>
+      <c r="H287" s="10"/>
       <c r="I287" s="16"/>
       <c r="J287" s="16"/>
       <c r="K287" s="16"/>
       <c r="L287" s="16"/>
       <c r="M287" s="16"/>
-    </row>
-    <row r="288" spans="1:13">
+      <c r="N287" s="16"/>
+    </row>
+    <row r="288" spans="1:14">
       <c r="A288" s="10"/>
       <c r="B288" s="16"/>
       <c r="C288" s="10"/>
@@ -5909,14 +6214,15 @@
       <c r="E288" s="10"/>
       <c r="F288" s="10"/>
       <c r="G288" s="10"/>
-      <c r="H288" s="16"/>
+      <c r="H288" s="10"/>
       <c r="I288" s="16"/>
       <c r="J288" s="16"/>
       <c r="K288" s="16"/>
       <c r="L288" s="16"/>
       <c r="M288" s="16"/>
-    </row>
-    <row r="289" spans="1:13">
+      <c r="N288" s="16"/>
+    </row>
+    <row r="289" spans="1:14">
       <c r="A289" s="10"/>
       <c r="B289" s="16"/>
       <c r="C289" s="10"/>
@@ -5924,14 +6230,15 @@
       <c r="E289" s="10"/>
       <c r="F289" s="10"/>
       <c r="G289" s="10"/>
-      <c r="H289" s="16"/>
+      <c r="H289" s="10"/>
       <c r="I289" s="16"/>
       <c r="J289" s="16"/>
       <c r="K289" s="16"/>
       <c r="L289" s="16"/>
       <c r="M289" s="16"/>
-    </row>
-    <row r="290" spans="1:13">
+      <c r="N289" s="16"/>
+    </row>
+    <row r="290" spans="1:14">
       <c r="A290" s="10"/>
       <c r="B290" s="16"/>
       <c r="C290" s="10"/>
@@ -5939,14 +6246,15 @@
       <c r="E290" s="10"/>
       <c r="F290" s="10"/>
       <c r="G290" s="10"/>
-      <c r="H290" s="16"/>
+      <c r="H290" s="10"/>
       <c r="I290" s="16"/>
       <c r="J290" s="16"/>
       <c r="K290" s="16"/>
       <c r="L290" s="16"/>
       <c r="M290" s="16"/>
-    </row>
-    <row r="291" spans="1:13">
+      <c r="N290" s="16"/>
+    </row>
+    <row r="291" spans="1:14">
       <c r="A291" s="10"/>
       <c r="B291" s="16"/>
       <c r="C291" s="10"/>
@@ -5954,14 +6262,15 @@
       <c r="E291" s="10"/>
       <c r="F291" s="10"/>
       <c r="G291" s="10"/>
-      <c r="H291" s="16"/>
+      <c r="H291" s="10"/>
       <c r="I291" s="16"/>
       <c r="J291" s="16"/>
       <c r="K291" s="16"/>
       <c r="L291" s="16"/>
       <c r="M291" s="16"/>
-    </row>
-    <row r="292" spans="1:13">
+      <c r="N291" s="16"/>
+    </row>
+    <row r="292" spans="1:14">
       <c r="A292" s="10"/>
       <c r="B292" s="16"/>
       <c r="C292" s="10"/>
@@ -5969,14 +6278,15 @@
       <c r="E292" s="10"/>
       <c r="F292" s="10"/>
       <c r="G292" s="10"/>
-      <c r="H292" s="16"/>
+      <c r="H292" s="10"/>
       <c r="I292" s="16"/>
       <c r="J292" s="16"/>
       <c r="K292" s="16"/>
       <c r="L292" s="16"/>
       <c r="M292" s="16"/>
-    </row>
-    <row r="293" spans="1:13">
+      <c r="N292" s="16"/>
+    </row>
+    <row r="293" spans="1:14">
       <c r="A293" s="10"/>
       <c r="B293" s="16"/>
       <c r="C293" s="10"/>
@@ -5984,14 +6294,15 @@
       <c r="E293" s="10"/>
       <c r="F293" s="10"/>
       <c r="G293" s="10"/>
-      <c r="H293" s="16"/>
+      <c r="H293" s="10"/>
       <c r="I293" s="16"/>
       <c r="J293" s="16"/>
       <c r="K293" s="16"/>
       <c r="L293" s="16"/>
       <c r="M293" s="16"/>
-    </row>
-    <row r="294" spans="1:13">
+      <c r="N293" s="16"/>
+    </row>
+    <row r="294" spans="1:14">
       <c r="A294" s="10"/>
       <c r="B294" s="16"/>
       <c r="C294" s="10"/>
@@ -5999,14 +6310,15 @@
       <c r="E294" s="10"/>
       <c r="F294" s="10"/>
       <c r="G294" s="10"/>
-      <c r="H294" s="16"/>
+      <c r="H294" s="10"/>
       <c r="I294" s="16"/>
       <c r="J294" s="16"/>
       <c r="K294" s="16"/>
       <c r="L294" s="16"/>
       <c r="M294" s="16"/>
-    </row>
-    <row r="295" spans="1:13">
+      <c r="N294" s="16"/>
+    </row>
+    <row r="295" spans="1:14">
       <c r="A295" s="10"/>
       <c r="B295" s="16"/>
       <c r="C295" s="10"/>
@@ -6014,14 +6326,15 @@
       <c r="E295" s="10"/>
       <c r="F295" s="10"/>
       <c r="G295" s="10"/>
-      <c r="H295" s="16"/>
+      <c r="H295" s="10"/>
       <c r="I295" s="16"/>
       <c r="J295" s="16"/>
       <c r="K295" s="16"/>
       <c r="L295" s="16"/>
       <c r="M295" s="16"/>
-    </row>
-    <row r="296" spans="1:13">
+      <c r="N295" s="16"/>
+    </row>
+    <row r="296" spans="1:14">
       <c r="A296" s="10"/>
       <c r="B296" s="16"/>
       <c r="C296" s="10"/>
@@ -6029,14 +6342,15 @@
       <c r="E296" s="10"/>
       <c r="F296" s="10"/>
       <c r="G296" s="10"/>
-      <c r="H296" s="16"/>
+      <c r="H296" s="10"/>
       <c r="I296" s="16"/>
       <c r="J296" s="16"/>
       <c r="K296" s="16"/>
       <c r="L296" s="16"/>
       <c r="M296" s="16"/>
-    </row>
-    <row r="297" spans="1:13">
+      <c r="N296" s="16"/>
+    </row>
+    <row r="297" spans="1:14">
       <c r="A297" s="10"/>
       <c r="B297" s="16"/>
       <c r="C297" s="10"/>
@@ -6044,14 +6358,15 @@
       <c r="E297" s="10"/>
       <c r="F297" s="10"/>
       <c r="G297" s="10"/>
-      <c r="H297" s="16"/>
+      <c r="H297" s="10"/>
       <c r="I297" s="16"/>
       <c r="J297" s="16"/>
       <c r="K297" s="16"/>
       <c r="L297" s="16"/>
       <c r="M297" s="16"/>
-    </row>
-    <row r="298" spans="1:13">
+      <c r="N297" s="16"/>
+    </row>
+    <row r="298" spans="1:14">
       <c r="A298" s="10"/>
       <c r="B298" s="16"/>
       <c r="C298" s="10"/>
@@ -6059,14 +6374,15 @@
       <c r="E298" s="10"/>
       <c r="F298" s="10"/>
       <c r="G298" s="10"/>
-      <c r="H298" s="16"/>
+      <c r="H298" s="10"/>
       <c r="I298" s="16"/>
       <c r="J298" s="16"/>
       <c r="K298" s="16"/>
       <c r="L298" s="16"/>
       <c r="M298" s="16"/>
-    </row>
-    <row r="299" spans="1:13">
+      <c r="N298" s="16"/>
+    </row>
+    <row r="299" spans="1:14">
       <c r="A299" s="10"/>
       <c r="B299" s="16"/>
       <c r="C299" s="10"/>
@@ -6074,14 +6390,15 @@
       <c r="E299" s="10"/>
       <c r="F299" s="10"/>
       <c r="G299" s="10"/>
-      <c r="H299" s="16"/>
+      <c r="H299" s="10"/>
       <c r="I299" s="16"/>
       <c r="J299" s="16"/>
       <c r="K299" s="16"/>
       <c r="L299" s="16"/>
       <c r="M299" s="16"/>
-    </row>
-    <row r="300" spans="1:13">
+      <c r="N299" s="16"/>
+    </row>
+    <row r="300" spans="1:14">
       <c r="A300" s="10"/>
       <c r="B300" s="16"/>
       <c r="C300" s="10"/>
@@ -6089,14 +6406,15 @@
       <c r="E300" s="10"/>
       <c r="F300" s="10"/>
       <c r="G300" s="10"/>
-      <c r="H300" s="16"/>
+      <c r="H300" s="10"/>
       <c r="I300" s="16"/>
       <c r="J300" s="16"/>
       <c r="K300" s="16"/>
       <c r="L300" s="16"/>
       <c r="M300" s="16"/>
-    </row>
-    <row r="301" spans="1:13">
+      <c r="N300" s="16"/>
+    </row>
+    <row r="301" spans="1:14">
       <c r="A301" s="10"/>
       <c r="B301" s="16"/>
       <c r="C301" s="10"/>
@@ -6104,14 +6422,15 @@
       <c r="E301" s="10"/>
       <c r="F301" s="10"/>
       <c r="G301" s="10"/>
-      <c r="H301" s="16"/>
+      <c r="H301" s="10"/>
       <c r="I301" s="16"/>
       <c r="J301" s="16"/>
       <c r="K301" s="16"/>
       <c r="L301" s="16"/>
       <c r="M301" s="16"/>
-    </row>
-    <row r="302" spans="1:13">
+      <c r="N301" s="16"/>
+    </row>
+    <row r="302" spans="1:14">
       <c r="A302" s="10"/>
       <c r="B302" s="16"/>
       <c r="C302" s="10"/>
@@ -6119,14 +6438,15 @@
       <c r="E302" s="10"/>
       <c r="F302" s="10"/>
       <c r="G302" s="10"/>
-      <c r="H302" s="16"/>
+      <c r="H302" s="10"/>
       <c r="I302" s="16"/>
       <c r="J302" s="16"/>
       <c r="K302" s="16"/>
       <c r="L302" s="16"/>
       <c r="M302" s="16"/>
-    </row>
-    <row r="303" spans="1:13">
+      <c r="N302" s="16"/>
+    </row>
+    <row r="303" spans="1:14">
       <c r="A303" s="10"/>
       <c r="B303" s="16"/>
       <c r="C303" s="10"/>
@@ -6134,14 +6454,15 @@
       <c r="E303" s="10"/>
       <c r="F303" s="10"/>
       <c r="G303" s="10"/>
-      <c r="H303" s="16"/>
+      <c r="H303" s="10"/>
       <c r="I303" s="16"/>
       <c r="J303" s="16"/>
       <c r="K303" s="16"/>
       <c r="L303" s="16"/>
       <c r="M303" s="16"/>
-    </row>
-    <row r="304" spans="1:13">
+      <c r="N303" s="16"/>
+    </row>
+    <row r="304" spans="1:14">
       <c r="A304" s="10"/>
       <c r="B304" s="16"/>
       <c r="C304" s="10"/>
@@ -6149,14 +6470,15 @@
       <c r="E304" s="10"/>
       <c r="F304" s="10"/>
       <c r="G304" s="10"/>
-      <c r="H304" s="16"/>
+      <c r="H304" s="10"/>
       <c r="I304" s="16"/>
       <c r="J304" s="16"/>
       <c r="K304" s="16"/>
       <c r="L304" s="16"/>
       <c r="M304" s="16"/>
-    </row>
-    <row r="305" spans="1:13">
+      <c r="N304" s="16"/>
+    </row>
+    <row r="305" spans="1:14">
       <c r="A305" s="10"/>
       <c r="B305" s="16"/>
       <c r="C305" s="10"/>
@@ -6164,14 +6486,15 @@
       <c r="E305" s="10"/>
       <c r="F305" s="10"/>
       <c r="G305" s="10"/>
-      <c r="H305" s="16"/>
+      <c r="H305" s="10"/>
       <c r="I305" s="16"/>
       <c r="J305" s="16"/>
       <c r="K305" s="16"/>
       <c r="L305" s="16"/>
       <c r="M305" s="16"/>
-    </row>
-    <row r="306" spans="1:13">
+      <c r="N305" s="16"/>
+    </row>
+    <row r="306" spans="1:14">
       <c r="A306" s="10"/>
       <c r="B306" s="16"/>
       <c r="C306" s="10"/>
@@ -6179,14 +6502,15 @@
       <c r="E306" s="10"/>
       <c r="F306" s="10"/>
       <c r="G306" s="10"/>
-      <c r="H306" s="16"/>
+      <c r="H306" s="10"/>
       <c r="I306" s="16"/>
       <c r="J306" s="16"/>
       <c r="K306" s="16"/>
       <c r="L306" s="16"/>
       <c r="M306" s="16"/>
-    </row>
-    <row r="307" spans="1:13">
+      <c r="N306" s="16"/>
+    </row>
+    <row r="307" spans="1:14">
       <c r="A307" s="10"/>
       <c r="B307" s="16"/>
       <c r="C307" s="10"/>
@@ -6194,14 +6518,15 @@
       <c r="E307" s="10"/>
       <c r="F307" s="10"/>
       <c r="G307" s="10"/>
-      <c r="H307" s="16"/>
+      <c r="H307" s="10"/>
       <c r="I307" s="16"/>
       <c r="J307" s="16"/>
       <c r="K307" s="16"/>
       <c r="L307" s="16"/>
       <c r="M307" s="16"/>
-    </row>
-    <row r="308" spans="1:13">
+      <c r="N307" s="16"/>
+    </row>
+    <row r="308" spans="1:14">
       <c r="A308" s="10"/>
       <c r="B308" s="16"/>
       <c r="C308" s="10"/>
@@ -6209,14 +6534,15 @@
       <c r="E308" s="10"/>
       <c r="F308" s="10"/>
       <c r="G308" s="10"/>
-      <c r="H308" s="16"/>
+      <c r="H308" s="10"/>
       <c r="I308" s="16"/>
       <c r="J308" s="16"/>
       <c r="K308" s="16"/>
       <c r="L308" s="16"/>
       <c r="M308" s="16"/>
-    </row>
-    <row r="309" spans="1:13">
+      <c r="N308" s="16"/>
+    </row>
+    <row r="309" spans="1:14">
       <c r="A309" s="10"/>
       <c r="B309" s="16"/>
       <c r="C309" s="10"/>
@@ -6224,14 +6550,15 @@
       <c r="E309" s="10"/>
       <c r="F309" s="10"/>
       <c r="G309" s="10"/>
-      <c r="H309" s="16"/>
+      <c r="H309" s="10"/>
       <c r="I309" s="16"/>
       <c r="J309" s="16"/>
       <c r="K309" s="16"/>
       <c r="L309" s="16"/>
       <c r="M309" s="16"/>
-    </row>
-    <row r="310" spans="1:13">
+      <c r="N309" s="16"/>
+    </row>
+    <row r="310" spans="1:14">
       <c r="A310" s="10"/>
       <c r="B310" s="16"/>
       <c r="C310" s="10"/>
@@ -6239,14 +6566,15 @@
       <c r="E310" s="10"/>
       <c r="F310" s="10"/>
       <c r="G310" s="10"/>
-      <c r="H310" s="16"/>
+      <c r="H310" s="10"/>
       <c r="I310" s="16"/>
       <c r="J310" s="16"/>
       <c r="K310" s="16"/>
       <c r="L310" s="16"/>
       <c r="M310" s="16"/>
-    </row>
-    <row r="311" spans="1:13">
+      <c r="N310" s="16"/>
+    </row>
+    <row r="311" spans="1:14">
       <c r="A311" s="10"/>
       <c r="B311" s="16"/>
       <c r="C311" s="10"/>
@@ -6254,14 +6582,15 @@
       <c r="E311" s="10"/>
       <c r="F311" s="10"/>
       <c r="G311" s="10"/>
-      <c r="H311" s="16"/>
+      <c r="H311" s="10"/>
       <c r="I311" s="16"/>
       <c r="J311" s="16"/>
       <c r="K311" s="16"/>
       <c r="L311" s="16"/>
       <c r="M311" s="16"/>
-    </row>
-    <row r="312" spans="1:13">
+      <c r="N311" s="16"/>
+    </row>
+    <row r="312" spans="1:14">
       <c r="A312" s="10"/>
       <c r="B312" s="16"/>
       <c r="C312" s="10"/>
@@ -6269,14 +6598,15 @@
       <c r="E312" s="10"/>
       <c r="F312" s="10"/>
       <c r="G312" s="10"/>
-      <c r="H312" s="16"/>
+      <c r="H312" s="10"/>
       <c r="I312" s="16"/>
       <c r="J312" s="16"/>
       <c r="K312" s="16"/>
       <c r="L312" s="16"/>
       <c r="M312" s="16"/>
-    </row>
-    <row r="313" spans="1:13">
+      <c r="N312" s="16"/>
+    </row>
+    <row r="313" spans="1:14">
       <c r="A313" s="10"/>
       <c r="B313" s="16"/>
       <c r="C313" s="10"/>
@@ -6284,14 +6614,15 @@
       <c r="E313" s="10"/>
       <c r="F313" s="10"/>
       <c r="G313" s="10"/>
-      <c r="H313" s="16"/>
+      <c r="H313" s="10"/>
       <c r="I313" s="16"/>
       <c r="J313" s="16"/>
       <c r="K313" s="16"/>
       <c r="L313" s="16"/>
       <c r="M313" s="16"/>
-    </row>
-    <row r="314" spans="1:13">
+      <c r="N313" s="16"/>
+    </row>
+    <row r="314" spans="1:14">
       <c r="A314" s="10"/>
       <c r="B314" s="16"/>
       <c r="C314" s="10"/>
@@ -6299,14 +6630,15 @@
       <c r="E314" s="10"/>
       <c r="F314" s="10"/>
       <c r="G314" s="10"/>
-      <c r="H314" s="16"/>
+      <c r="H314" s="10"/>
       <c r="I314" s="16"/>
       <c r="J314" s="16"/>
       <c r="K314" s="16"/>
       <c r="L314" s="16"/>
       <c r="M314" s="16"/>
-    </row>
-    <row r="315" spans="1:13">
+      <c r="N314" s="16"/>
+    </row>
+    <row r="315" spans="1:14">
       <c r="A315" s="10"/>
       <c r="B315" s="16"/>
       <c r="C315" s="10"/>
@@ -6314,14 +6646,15 @@
       <c r="E315" s="10"/>
       <c r="F315" s="10"/>
       <c r="G315" s="10"/>
-      <c r="H315" s="16"/>
+      <c r="H315" s="10"/>
       <c r="I315" s="16"/>
       <c r="J315" s="16"/>
       <c r="K315" s="16"/>
       <c r="L315" s="16"/>
       <c r="M315" s="16"/>
-    </row>
-    <row r="316" spans="1:13">
+      <c r="N315" s="16"/>
+    </row>
+    <row r="316" spans="1:14">
       <c r="A316" s="10"/>
       <c r="B316" s="16"/>
       <c r="C316" s="10"/>
@@ -6329,14 +6662,15 @@
       <c r="E316" s="10"/>
       <c r="F316" s="10"/>
       <c r="G316" s="10"/>
-      <c r="H316" s="16"/>
+      <c r="H316" s="10"/>
       <c r="I316" s="16"/>
       <c r="J316" s="16"/>
       <c r="K316" s="16"/>
       <c r="L316" s="16"/>
       <c r="M316" s="16"/>
-    </row>
-    <row r="317" spans="1:13">
+      <c r="N316" s="16"/>
+    </row>
+    <row r="317" spans="1:14">
       <c r="A317" s="10"/>
       <c r="B317" s="16"/>
       <c r="C317" s="10"/>
@@ -6344,14 +6678,15 @@
       <c r="E317" s="10"/>
       <c r="F317" s="10"/>
       <c r="G317" s="10"/>
-      <c r="H317" s="16"/>
+      <c r="H317" s="10"/>
       <c r="I317" s="16"/>
       <c r="J317" s="16"/>
       <c r="K317" s="16"/>
       <c r="L317" s="16"/>
       <c r="M317" s="16"/>
-    </row>
-    <row r="318" spans="1:13">
+      <c r="N317" s="16"/>
+    </row>
+    <row r="318" spans="1:14">
       <c r="A318" s="10"/>
       <c r="B318" s="16"/>
       <c r="C318" s="10"/>
@@ -6359,14 +6694,15 @@
       <c r="E318" s="10"/>
       <c r="F318" s="10"/>
       <c r="G318" s="10"/>
-      <c r="H318" s="16"/>
+      <c r="H318" s="10"/>
       <c r="I318" s="16"/>
       <c r="J318" s="16"/>
       <c r="K318" s="16"/>
       <c r="L318" s="16"/>
       <c r="M318" s="16"/>
-    </row>
-    <row r="319" spans="1:13">
+      <c r="N318" s="16"/>
+    </row>
+    <row r="319" spans="1:14">
       <c r="A319" s="10"/>
       <c r="B319" s="16"/>
       <c r="C319" s="10"/>
@@ -6374,14 +6710,15 @@
       <c r="E319" s="10"/>
       <c r="F319" s="10"/>
       <c r="G319" s="10"/>
-      <c r="H319" s="16"/>
+      <c r="H319" s="10"/>
       <c r="I319" s="16"/>
       <c r="J319" s="16"/>
       <c r="K319" s="16"/>
       <c r="L319" s="16"/>
       <c r="M319" s="16"/>
-    </row>
-    <row r="320" spans="1:13">
+      <c r="N319" s="16"/>
+    </row>
+    <row r="320" spans="1:14">
       <c r="A320" s="10"/>
       <c r="B320" s="16"/>
       <c r="C320" s="10"/>
@@ -6389,14 +6726,15 @@
       <c r="E320" s="10"/>
       <c r="F320" s="10"/>
       <c r="G320" s="10"/>
-      <c r="H320" s="16"/>
+      <c r="H320" s="10"/>
       <c r="I320" s="16"/>
       <c r="J320" s="16"/>
       <c r="K320" s="16"/>
       <c r="L320" s="16"/>
       <c r="M320" s="16"/>
-    </row>
-    <row r="321" spans="1:13">
+      <c r="N320" s="16"/>
+    </row>
+    <row r="321" spans="1:14">
       <c r="A321" s="10"/>
       <c r="B321" s="16"/>
       <c r="C321" s="10"/>
@@ -6404,14 +6742,15 @@
       <c r="E321" s="10"/>
       <c r="F321" s="10"/>
       <c r="G321" s="10"/>
-      <c r="H321" s="16"/>
+      <c r="H321" s="10"/>
       <c r="I321" s="16"/>
       <c r="J321" s="16"/>
       <c r="K321" s="16"/>
       <c r="L321" s="16"/>
       <c r="M321" s="16"/>
-    </row>
-    <row r="322" spans="1:13">
+      <c r="N321" s="16"/>
+    </row>
+    <row r="322" spans="1:14">
       <c r="A322" s="10"/>
       <c r="B322" s="16"/>
       <c r="C322" s="10"/>
@@ -6419,14 +6758,15 @@
       <c r="E322" s="10"/>
       <c r="F322" s="10"/>
       <c r="G322" s="10"/>
-      <c r="H322" s="16"/>
+      <c r="H322" s="10"/>
       <c r="I322" s="16"/>
       <c r="J322" s="16"/>
       <c r="K322" s="16"/>
       <c r="L322" s="16"/>
       <c r="M322" s="16"/>
-    </row>
-    <row r="323" spans="1:13">
+      <c r="N322" s="16"/>
+    </row>
+    <row r="323" spans="1:14">
       <c r="A323" s="10"/>
       <c r="B323" s="16"/>
       <c r="C323" s="10"/>
@@ -6434,14 +6774,15 @@
       <c r="E323" s="10"/>
       <c r="F323" s="10"/>
       <c r="G323" s="10"/>
-      <c r="H323" s="16"/>
+      <c r="H323" s="10"/>
       <c r="I323" s="16"/>
       <c r="J323" s="16"/>
       <c r="K323" s="16"/>
       <c r="L323" s="16"/>
       <c r="M323" s="16"/>
-    </row>
-    <row r="324" spans="1:13">
+      <c r="N323" s="16"/>
+    </row>
+    <row r="324" spans="1:14">
       <c r="A324" s="10"/>
       <c r="B324" s="16"/>
       <c r="C324" s="10"/>
@@ -6449,14 +6790,15 @@
       <c r="E324" s="10"/>
       <c r="F324" s="10"/>
       <c r="G324" s="10"/>
-      <c r="H324" s="16"/>
+      <c r="H324" s="10"/>
       <c r="I324" s="16"/>
       <c r="J324" s="16"/>
       <c r="K324" s="16"/>
       <c r="L324" s="16"/>
       <c r="M324" s="16"/>
-    </row>
-    <row r="325" spans="1:13">
+      <c r="N324" s="16"/>
+    </row>
+    <row r="325" spans="1:14">
       <c r="A325" s="10"/>
       <c r="B325" s="16"/>
       <c r="C325" s="10"/>
@@ -6464,14 +6806,15 @@
       <c r="E325" s="10"/>
       <c r="F325" s="10"/>
       <c r="G325" s="10"/>
-      <c r="H325" s="16"/>
+      <c r="H325" s="10"/>
       <c r="I325" s="16"/>
       <c r="J325" s="16"/>
       <c r="K325" s="16"/>
       <c r="L325" s="16"/>
       <c r="M325" s="16"/>
-    </row>
-    <row r="326" spans="1:13">
+      <c r="N325" s="16"/>
+    </row>
+    <row r="326" spans="1:14">
       <c r="A326" s="10"/>
       <c r="B326" s="16"/>
       <c r="C326" s="10"/>
@@ -6479,14 +6822,15 @@
       <c r="E326" s="10"/>
       <c r="F326" s="10"/>
       <c r="G326" s="10"/>
-      <c r="H326" s="16"/>
+      <c r="H326" s="10"/>
       <c r="I326" s="16"/>
       <c r="J326" s="16"/>
       <c r="K326" s="16"/>
       <c r="L326" s="16"/>
       <c r="M326" s="16"/>
-    </row>
-    <row r="327" spans="1:13">
+      <c r="N326" s="16"/>
+    </row>
+    <row r="327" spans="1:14">
       <c r="A327" s="10"/>
       <c r="B327" s="16"/>
       <c r="C327" s="10"/>
@@ -6494,14 +6838,15 @@
       <c r="E327" s="10"/>
       <c r="F327" s="10"/>
       <c r="G327" s="10"/>
-      <c r="H327" s="16"/>
+      <c r="H327" s="10"/>
       <c r="I327" s="16"/>
       <c r="J327" s="16"/>
       <c r="K327" s="16"/>
       <c r="L327" s="16"/>
       <c r="M327" s="16"/>
-    </row>
-    <row r="328" spans="1:13">
+      <c r="N327" s="16"/>
+    </row>
+    <row r="328" spans="1:14">
       <c r="A328" s="10"/>
       <c r="B328" s="16"/>
       <c r="C328" s="10"/>
@@ -6509,14 +6854,15 @@
       <c r="E328" s="10"/>
       <c r="F328" s="10"/>
       <c r="G328" s="10"/>
-      <c r="H328" s="16"/>
+      <c r="H328" s="10"/>
       <c r="I328" s="16"/>
       <c r="J328" s="16"/>
       <c r="K328" s="16"/>
       <c r="L328" s="16"/>
       <c r="M328" s="16"/>
-    </row>
-    <row r="329" spans="1:13">
+      <c r="N328" s="16"/>
+    </row>
+    <row r="329" spans="1:14">
       <c r="A329" s="10"/>
       <c r="B329" s="16"/>
       <c r="C329" s="10"/>
@@ -6524,14 +6870,15 @@
       <c r="E329" s="10"/>
       <c r="F329" s="10"/>
       <c r="G329" s="10"/>
-      <c r="H329" s="16"/>
+      <c r="H329" s="10"/>
       <c r="I329" s="16"/>
       <c r="J329" s="16"/>
       <c r="K329" s="16"/>
       <c r="L329" s="16"/>
       <c r="M329" s="16"/>
-    </row>
-    <row r="330" spans="1:13">
+      <c r="N329" s="16"/>
+    </row>
+    <row r="330" spans="1:14">
       <c r="A330" s="10"/>
       <c r="B330" s="16"/>
       <c r="C330" s="10"/>
@@ -6539,14 +6886,15 @@
       <c r="E330" s="10"/>
       <c r="F330" s="10"/>
       <c r="G330" s="10"/>
-      <c r="H330" s="16"/>
+      <c r="H330" s="10"/>
       <c r="I330" s="16"/>
       <c r="J330" s="16"/>
       <c r="K330" s="16"/>
       <c r="L330" s="16"/>
       <c r="M330" s="16"/>
-    </row>
-    <row r="331" spans="1:13">
+      <c r="N330" s="16"/>
+    </row>
+    <row r="331" spans="1:14">
       <c r="A331" s="10"/>
       <c r="B331" s="16"/>
       <c r="C331" s="10"/>
@@ -6554,14 +6902,15 @@
       <c r="E331" s="10"/>
       <c r="F331" s="10"/>
       <c r="G331" s="10"/>
-      <c r="H331" s="16"/>
+      <c r="H331" s="10"/>
       <c r="I331" s="16"/>
       <c r="J331" s="16"/>
       <c r="K331" s="16"/>
       <c r="L331" s="16"/>
       <c r="M331" s="16"/>
-    </row>
-    <row r="332" spans="1:13">
+      <c r="N331" s="16"/>
+    </row>
+    <row r="332" spans="1:14">
       <c r="A332" s="10"/>
       <c r="B332" s="16"/>
       <c r="C332" s="10"/>
@@ -6569,14 +6918,15 @@
       <c r="E332" s="10"/>
       <c r="F332" s="10"/>
       <c r="G332" s="10"/>
-      <c r="H332" s="16"/>
+      <c r="H332" s="10"/>
       <c r="I332" s="16"/>
       <c r="J332" s="16"/>
       <c r="K332" s="16"/>
       <c r="L332" s="16"/>
       <c r="M332" s="16"/>
-    </row>
-    <row r="333" spans="1:13">
+      <c r="N332" s="16"/>
+    </row>
+    <row r="333" spans="1:14">
       <c r="A333" s="10"/>
       <c r="B333" s="16"/>
       <c r="C333" s="10"/>
@@ -6584,14 +6934,15 @@
       <c r="E333" s="10"/>
       <c r="F333" s="10"/>
       <c r="G333" s="10"/>
-      <c r="H333" s="16"/>
+      <c r="H333" s="10"/>
       <c r="I333" s="16"/>
       <c r="J333" s="16"/>
       <c r="K333" s="16"/>
       <c r="L333" s="16"/>
       <c r="M333" s="16"/>
-    </row>
-    <row r="334" spans="1:13">
+      <c r="N333" s="16"/>
+    </row>
+    <row r="334" spans="1:14">
       <c r="A334" s="10"/>
       <c r="B334" s="16"/>
       <c r="C334" s="10"/>
@@ -6599,14 +6950,15 @@
       <c r="E334" s="10"/>
       <c r="F334" s="10"/>
       <c r="G334" s="10"/>
-      <c r="H334" s="16"/>
+      <c r="H334" s="10"/>
       <c r="I334" s="16"/>
       <c r="J334" s="16"/>
       <c r="K334" s="16"/>
       <c r="L334" s="16"/>
       <c r="M334" s="16"/>
-    </row>
-    <row r="335" spans="1:13">
+      <c r="N334" s="16"/>
+    </row>
+    <row r="335" spans="1:14">
       <c r="A335" s="10"/>
       <c r="B335" s="16"/>
       <c r="C335" s="10"/>
@@ -6614,14 +6966,15 @@
       <c r="E335" s="10"/>
       <c r="F335" s="10"/>
       <c r="G335" s="10"/>
-      <c r="H335" s="16"/>
+      <c r="H335" s="10"/>
       <c r="I335" s="16"/>
       <c r="J335" s="16"/>
       <c r="K335" s="16"/>
       <c r="L335" s="16"/>
       <c r="M335" s="16"/>
-    </row>
-    <row r="336" spans="1:13">
+      <c r="N335" s="16"/>
+    </row>
+    <row r="336" spans="1:14">
       <c r="A336" s="10"/>
       <c r="B336" s="16"/>
       <c r="C336" s="10"/>
@@ -6629,14 +6982,15 @@
       <c r="E336" s="10"/>
       <c r="F336" s="10"/>
       <c r="G336" s="10"/>
-      <c r="H336" s="16"/>
+      <c r="H336" s="10"/>
       <c r="I336" s="16"/>
       <c r="J336" s="16"/>
       <c r="K336" s="16"/>
       <c r="L336" s="16"/>
       <c r="M336" s="16"/>
-    </row>
-    <row r="337" spans="1:13">
+      <c r="N336" s="16"/>
+    </row>
+    <row r="337" spans="1:14">
       <c r="A337" s="10"/>
       <c r="B337" s="16"/>
       <c r="C337" s="10"/>
@@ -6644,14 +6998,15 @@
       <c r="E337" s="10"/>
       <c r="F337" s="10"/>
       <c r="G337" s="10"/>
-      <c r="H337" s="16"/>
+      <c r="H337" s="10"/>
       <c r="I337" s="16"/>
       <c r="J337" s="16"/>
       <c r="K337" s="16"/>
       <c r="L337" s="16"/>
       <c r="M337" s="16"/>
-    </row>
-    <row r="338" spans="1:13">
+      <c r="N337" s="16"/>
+    </row>
+    <row r="338" spans="1:14">
       <c r="A338" s="10"/>
       <c r="B338" s="16"/>
       <c r="C338" s="10"/>
@@ -6659,14 +7014,15 @@
       <c r="E338" s="10"/>
       <c r="F338" s="10"/>
       <c r="G338" s="10"/>
-      <c r="H338" s="16"/>
+      <c r="H338" s="10"/>
       <c r="I338" s="16"/>
       <c r="J338" s="16"/>
       <c r="K338" s="16"/>
       <c r="L338" s="16"/>
       <c r="M338" s="16"/>
-    </row>
-    <row r="339" spans="1:13">
+      <c r="N338" s="16"/>
+    </row>
+    <row r="339" spans="1:14">
       <c r="A339" s="10"/>
       <c r="B339" s="16"/>
       <c r="C339" s="10"/>
@@ -6674,14 +7030,15 @@
       <c r="E339" s="10"/>
       <c r="F339" s="10"/>
       <c r="G339" s="10"/>
-      <c r="H339" s="16"/>
+      <c r="H339" s="10"/>
       <c r="I339" s="16"/>
       <c r="J339" s="16"/>
       <c r="K339" s="16"/>
       <c r="L339" s="16"/>
       <c r="M339" s="16"/>
-    </row>
-    <row r="340" spans="1:13">
+      <c r="N339" s="16"/>
+    </row>
+    <row r="340" spans="1:14">
       <c r="A340" s="10"/>
       <c r="B340" s="16"/>
       <c r="C340" s="10"/>
@@ -6689,14 +7046,15 @@
       <c r="E340" s="10"/>
       <c r="F340" s="10"/>
       <c r="G340" s="10"/>
-      <c r="H340" s="16"/>
+      <c r="H340" s="10"/>
       <c r="I340" s="16"/>
       <c r="J340" s="16"/>
       <c r="K340" s="16"/>
       <c r="L340" s="16"/>
       <c r="M340" s="16"/>
-    </row>
-    <row r="341" spans="1:13">
+      <c r="N340" s="16"/>
+    </row>
+    <row r="341" spans="1:14">
       <c r="A341" s="10"/>
       <c r="B341" s="16"/>
       <c r="C341" s="10"/>
@@ -6704,14 +7062,15 @@
       <c r="E341" s="10"/>
       <c r="F341" s="10"/>
       <c r="G341" s="10"/>
-      <c r="H341" s="16"/>
+      <c r="H341" s="10"/>
       <c r="I341" s="16"/>
       <c r="J341" s="16"/>
       <c r="K341" s="16"/>
       <c r="L341" s="16"/>
       <c r="M341" s="16"/>
-    </row>
-    <row r="342" spans="1:13">
+      <c r="N341" s="16"/>
+    </row>
+    <row r="342" spans="1:14">
       <c r="A342" s="10"/>
       <c r="B342" s="16"/>
       <c r="C342" s="10"/>
@@ -6719,14 +7078,15 @@
       <c r="E342" s="10"/>
       <c r="F342" s="10"/>
       <c r="G342" s="10"/>
-      <c r="H342" s="16"/>
+      <c r="H342" s="10"/>
       <c r="I342" s="16"/>
       <c r="J342" s="16"/>
       <c r="K342" s="16"/>
       <c r="L342" s="16"/>
       <c r="M342" s="16"/>
-    </row>
-    <row r="343" spans="1:13">
+      <c r="N342" s="16"/>
+    </row>
+    <row r="343" spans="1:14">
       <c r="A343" s="10"/>
       <c r="B343" s="16"/>
       <c r="C343" s="10"/>
@@ -6734,14 +7094,15 @@
       <c r="E343" s="10"/>
       <c r="F343" s="10"/>
       <c r="G343" s="10"/>
-      <c r="H343" s="16"/>
+      <c r="H343" s="10"/>
       <c r="I343" s="16"/>
       <c r="J343" s="16"/>
       <c r="K343" s="16"/>
       <c r="L343" s="16"/>
       <c r="M343" s="16"/>
-    </row>
-    <row r="344" spans="1:13">
+      <c r="N343" s="16"/>
+    </row>
+    <row r="344" spans="1:14">
       <c r="A344" s="10"/>
       <c r="B344" s="16"/>
       <c r="C344" s="10"/>
@@ -6749,14 +7110,15 @@
       <c r="E344" s="10"/>
       <c r="F344" s="10"/>
       <c r="G344" s="10"/>
-      <c r="H344" s="16"/>
+      <c r="H344" s="10"/>
       <c r="I344" s="16"/>
       <c r="J344" s="16"/>
       <c r="K344" s="16"/>
       <c r="L344" s="16"/>
       <c r="M344" s="16"/>
-    </row>
-    <row r="345" spans="1:13">
+      <c r="N344" s="16"/>
+    </row>
+    <row r="345" spans="1:14">
       <c r="A345" s="10"/>
       <c r="B345" s="16"/>
       <c r="C345" s="10"/>
@@ -6764,14 +7126,15 @@
       <c r="E345" s="10"/>
       <c r="F345" s="10"/>
       <c r="G345" s="10"/>
-      <c r="H345" s="16"/>
+      <c r="H345" s="10"/>
       <c r="I345" s="16"/>
       <c r="J345" s="16"/>
       <c r="K345" s="16"/>
       <c r="L345" s="16"/>
       <c r="M345" s="16"/>
-    </row>
-    <row r="346" spans="1:13">
+      <c r="N345" s="16"/>
+    </row>
+    <row r="346" spans="1:14">
       <c r="A346" s="10"/>
       <c r="B346" s="16"/>
       <c r="C346" s="10"/>
@@ -6779,14 +7142,15 @@
       <c r="E346" s="10"/>
       <c r="F346" s="10"/>
       <c r="G346" s="10"/>
-      <c r="H346" s="16"/>
+      <c r="H346" s="10"/>
       <c r="I346" s="16"/>
       <c r="J346" s="16"/>
       <c r="K346" s="16"/>
       <c r="L346" s="16"/>
       <c r="M346" s="16"/>
-    </row>
-    <row r="347" spans="1:13">
+      <c r="N346" s="16"/>
+    </row>
+    <row r="347" spans="1:14">
       <c r="A347" s="10"/>
       <c r="B347" s="16"/>
       <c r="C347" s="10"/>
@@ -6794,14 +7158,15 @@
       <c r="E347" s="10"/>
       <c r="F347" s="10"/>
       <c r="G347" s="10"/>
-      <c r="H347" s="16"/>
+      <c r="H347" s="10"/>
       <c r="I347" s="16"/>
       <c r="J347" s="16"/>
       <c r="K347" s="16"/>
       <c r="L347" s="16"/>
       <c r="M347" s="16"/>
-    </row>
-    <row r="348" spans="1:13">
+      <c r="N347" s="16"/>
+    </row>
+    <row r="348" spans="1:14">
       <c r="A348" s="10"/>
       <c r="B348" s="16"/>
       <c r="C348" s="10"/>
@@ -6809,14 +7174,15 @@
       <c r="E348" s="10"/>
       <c r="F348" s="10"/>
       <c r="G348" s="10"/>
-      <c r="H348" s="16"/>
+      <c r="H348" s="10"/>
       <c r="I348" s="16"/>
       <c r="J348" s="16"/>
       <c r="K348" s="16"/>
       <c r="L348" s="16"/>
       <c r="M348" s="16"/>
-    </row>
-    <row r="349" spans="1:13">
+      <c r="N348" s="16"/>
+    </row>
+    <row r="349" spans="1:14">
       <c r="A349" s="10"/>
       <c r="B349" s="16"/>
       <c r="C349" s="10"/>
@@ -6824,14 +7190,15 @@
       <c r="E349" s="10"/>
       <c r="F349" s="10"/>
       <c r="G349" s="10"/>
-      <c r="H349" s="16"/>
+      <c r="H349" s="10"/>
       <c r="I349" s="16"/>
       <c r="J349" s="16"/>
       <c r="K349" s="16"/>
       <c r="L349" s="16"/>
       <c r="M349" s="16"/>
-    </row>
-    <row r="350" spans="1:13">
+      <c r="N349" s="16"/>
+    </row>
+    <row r="350" spans="1:14">
       <c r="A350" s="10"/>
       <c r="B350" s="16"/>
       <c r="C350" s="10"/>
@@ -6839,14 +7206,15 @@
       <c r="E350" s="10"/>
       <c r="F350" s="10"/>
       <c r="G350" s="10"/>
-      <c r="H350" s="16"/>
+      <c r="H350" s="10"/>
       <c r="I350" s="16"/>
       <c r="J350" s="16"/>
       <c r="K350" s="16"/>
       <c r="L350" s="16"/>
       <c r="M350" s="16"/>
-    </row>
-    <row r="351" spans="1:13">
+      <c r="N350" s="16"/>
+    </row>
+    <row r="351" spans="1:14">
       <c r="A351" s="10"/>
       <c r="B351" s="16"/>
       <c r="C351" s="10"/>
@@ -6854,14 +7222,15 @@
       <c r="E351" s="10"/>
       <c r="F351" s="10"/>
       <c r="G351" s="10"/>
-      <c r="H351" s="16"/>
+      <c r="H351" s="10"/>
       <c r="I351" s="16"/>
       <c r="J351" s="16"/>
       <c r="K351" s="16"/>
       <c r="L351" s="16"/>
       <c r="M351" s="16"/>
-    </row>
-    <row r="352" spans="1:13">
+      <c r="N351" s="16"/>
+    </row>
+    <row r="352" spans="1:14">
       <c r="A352" s="10"/>
       <c r="B352" s="16"/>
       <c r="C352" s="10"/>
@@ -6869,14 +7238,15 @@
       <c r="E352" s="10"/>
       <c r="F352" s="10"/>
       <c r="G352" s="10"/>
-      <c r="H352" s="16"/>
+      <c r="H352" s="10"/>
       <c r="I352" s="16"/>
       <c r="J352" s="16"/>
       <c r="K352" s="16"/>
       <c r="L352" s="16"/>
       <c r="M352" s="16"/>
-    </row>
-    <row r="353" spans="1:13">
+      <c r="N352" s="16"/>
+    </row>
+    <row r="353" spans="1:14">
       <c r="A353" s="10"/>
       <c r="B353" s="16"/>
       <c r="C353" s="10"/>
@@ -6884,14 +7254,15 @@
       <c r="E353" s="10"/>
       <c r="F353" s="10"/>
       <c r="G353" s="10"/>
-      <c r="H353" s="16"/>
+      <c r="H353" s="10"/>
       <c r="I353" s="16"/>
       <c r="J353" s="16"/>
       <c r="K353" s="16"/>
       <c r="L353" s="16"/>
       <c r="M353" s="16"/>
-    </row>
-    <row r="354" spans="1:13">
+      <c r="N353" s="16"/>
+    </row>
+    <row r="354" spans="1:14">
       <c r="A354" s="10"/>
       <c r="B354" s="16"/>
       <c r="C354" s="10"/>
@@ -6899,14 +7270,15 @@
       <c r="E354" s="10"/>
       <c r="F354" s="10"/>
       <c r="G354" s="10"/>
-      <c r="H354" s="16"/>
+      <c r="H354" s="10"/>
       <c r="I354" s="16"/>
       <c r="J354" s="16"/>
       <c r="K354" s="16"/>
       <c r="L354" s="16"/>
       <c r="M354" s="16"/>
-    </row>
-    <row r="355" spans="1:13">
+      <c r="N354" s="16"/>
+    </row>
+    <row r="355" spans="1:14">
       <c r="A355" s="10"/>
       <c r="B355" s="16"/>
       <c r="C355" s="10"/>
@@ -6914,14 +7286,15 @@
       <c r="E355" s="10"/>
       <c r="F355" s="10"/>
       <c r="G355" s="10"/>
-      <c r="H355" s="16"/>
+      <c r="H355" s="10"/>
       <c r="I355" s="16"/>
       <c r="J355" s="16"/>
       <c r="K355" s="16"/>
       <c r="L355" s="16"/>
       <c r="M355" s="16"/>
-    </row>
-    <row r="356" spans="1:13">
+      <c r="N355" s="16"/>
+    </row>
+    <row r="356" spans="1:14">
       <c r="A356" s="10"/>
       <c r="B356" s="16"/>
       <c r="C356" s="10"/>
@@ -6929,14 +7302,15 @@
       <c r="E356" s="10"/>
       <c r="F356" s="10"/>
       <c r="G356" s="10"/>
-      <c r="H356" s="16"/>
+      <c r="H356" s="10"/>
       <c r="I356" s="16"/>
       <c r="J356" s="16"/>
       <c r="K356" s="16"/>
       <c r="L356" s="16"/>
       <c r="M356" s="16"/>
-    </row>
-    <row r="357" spans="1:13">
+      <c r="N356" s="16"/>
+    </row>
+    <row r="357" spans="1:14">
       <c r="A357" s="10"/>
       <c r="B357" s="16"/>
       <c r="C357" s="10"/>
@@ -6944,14 +7318,15 @@
       <c r="E357" s="10"/>
       <c r="F357" s="10"/>
       <c r="G357" s="10"/>
-      <c r="H357" s="16"/>
+      <c r="H357" s="10"/>
       <c r="I357" s="16"/>
       <c r="J357" s="16"/>
       <c r="K357" s="16"/>
       <c r="L357" s="16"/>
       <c r="M357" s="16"/>
-    </row>
-    <row r="358" spans="1:13">
+      <c r="N357" s="16"/>
+    </row>
+    <row r="358" spans="1:14">
       <c r="A358" s="10"/>
       <c r="B358" s="16"/>
       <c r="C358" s="10"/>
@@ -6959,14 +7334,15 @@
       <c r="E358" s="10"/>
       <c r="F358" s="10"/>
       <c r="G358" s="10"/>
-      <c r="H358" s="16"/>
+      <c r="H358" s="10"/>
       <c r="I358" s="16"/>
       <c r="J358" s="16"/>
       <c r="K358" s="16"/>
       <c r="L358" s="16"/>
       <c r="M358" s="16"/>
-    </row>
-    <row r="359" spans="1:13">
+      <c r="N358" s="16"/>
+    </row>
+    <row r="359" spans="1:14">
       <c r="A359" s="10"/>
       <c r="B359" s="16"/>
       <c r="C359" s="10"/>
@@ -6974,14 +7350,15 @@
       <c r="E359" s="10"/>
       <c r="F359" s="10"/>
       <c r="G359" s="10"/>
-      <c r="H359" s="16"/>
+      <c r="H359" s="10"/>
       <c r="I359" s="16"/>
       <c r="J359" s="16"/>
       <c r="K359" s="16"/>
       <c r="L359" s="16"/>
       <c r="M359" s="16"/>
-    </row>
-    <row r="360" spans="1:13">
+      <c r="N359" s="16"/>
+    </row>
+    <row r="360" spans="1:14">
       <c r="A360" s="10"/>
       <c r="B360" s="16"/>
       <c r="C360" s="10"/>
@@ -6989,14 +7366,15 @@
       <c r="E360" s="10"/>
       <c r="F360" s="10"/>
       <c r="G360" s="10"/>
-      <c r="H360" s="16"/>
+      <c r="H360" s="10"/>
       <c r="I360" s="16"/>
       <c r="J360" s="16"/>
       <c r="K360" s="16"/>
       <c r="L360" s="16"/>
       <c r="M360" s="16"/>
-    </row>
-    <row r="361" spans="1:13">
+      <c r="N360" s="16"/>
+    </row>
+    <row r="361" spans="1:14">
       <c r="A361" s="10"/>
       <c r="B361" s="16"/>
       <c r="C361" s="10"/>
@@ -7004,14 +7382,15 @@
       <c r="E361" s="10"/>
       <c r="F361" s="10"/>
       <c r="G361" s="10"/>
-      <c r="H361" s="16"/>
+      <c r="H361" s="10"/>
       <c r="I361" s="16"/>
       <c r="J361" s="16"/>
       <c r="K361" s="16"/>
       <c r="L361" s="16"/>
       <c r="M361" s="16"/>
-    </row>
-    <row r="362" spans="1:13">
+      <c r="N361" s="16"/>
+    </row>
+    <row r="362" spans="1:14">
       <c r="A362" s="10"/>
       <c r="B362" s="16"/>
       <c r="C362" s="10"/>
@@ -7019,14 +7398,15 @@
       <c r="E362" s="10"/>
       <c r="F362" s="10"/>
       <c r="G362" s="10"/>
-      <c r="H362" s="16"/>
+      <c r="H362" s="10"/>
       <c r="I362" s="16"/>
       <c r="J362" s="16"/>
       <c r="K362" s="16"/>
       <c r="L362" s="16"/>
       <c r="M362" s="16"/>
-    </row>
-    <row r="363" spans="1:13">
+      <c r="N362" s="16"/>
+    </row>
+    <row r="363" spans="1:14">
       <c r="A363" s="10"/>
       <c r="B363" s="16"/>
       <c r="C363" s="10"/>
@@ -7034,14 +7414,15 @@
       <c r="E363" s="10"/>
       <c r="F363" s="10"/>
       <c r="G363" s="10"/>
-      <c r="H363" s="16"/>
+      <c r="H363" s="10"/>
       <c r="I363" s="16"/>
       <c r="J363" s="16"/>
       <c r="K363" s="16"/>
       <c r="L363" s="16"/>
       <c r="M363" s="16"/>
-    </row>
-    <row r="364" spans="1:13">
+      <c r="N363" s="16"/>
+    </row>
+    <row r="364" spans="1:14">
       <c r="A364" s="10"/>
       <c r="B364" s="16"/>
       <c r="C364" s="10"/>
@@ -7049,14 +7430,15 @@
       <c r="E364" s="10"/>
       <c r="F364" s="10"/>
       <c r="G364" s="10"/>
-      <c r="H364" s="16"/>
+      <c r="H364" s="10"/>
       <c r="I364" s="16"/>
       <c r="J364" s="16"/>
       <c r="K364" s="16"/>
       <c r="L364" s="16"/>
       <c r="M364" s="16"/>
-    </row>
-    <row r="365" spans="1:13">
+      <c r="N364" s="16"/>
+    </row>
+    <row r="365" spans="1:14">
       <c r="A365" s="10"/>
       <c r="B365" s="16"/>
       <c r="C365" s="10"/>
@@ -7064,14 +7446,15 @@
       <c r="E365" s="10"/>
       <c r="F365" s="10"/>
       <c r="G365" s="10"/>
-      <c r="H365" s="16"/>
+      <c r="H365" s="10"/>
       <c r="I365" s="16"/>
       <c r="J365" s="16"/>
       <c r="K365" s="16"/>
       <c r="L365" s="16"/>
       <c r="M365" s="16"/>
-    </row>
-    <row r="366" spans="1:13">
+      <c r="N365" s="16"/>
+    </row>
+    <row r="366" spans="1:14">
       <c r="A366" s="10"/>
       <c r="B366" s="16"/>
       <c r="C366" s="10"/>
@@ -7079,14 +7462,15 @@
       <c r="E366" s="10"/>
       <c r="F366" s="10"/>
       <c r="G366" s="10"/>
-      <c r="H366" s="16"/>
+      <c r="H366" s="10"/>
       <c r="I366" s="16"/>
       <c r="J366" s="16"/>
       <c r="K366" s="16"/>
       <c r="L366" s="16"/>
       <c r="M366" s="16"/>
-    </row>
-    <row r="367" spans="1:13">
+      <c r="N366" s="16"/>
+    </row>
+    <row r="367" spans="1:14">
       <c r="A367" s="10"/>
       <c r="B367" s="16"/>
       <c r="C367" s="10"/>
@@ -7094,14 +7478,15 @@
       <c r="E367" s="10"/>
       <c r="F367" s="10"/>
       <c r="G367" s="10"/>
-      <c r="H367" s="16"/>
+      <c r="H367" s="10"/>
       <c r="I367" s="16"/>
       <c r="J367" s="16"/>
       <c r="K367" s="16"/>
       <c r="L367" s="16"/>
       <c r="M367" s="16"/>
-    </row>
-    <row r="368" spans="1:13">
+      <c r="N367" s="16"/>
+    </row>
+    <row r="368" spans="1:14">
       <c r="A368" s="10"/>
       <c r="B368" s="16"/>
       <c r="C368" s="10"/>
@@ -7109,14 +7494,15 @@
       <c r="E368" s="10"/>
       <c r="F368" s="10"/>
       <c r="G368" s="10"/>
-      <c r="H368" s="16"/>
+      <c r="H368" s="10"/>
       <c r="I368" s="16"/>
       <c r="J368" s="16"/>
       <c r="K368" s="16"/>
       <c r="L368" s="16"/>
       <c r="M368" s="16"/>
-    </row>
-    <row r="369" spans="1:13">
+      <c r="N368" s="16"/>
+    </row>
+    <row r="369" spans="1:14">
       <c r="A369" s="10"/>
       <c r="B369" s="16"/>
       <c r="C369" s="10"/>
@@ -7124,14 +7510,15 @@
       <c r="E369" s="10"/>
       <c r="F369" s="10"/>
       <c r="G369" s="10"/>
-      <c r="H369" s="16"/>
+      <c r="H369" s="10"/>
       <c r="I369" s="16"/>
       <c r="J369" s="16"/>
       <c r="K369" s="16"/>
       <c r="L369" s="16"/>
       <c r="M369" s="16"/>
-    </row>
-    <row r="370" spans="1:13">
+      <c r="N369" s="16"/>
+    </row>
+    <row r="370" spans="1:14">
       <c r="A370" s="10"/>
       <c r="B370" s="16"/>
       <c r="C370" s="10"/>
@@ -7139,14 +7526,15 @@
       <c r="E370" s="10"/>
       <c r="F370" s="10"/>
       <c r="G370" s="10"/>
-      <c r="H370" s="16"/>
+      <c r="H370" s="10"/>
       <c r="I370" s="16"/>
       <c r="J370" s="16"/>
       <c r="K370" s="16"/>
       <c r="L370" s="16"/>
       <c r="M370" s="16"/>
-    </row>
-    <row r="371" spans="1:13">
+      <c r="N370" s="16"/>
+    </row>
+    <row r="371" spans="1:14">
       <c r="A371" s="10"/>
       <c r="B371" s="16"/>
       <c r="C371" s="10"/>
@@ -7154,14 +7542,15 @@
       <c r="E371" s="10"/>
       <c r="F371" s="10"/>
       <c r="G371" s="10"/>
-      <c r="H371" s="16"/>
+      <c r="H371" s="10"/>
       <c r="I371" s="16"/>
       <c r="J371" s="16"/>
       <c r="K371" s="16"/>
       <c r="L371" s="16"/>
       <c r="M371" s="16"/>
-    </row>
-    <row r="372" spans="1:13">
+      <c r="N371" s="16"/>
+    </row>
+    <row r="372" spans="1:14">
       <c r="A372" s="10"/>
       <c r="B372" s="16"/>
       <c r="C372" s="10"/>
@@ -7169,14 +7558,15 @@
       <c r="E372" s="10"/>
       <c r="F372" s="10"/>
       <c r="G372" s="10"/>
-      <c r="H372" s="16"/>
+      <c r="H372" s="10"/>
       <c r="I372" s="16"/>
       <c r="J372" s="16"/>
       <c r="K372" s="16"/>
       <c r="L372" s="16"/>
       <c r="M372" s="16"/>
-    </row>
-    <row r="373" spans="1:13">
+      <c r="N372" s="16"/>
+    </row>
+    <row r="373" spans="1:14">
       <c r="A373" s="10"/>
       <c r="B373" s="16"/>
       <c r="C373" s="10"/>
@@ -7184,14 +7574,15 @@
       <c r="E373" s="10"/>
       <c r="F373" s="10"/>
       <c r="G373" s="10"/>
-      <c r="H373" s="16"/>
+      <c r="H373" s="10"/>
       <c r="I373" s="16"/>
       <c r="J373" s="16"/>
       <c r="K373" s="16"/>
       <c r="L373" s="16"/>
       <c r="M373" s="16"/>
-    </row>
-    <row r="374" spans="1:13">
+      <c r="N373" s="16"/>
+    </row>
+    <row r="374" spans="1:14">
       <c r="A374" s="10"/>
       <c r="B374" s="16"/>
       <c r="C374" s="10"/>
@@ -7199,14 +7590,15 @@
       <c r="E374" s="10"/>
       <c r="F374" s="10"/>
       <c r="G374" s="10"/>
-      <c r="H374" s="16"/>
+      <c r="H374" s="10"/>
       <c r="I374" s="16"/>
       <c r="J374" s="16"/>
       <c r="K374" s="16"/>
       <c r="L374" s="16"/>
       <c r="M374" s="16"/>
-    </row>
-    <row r="375" spans="1:13">
+      <c r="N374" s="16"/>
+    </row>
+    <row r="375" spans="1:14">
       <c r="A375" s="10"/>
       <c r="B375" s="16"/>
       <c r="C375" s="10"/>
@@ -7214,14 +7606,15 @@
       <c r="E375" s="10"/>
       <c r="F375" s="10"/>
       <c r="G375" s="10"/>
-      <c r="H375" s="16"/>
+      <c r="H375" s="10"/>
       <c r="I375" s="16"/>
       <c r="J375" s="16"/>
       <c r="K375" s="16"/>
       <c r="L375" s="16"/>
       <c r="M375" s="16"/>
-    </row>
-    <row r="376" spans="1:13">
+      <c r="N375" s="16"/>
+    </row>
+    <row r="376" spans="1:14">
       <c r="A376" s="10"/>
       <c r="B376" s="16"/>
       <c r="C376" s="10"/>
@@ -7229,14 +7622,15 @@
       <c r="E376" s="10"/>
       <c r="F376" s="10"/>
       <c r="G376" s="10"/>
-      <c r="H376" s="16"/>
+      <c r="H376" s="10"/>
       <c r="I376" s="16"/>
       <c r="J376" s="16"/>
       <c r="K376" s="16"/>
       <c r="L376" s="16"/>
       <c r="M376" s="16"/>
-    </row>
-    <row r="377" spans="1:13">
+      <c r="N376" s="16"/>
+    </row>
+    <row r="377" spans="1:14">
       <c r="A377" s="10"/>
       <c r="B377" s="16"/>
       <c r="C377" s="10"/>
@@ -7244,14 +7638,15 @@
       <c r="E377" s="10"/>
       <c r="F377" s="10"/>
       <c r="G377" s="10"/>
-      <c r="H377" s="16"/>
+      <c r="H377" s="10"/>
       <c r="I377" s="16"/>
       <c r="J377" s="16"/>
       <c r="K377" s="16"/>
       <c r="L377" s="16"/>
       <c r="M377" s="16"/>
-    </row>
-    <row r="378" spans="1:13">
+      <c r="N377" s="16"/>
+    </row>
+    <row r="378" spans="1:14">
       <c r="A378" s="10"/>
       <c r="B378" s="16"/>
       <c r="C378" s="10"/>
@@ -7259,14 +7654,15 @@
       <c r="E378" s="10"/>
       <c r="F378" s="10"/>
       <c r="G378" s="10"/>
-      <c r="H378" s="16"/>
+      <c r="H378" s="10"/>
       <c r="I378" s="16"/>
       <c r="J378" s="16"/>
       <c r="K378" s="16"/>
       <c r="L378" s="16"/>
       <c r="M378" s="16"/>
-    </row>
-    <row r="379" spans="1:13">
+      <c r="N378" s="16"/>
+    </row>
+    <row r="379" spans="1:14">
       <c r="A379" s="10"/>
       <c r="B379" s="16"/>
       <c r="C379" s="10"/>
@@ -7274,14 +7670,15 @@
       <c r="E379" s="10"/>
       <c r="F379" s="10"/>
       <c r="G379" s="10"/>
-      <c r="H379" s="16"/>
+      <c r="H379" s="10"/>
       <c r="I379" s="16"/>
       <c r="J379" s="16"/>
       <c r="K379" s="16"/>
       <c r="L379" s="16"/>
       <c r="M379" s="16"/>
-    </row>
-    <row r="380" spans="1:13">
+      <c r="N379" s="16"/>
+    </row>
+    <row r="380" spans="1:14">
       <c r="A380" s="10"/>
       <c r="B380" s="16"/>
       <c r="C380" s="10"/>
@@ -7289,14 +7686,15 @@
       <c r="E380" s="10"/>
       <c r="F380" s="10"/>
       <c r="G380" s="10"/>
-      <c r="H380" s="16"/>
+      <c r="H380" s="10"/>
       <c r="I380" s="16"/>
       <c r="J380" s="16"/>
       <c r="K380" s="16"/>
       <c r="L380" s="16"/>
       <c r="M380" s="16"/>
-    </row>
-    <row r="381" spans="1:13">
+      <c r="N380" s="16"/>
+    </row>
+    <row r="381" spans="1:14">
       <c r="A381" s="10"/>
       <c r="B381" s="16"/>
       <c r="C381" s="10"/>
@@ -7304,14 +7702,15 @@
       <c r="E381" s="10"/>
       <c r="F381" s="10"/>
       <c r="G381" s="10"/>
-      <c r="H381" s="16"/>
+      <c r="H381" s="10"/>
       <c r="I381" s="16"/>
       <c r="J381" s="16"/>
       <c r="K381" s="16"/>
       <c r="L381" s="16"/>
       <c r="M381" s="16"/>
-    </row>
-    <row r="382" spans="1:13">
+      <c r="N381" s="16"/>
+    </row>
+    <row r="382" spans="1:14">
       <c r="A382" s="10"/>
       <c r="B382" s="16"/>
       <c r="C382" s="10"/>
@@ -7319,14 +7718,15 @@
       <c r="E382" s="10"/>
       <c r="F382" s="10"/>
       <c r="G382" s="10"/>
-      <c r="H382" s="16"/>
+      <c r="H382" s="10"/>
       <c r="I382" s="16"/>
       <c r="J382" s="16"/>
       <c r="K382" s="16"/>
       <c r="L382" s="16"/>
       <c r="M382" s="16"/>
-    </row>
-    <row r="383" spans="1:13">
+      <c r="N382" s="16"/>
+    </row>
+    <row r="383" spans="1:14">
       <c r="A383" s="10"/>
       <c r="B383" s="16"/>
       <c r="C383" s="10"/>
@@ -7334,14 +7734,15 @@
       <c r="E383" s="10"/>
       <c r="F383" s="10"/>
       <c r="G383" s="10"/>
-      <c r="H383" s="16"/>
+      <c r="H383" s="10"/>
       <c r="I383" s="16"/>
       <c r="J383" s="16"/>
       <c r="K383" s="16"/>
       <c r="L383" s="16"/>
       <c r="M383" s="16"/>
-    </row>
-    <row r="384" spans="1:13">
+      <c r="N383" s="16"/>
+    </row>
+    <row r="384" spans="1:14">
       <c r="A384" s="10"/>
       <c r="B384" s="16"/>
       <c r="C384" s="10"/>
@@ -7349,14 +7750,15 @@
       <c r="E384" s="10"/>
       <c r="F384" s="10"/>
       <c r="G384" s="10"/>
-      <c r="H384" s="16"/>
+      <c r="H384" s="10"/>
       <c r="I384" s="16"/>
       <c r="J384" s="16"/>
       <c r="K384" s="16"/>
       <c r="L384" s="16"/>
       <c r="M384" s="16"/>
-    </row>
-    <row r="385" spans="1:13">
+      <c r="N384" s="16"/>
+    </row>
+    <row r="385" spans="1:14">
       <c r="A385" s="10"/>
       <c r="B385" s="16"/>
       <c r="C385" s="10"/>
@@ -7364,14 +7766,15 @@
       <c r="E385" s="10"/>
       <c r="F385" s="10"/>
       <c r="G385" s="10"/>
-      <c r="H385" s="16"/>
+      <c r="H385" s="10"/>
       <c r="I385" s="16"/>
       <c r="J385" s="16"/>
       <c r="K385" s="16"/>
       <c r="L385" s="16"/>
       <c r="M385" s="16"/>
-    </row>
-    <row r="386" spans="1:13">
+      <c r="N385" s="16"/>
+    </row>
+    <row r="386" spans="1:14">
       <c r="A386" s="10"/>
       <c r="B386" s="16"/>
       <c r="C386" s="10"/>
@@ -7379,14 +7782,15 @@
       <c r="E386" s="10"/>
       <c r="F386" s="10"/>
       <c r="G386" s="10"/>
-      <c r="H386" s="16"/>
+      <c r="H386" s="10"/>
       <c r="I386" s="16"/>
       <c r="J386" s="16"/>
       <c r="K386" s="16"/>
       <c r="L386" s="16"/>
       <c r="M386" s="16"/>
-    </row>
-    <row r="387" spans="1:13">
+      <c r="N386" s="16"/>
+    </row>
+    <row r="387" spans="1:14">
       <c r="A387" s="10"/>
       <c r="B387" s="16"/>
       <c r="C387" s="10"/>
@@ -7394,14 +7798,15 @@
       <c r="E387" s="10"/>
       <c r="F387" s="10"/>
       <c r="G387" s="10"/>
-      <c r="H387" s="16"/>
+      <c r="H387" s="10"/>
       <c r="I387" s="16"/>
       <c r="J387" s="16"/>
       <c r="K387" s="16"/>
       <c r="L387" s="16"/>
       <c r="M387" s="16"/>
-    </row>
-    <row r="388" spans="1:13">
+      <c r="N387" s="16"/>
+    </row>
+    <row r="388" spans="1:14">
       <c r="A388" s="10"/>
       <c r="B388" s="16"/>
       <c r="C388" s="10"/>
@@ -7409,14 +7814,15 @@
       <c r="E388" s="10"/>
       <c r="F388" s="10"/>
       <c r="G388" s="10"/>
-      <c r="H388" s="16"/>
+      <c r="H388" s="10"/>
       <c r="I388" s="16"/>
       <c r="J388" s="16"/>
       <c r="K388" s="16"/>
       <c r="L388" s="16"/>
       <c r="M388" s="16"/>
-    </row>
-    <row r="389" spans="1:13">
+      <c r="N388" s="16"/>
+    </row>
+    <row r="389" spans="1:14">
       <c r="A389" s="10"/>
       <c r="B389" s="16"/>
       <c r="C389" s="10"/>
@@ -7424,14 +7830,15 @@
       <c r="E389" s="10"/>
       <c r="F389" s="10"/>
       <c r="G389" s="10"/>
-      <c r="H389" s="16"/>
+      <c r="H389" s="10"/>
       <c r="I389" s="16"/>
       <c r="J389" s="16"/>
       <c r="K389" s="16"/>
       <c r="L389" s="16"/>
       <c r="M389" s="16"/>
-    </row>
-    <row r="390" spans="1:13">
+      <c r="N389" s="16"/>
+    </row>
+    <row r="390" spans="1:14">
       <c r="A390" s="10"/>
       <c r="B390" s="16"/>
       <c r="C390" s="10"/>
@@ -7439,14 +7846,15 @@
       <c r="E390" s="10"/>
       <c r="F390" s="10"/>
       <c r="G390" s="10"/>
-      <c r="H390" s="16"/>
+      <c r="H390" s="10"/>
       <c r="I390" s="16"/>
       <c r="J390" s="16"/>
       <c r="K390" s="16"/>
       <c r="L390" s="16"/>
       <c r="M390" s="16"/>
-    </row>
-    <row r="391" spans="1:13">
+      <c r="N390" s="16"/>
+    </row>
+    <row r="391" spans="1:14">
       <c r="A391" s="10"/>
       <c r="B391" s="16"/>
       <c r="C391" s="10"/>
@@ -7454,14 +7862,15 @@
       <c r="E391" s="10"/>
       <c r="F391" s="10"/>
       <c r="G391" s="10"/>
-      <c r="H391" s="16"/>
+      <c r="H391" s="10"/>
       <c r="I391" s="16"/>
       <c r="J391" s="16"/>
       <c r="K391" s="16"/>
       <c r="L391" s="16"/>
       <c r="M391" s="16"/>
-    </row>
-    <row r="392" spans="1:13">
+      <c r="N391" s="16"/>
+    </row>
+    <row r="392" spans="1:14">
       <c r="A392" s="10"/>
       <c r="B392" s="16"/>
       <c r="C392" s="10"/>
@@ -7469,14 +7878,15 @@
       <c r="E392" s="10"/>
       <c r="F392" s="10"/>
       <c r="G392" s="10"/>
-      <c r="H392" s="16"/>
+      <c r="H392" s="10"/>
       <c r="I392" s="16"/>
       <c r="J392" s="16"/>
       <c r="K392" s="16"/>
       <c r="L392" s="16"/>
       <c r="M392" s="16"/>
-    </row>
-    <row r="393" spans="1:13">
+      <c r="N392" s="16"/>
+    </row>
+    <row r="393" spans="1:14">
       <c r="A393" s="10"/>
       <c r="B393" s="16"/>
       <c r="C393" s="10"/>
@@ -7484,14 +7894,15 @@
       <c r="E393" s="10"/>
       <c r="F393" s="10"/>
       <c r="G393" s="10"/>
-      <c r="H393" s="16"/>
+      <c r="H393" s="10"/>
       <c r="I393" s="16"/>
       <c r="J393" s="16"/>
       <c r="K393" s="16"/>
       <c r="L393" s="16"/>
       <c r="M393" s="16"/>
-    </row>
-    <row r="394" spans="1:13">
+      <c r="N393" s="16"/>
+    </row>
+    <row r="394" spans="1:14">
       <c r="A394" s="10"/>
       <c r="B394" s="16"/>
       <c r="C394" s="10"/>
@@ -7499,14 +7910,15 @@
       <c r="E394" s="10"/>
       <c r="F394" s="10"/>
       <c r="G394" s="10"/>
-      <c r="H394" s="16"/>
+      <c r="H394" s="10"/>
       <c r="I394" s="16"/>
       <c r="J394" s="16"/>
       <c r="K394" s="16"/>
       <c r="L394" s="16"/>
       <c r="M394" s="16"/>
-    </row>
-    <row r="395" spans="1:13">
+      <c r="N394" s="16"/>
+    </row>
+    <row r="395" spans="1:14">
       <c r="A395" s="10"/>
       <c r="B395" s="16"/>
       <c r="C395" s="10"/>
@@ -7514,14 +7926,15 @@
       <c r="E395" s="10"/>
       <c r="F395" s="10"/>
       <c r="G395" s="10"/>
-      <c r="H395" s="16"/>
+      <c r="H395" s="10"/>
       <c r="I395" s="16"/>
       <c r="J395" s="16"/>
       <c r="K395" s="16"/>
       <c r="L395" s="16"/>
       <c r="M395" s="16"/>
-    </row>
-    <row r="396" spans="1:13">
+      <c r="N395" s="16"/>
+    </row>
+    <row r="396" spans="1:14">
       <c r="A396" s="10"/>
       <c r="B396" s="16"/>
       <c r="C396" s="10"/>
@@ -7529,14 +7942,15 @@
       <c r="E396" s="10"/>
       <c r="F396" s="10"/>
       <c r="G396" s="10"/>
-      <c r="H396" s="16"/>
+      <c r="H396" s="10"/>
       <c r="I396" s="16"/>
       <c r="J396" s="16"/>
       <c r="K396" s="16"/>
       <c r="L396" s="16"/>
       <c r="M396" s="16"/>
-    </row>
-    <row r="397" spans="1:13">
+      <c r="N396" s="16"/>
+    </row>
+    <row r="397" spans="1:14">
       <c r="A397" s="10"/>
       <c r="B397" s="16"/>
       <c r="C397" s="10"/>
@@ -7544,14 +7958,15 @@
       <c r="E397" s="10"/>
       <c r="F397" s="10"/>
       <c r="G397" s="10"/>
-      <c r="H397" s="16"/>
+      <c r="H397" s="10"/>
       <c r="I397" s="16"/>
       <c r="J397" s="16"/>
       <c r="K397" s="16"/>
       <c r="L397" s="16"/>
       <c r="M397" s="16"/>
-    </row>
-    <row r="398" spans="1:13">
+      <c r="N397" s="16"/>
+    </row>
+    <row r="398" spans="1:14">
       <c r="A398" s="10"/>
       <c r="B398" s="16"/>
       <c r="C398" s="10"/>
@@ -7559,14 +7974,15 @@
       <c r="E398" s="10"/>
       <c r="F398" s="10"/>
       <c r="G398" s="10"/>
-      <c r="H398" s="16"/>
+      <c r="H398" s="10"/>
       <c r="I398" s="16"/>
       <c r="J398" s="16"/>
       <c r="K398" s="16"/>
       <c r="L398" s="16"/>
       <c r="M398" s="16"/>
-    </row>
-    <row r="399" spans="1:13">
+      <c r="N398" s="16"/>
+    </row>
+    <row r="399" spans="1:14">
       <c r="A399" s="10"/>
       <c r="B399" s="16"/>
       <c r="C399" s="10"/>
@@ -7574,14 +7990,15 @@
       <c r="E399" s="10"/>
       <c r="F399" s="10"/>
       <c r="G399" s="10"/>
-      <c r="H399" s="16"/>
+      <c r="H399" s="10"/>
       <c r="I399" s="16"/>
       <c r="J399" s="16"/>
       <c r="K399" s="16"/>
       <c r="L399" s="16"/>
       <c r="M399" s="16"/>
-    </row>
-    <row r="400" spans="1:13">
+      <c r="N399" s="16"/>
+    </row>
+    <row r="400" spans="1:14">
       <c r="A400" s="10"/>
       <c r="B400" s="16"/>
       <c r="C400" s="10"/>
@@ -7589,14 +8006,15 @@
       <c r="E400" s="10"/>
       <c r="F400" s="10"/>
       <c r="G400" s="10"/>
-      <c r="H400" s="16"/>
+      <c r="H400" s="10"/>
       <c r="I400" s="16"/>
       <c r="J400" s="16"/>
       <c r="K400" s="16"/>
       <c r="L400" s="16"/>
       <c r="M400" s="16"/>
-    </row>
-    <row r="401" spans="1:13">
+      <c r="N400" s="16"/>
+    </row>
+    <row r="401" spans="1:14">
       <c r="A401" s="10"/>
       <c r="B401" s="16"/>
       <c r="C401" s="10"/>
@@ -7604,14 +8022,15 @@
       <c r="E401" s="10"/>
       <c r="F401" s="10"/>
       <c r="G401" s="10"/>
-      <c r="H401" s="16"/>
+      <c r="H401" s="10"/>
       <c r="I401" s="16"/>
       <c r="J401" s="16"/>
       <c r="K401" s="16"/>
       <c r="L401" s="16"/>
       <c r="M401" s="16"/>
-    </row>
-    <row r="402" spans="1:13">
+      <c r="N401" s="16"/>
+    </row>
+    <row r="402" spans="1:14">
       <c r="A402" s="10"/>
       <c r="B402" s="16"/>
       <c r="C402" s="10"/>
@@ -7619,14 +8038,15 @@
       <c r="E402" s="10"/>
       <c r="F402" s="10"/>
       <c r="G402" s="10"/>
-      <c r="H402" s="16"/>
+      <c r="H402" s="10"/>
       <c r="I402" s="16"/>
       <c r="J402" s="16"/>
       <c r="K402" s="16"/>
       <c r="L402" s="16"/>
       <c r="M402" s="16"/>
-    </row>
-    <row r="403" spans="1:13">
+      <c r="N402" s="16"/>
+    </row>
+    <row r="403" spans="1:14">
       <c r="A403" s="10"/>
       <c r="B403" s="16"/>
       <c r="C403" s="10"/>
@@ -7634,14 +8054,15 @@
       <c r="E403" s="10"/>
       <c r="F403" s="10"/>
       <c r="G403" s="10"/>
-      <c r="H403" s="16"/>
+      <c r="H403" s="10"/>
       <c r="I403" s="16"/>
       <c r="J403" s="16"/>
       <c r="K403" s="16"/>
       <c r="L403" s="16"/>
       <c r="M403" s="16"/>
-    </row>
-    <row r="404" spans="1:13">
+      <c r="N403" s="16"/>
+    </row>
+    <row r="404" spans="1:14">
       <c r="A404" s="10"/>
       <c r="B404" s="16"/>
       <c r="C404" s="10"/>
@@ -7649,14 +8070,15 @@
       <c r="E404" s="10"/>
       <c r="F404" s="10"/>
       <c r="G404" s="10"/>
-      <c r="H404" s="16"/>
+      <c r="H404" s="10"/>
       <c r="I404" s="16"/>
       <c r="J404" s="16"/>
       <c r="K404" s="16"/>
       <c r="L404" s="16"/>
       <c r="M404" s="16"/>
-    </row>
-    <row r="405" spans="1:13">
+      <c r="N404" s="16"/>
+    </row>
+    <row r="405" spans="1:14">
       <c r="A405" s="10"/>
       <c r="B405" s="16"/>
       <c r="C405" s="10"/>
@@ -7664,14 +8086,15 @@
       <c r="E405" s="10"/>
       <c r="F405" s="10"/>
       <c r="G405" s="10"/>
-      <c r="H405" s="16"/>
+      <c r="H405" s="10"/>
       <c r="I405" s="16"/>
       <c r="J405" s="16"/>
       <c r="K405" s="16"/>
       <c r="L405" s="16"/>
       <c r="M405" s="16"/>
-    </row>
-    <row r="406" spans="1:13">
+      <c r="N405" s="16"/>
+    </row>
+    <row r="406" spans="1:14">
       <c r="A406" s="10"/>
       <c r="B406" s="16"/>
       <c r="C406" s="10"/>
@@ -7679,14 +8102,15 @@
       <c r="E406" s="10"/>
       <c r="F406" s="10"/>
       <c r="G406" s="10"/>
-      <c r="H406" s="16"/>
+      <c r="H406" s="10"/>
       <c r="I406" s="16"/>
       <c r="J406" s="16"/>
       <c r="K406" s="16"/>
       <c r="L406" s="16"/>
       <c r="M406" s="16"/>
-    </row>
-    <row r="407" spans="1:13">
+      <c r="N406" s="16"/>
+    </row>
+    <row r="407" spans="1:14">
       <c r="A407" s="10"/>
       <c r="B407" s="16"/>
       <c r="C407" s="10"/>
@@ -7694,14 +8118,15 @@
       <c r="E407" s="10"/>
       <c r="F407" s="10"/>
       <c r="G407" s="10"/>
-      <c r="H407" s="16"/>
+      <c r="H407" s="10"/>
       <c r="I407" s="16"/>
       <c r="J407" s="16"/>
       <c r="K407" s="16"/>
       <c r="L407" s="16"/>
       <c r="M407" s="16"/>
-    </row>
-    <row r="408" spans="1:13">
+      <c r="N407" s="16"/>
+    </row>
+    <row r="408" spans="1:14">
       <c r="A408" s="10"/>
       <c r="B408" s="16"/>
       <c r="C408" s="10"/>
@@ -7709,14 +8134,15 @@
       <c r="E408" s="10"/>
       <c r="F408" s="10"/>
       <c r="G408" s="10"/>
-      <c r="H408" s="16"/>
+      <c r="H408" s="10"/>
       <c r="I408" s="16"/>
       <c r="J408" s="16"/>
       <c r="K408" s="16"/>
       <c r="L408" s="16"/>
       <c r="M408" s="16"/>
-    </row>
-    <row r="409" spans="1:13">
+      <c r="N408" s="16"/>
+    </row>
+    <row r="409" spans="1:14">
       <c r="A409" s="10"/>
       <c r="B409" s="16"/>
       <c r="C409" s="10"/>
@@ -7724,14 +8150,15 @@
       <c r="E409" s="10"/>
       <c r="F409" s="10"/>
       <c r="G409" s="10"/>
-      <c r="H409" s="16"/>
+      <c r="H409" s="10"/>
       <c r="I409" s="16"/>
       <c r="J409" s="16"/>
       <c r="K409" s="16"/>
       <c r="L409" s="16"/>
       <c r="M409" s="16"/>
-    </row>
-    <row r="410" spans="1:13">
+      <c r="N409" s="16"/>
+    </row>
+    <row r="410" spans="1:14">
       <c r="A410" s="10"/>
       <c r="B410" s="16"/>
       <c r="C410" s="10"/>
@@ -7739,14 +8166,15 @@
       <c r="E410" s="10"/>
       <c r="F410" s="10"/>
       <c r="G410" s="10"/>
-      <c r="H410" s="16"/>
+      <c r="H410" s="10"/>
       <c r="I410" s="16"/>
       <c r="J410" s="16"/>
       <c r="K410" s="16"/>
       <c r="L410" s="16"/>
       <c r="M410" s="16"/>
-    </row>
-    <row r="411" spans="1:13">
+      <c r="N410" s="16"/>
+    </row>
+    <row r="411" spans="1:14">
       <c r="A411" s="10"/>
       <c r="B411" s="16"/>
       <c r="C411" s="10"/>
@@ -7754,14 +8182,15 @@
       <c r="E411" s="10"/>
       <c r="F411" s="10"/>
       <c r="G411" s="10"/>
-      <c r="H411" s="16"/>
+      <c r="H411" s="10"/>
       <c r="I411" s="16"/>
       <c r="J411" s="16"/>
       <c r="K411" s="16"/>
       <c r="L411" s="16"/>
       <c r="M411" s="16"/>
-    </row>
-    <row r="412" spans="1:13">
+      <c r="N411" s="16"/>
+    </row>
+    <row r="412" spans="1:14">
       <c r="A412" s="10"/>
       <c r="B412" s="16"/>
       <c r="C412" s="10"/>
@@ -7769,14 +8198,15 @@
       <c r="E412" s="10"/>
       <c r="F412" s="10"/>
       <c r="G412" s="10"/>
-      <c r="H412" s="16"/>
+      <c r="H412" s="10"/>
       <c r="I412" s="16"/>
       <c r="J412" s="16"/>
       <c r="K412" s="16"/>
       <c r="L412" s="16"/>
       <c r="M412" s="16"/>
-    </row>
-    <row r="413" spans="1:13">
+      <c r="N412" s="16"/>
+    </row>
+    <row r="413" spans="1:14">
       <c r="A413" s="10"/>
       <c r="B413" s="16"/>
       <c r="C413" s="10"/>
@@ -7784,14 +8214,15 @@
       <c r="E413" s="10"/>
       <c r="F413" s="10"/>
       <c r="G413" s="10"/>
-      <c r="H413" s="16"/>
+      <c r="H413" s="10"/>
       <c r="I413" s="16"/>
       <c r="J413" s="16"/>
       <c r="K413" s="16"/>
       <c r="L413" s="16"/>
       <c r="M413" s="16"/>
-    </row>
-    <row r="414" spans="1:13">
+      <c r="N413" s="16"/>
+    </row>
+    <row r="414" spans="1:14">
       <c r="A414" s="10"/>
       <c r="B414" s="16"/>
       <c r="C414" s="10"/>
@@ -7799,14 +8230,15 @@
       <c r="E414" s="10"/>
       <c r="F414" s="10"/>
       <c r="G414" s="10"/>
-      <c r="H414" s="16"/>
+      <c r="H414" s="10"/>
       <c r="I414" s="16"/>
       <c r="J414" s="16"/>
       <c r="K414" s="16"/>
       <c r="L414" s="16"/>
       <c r="M414" s="16"/>
-    </row>
-    <row r="415" spans="1:13">
+      <c r="N414" s="16"/>
+    </row>
+    <row r="415" spans="1:14">
       <c r="A415" s="10"/>
       <c r="B415" s="16"/>
       <c r="C415" s="10"/>
@@ -7814,14 +8246,15 @@
       <c r="E415" s="10"/>
       <c r="F415" s="10"/>
       <c r="G415" s="10"/>
-      <c r="H415" s="16"/>
+      <c r="H415" s="10"/>
       <c r="I415" s="16"/>
       <c r="J415" s="16"/>
       <c r="K415" s="16"/>
       <c r="L415" s="16"/>
       <c r="M415" s="16"/>
-    </row>
-    <row r="416" spans="1:13">
+      <c r="N415" s="16"/>
+    </row>
+    <row r="416" spans="1:14">
       <c r="A416" s="10"/>
       <c r="B416" s="16"/>
       <c r="C416" s="10"/>
@@ -7829,14 +8262,15 @@
       <c r="E416" s="10"/>
       <c r="F416" s="10"/>
       <c r="G416" s="10"/>
-      <c r="H416" s="16"/>
+      <c r="H416" s="10"/>
       <c r="I416" s="16"/>
       <c r="J416" s="16"/>
       <c r="K416" s="16"/>
       <c r="L416" s="16"/>
       <c r="M416" s="16"/>
-    </row>
-    <row r="417" spans="1:13">
+      <c r="N416" s="16"/>
+    </row>
+    <row r="417" spans="1:14">
       <c r="A417" s="10"/>
       <c r="B417" s="16"/>
       <c r="C417" s="10"/>
@@ -7844,14 +8278,15 @@
       <c r="E417" s="10"/>
       <c r="F417" s="10"/>
       <c r="G417" s="10"/>
-      <c r="H417" s="16"/>
+      <c r="H417" s="10"/>
       <c r="I417" s="16"/>
       <c r="J417" s="16"/>
       <c r="K417" s="16"/>
       <c r="L417" s="16"/>
       <c r="M417" s="16"/>
-    </row>
-    <row r="418" spans="1:13">
+      <c r="N417" s="16"/>
+    </row>
+    <row r="418" spans="1:14">
       <c r="A418" s="10"/>
       <c r="B418" s="16"/>
       <c r="C418" s="10"/>
@@ -7859,14 +8294,15 @@
       <c r="E418" s="10"/>
       <c r="F418" s="10"/>
       <c r="G418" s="10"/>
-      <c r="H418" s="16"/>
+      <c r="H418" s="10"/>
       <c r="I418" s="16"/>
       <c r="J418" s="16"/>
       <c r="K418" s="16"/>
       <c r="L418" s="16"/>
       <c r="M418" s="16"/>
-    </row>
-    <row r="419" spans="1:13">
+      <c r="N418" s="16"/>
+    </row>
+    <row r="419" spans="1:14">
       <c r="A419" s="10"/>
       <c r="B419" s="16"/>
       <c r="C419" s="10"/>
@@ -7874,14 +8310,15 @@
       <c r="E419" s="10"/>
       <c r="F419" s="10"/>
       <c r="G419" s="10"/>
-      <c r="H419" s="16"/>
+      <c r="H419" s="10"/>
       <c r="I419" s="16"/>
       <c r="J419" s="16"/>
       <c r="K419" s="16"/>
       <c r="L419" s="16"/>
       <c r="M419" s="16"/>
-    </row>
-    <row r="420" spans="1:13">
+      <c r="N419" s="16"/>
+    </row>
+    <row r="420" spans="1:14">
       <c r="A420" s="10"/>
       <c r="B420" s="16"/>
       <c r="C420" s="10"/>
@@ -7889,14 +8326,15 @@
       <c r="E420" s="10"/>
       <c r="F420" s="10"/>
       <c r="G420" s="10"/>
-      <c r="H420" s="16"/>
+      <c r="H420" s="10"/>
       <c r="I420" s="16"/>
       <c r="J420" s="16"/>
       <c r="K420" s="16"/>
       <c r="L420" s="16"/>
       <c r="M420" s="16"/>
-    </row>
-    <row r="421" spans="1:13">
+      <c r="N420" s="16"/>
+    </row>
+    <row r="421" spans="1:14">
       <c r="A421" s="10"/>
       <c r="B421" s="16"/>
       <c r="C421" s="10"/>
@@ -7904,14 +8342,15 @@
       <c r="E421" s="10"/>
       <c r="F421" s="10"/>
       <c r="G421" s="10"/>
-      <c r="H421" s="16"/>
+      <c r="H421" s="10"/>
       <c r="I421" s="16"/>
       <c r="J421" s="16"/>
       <c r="K421" s="16"/>
       <c r="L421" s="16"/>
       <c r="M421" s="16"/>
-    </row>
-    <row r="422" spans="1:13">
+      <c r="N421" s="16"/>
+    </row>
+    <row r="422" spans="1:14">
       <c r="A422" s="10"/>
       <c r="B422" s="16"/>
       <c r="C422" s="10"/>
@@ -7919,14 +8358,15 @@
       <c r="E422" s="10"/>
       <c r="F422" s="10"/>
       <c r="G422" s="10"/>
-      <c r="H422" s="16"/>
+      <c r="H422" s="10"/>
       <c r="I422" s="16"/>
       <c r="J422" s="16"/>
       <c r="K422" s="16"/>
       <c r="L422" s="16"/>
       <c r="M422" s="16"/>
-    </row>
-    <row r="423" spans="1:13">
+      <c r="N422" s="16"/>
+    </row>
+    <row r="423" spans="1:14">
       <c r="A423" s="10"/>
       <c r="B423" s="16"/>
       <c r="C423" s="10"/>
@@ -7934,14 +8374,15 @@
       <c r="E423" s="10"/>
       <c r="F423" s="10"/>
       <c r="G423" s="10"/>
-      <c r="H423" s="16"/>
+      <c r="H423" s="10"/>
       <c r="I423" s="16"/>
       <c r="J423" s="16"/>
       <c r="K423" s="16"/>
       <c r="L423" s="16"/>
       <c r="M423" s="16"/>
-    </row>
-    <row r="424" spans="1:13">
+      <c r="N423" s="16"/>
+    </row>
+    <row r="424" spans="1:14">
       <c r="A424" s="10"/>
       <c r="B424" s="16"/>
       <c r="C424" s="10"/>
@@ -7949,14 +8390,15 @@
       <c r="E424" s="10"/>
       <c r="F424" s="10"/>
       <c r="G424" s="10"/>
-      <c r="H424" s="16"/>
+      <c r="H424" s="10"/>
       <c r="I424" s="16"/>
       <c r="J424" s="16"/>
       <c r="K424" s="16"/>
       <c r="L424" s="16"/>
       <c r="M424" s="16"/>
-    </row>
-    <row r="425" spans="1:13">
+      <c r="N424" s="16"/>
+    </row>
+    <row r="425" spans="1:14">
       <c r="A425" s="10"/>
       <c r="B425" s="16"/>
       <c r="C425" s="10"/>
@@ -7964,14 +8406,15 @@
       <c r="E425" s="10"/>
       <c r="F425" s="10"/>
       <c r="G425" s="10"/>
-      <c r="H425" s="16"/>
+      <c r="H425" s="10"/>
       <c r="I425" s="16"/>
       <c r="J425" s="16"/>
       <c r="K425" s="16"/>
       <c r="L425" s="16"/>
       <c r="M425" s="16"/>
-    </row>
-    <row r="426" spans="1:13">
+      <c r="N425" s="16"/>
+    </row>
+    <row r="426" spans="1:14">
       <c r="A426" s="10"/>
       <c r="B426" s="16"/>
       <c r="C426" s="10"/>
@@ -7979,14 +8422,15 @@
       <c r="E426" s="10"/>
       <c r="F426" s="10"/>
       <c r="G426" s="10"/>
-      <c r="H426" s="16"/>
+      <c r="H426" s="10"/>
       <c r="I426" s="16"/>
       <c r="J426" s="16"/>
       <c r="K426" s="16"/>
       <c r="L426" s="16"/>
       <c r="M426" s="16"/>
-    </row>
-    <row r="427" spans="1:13">
+      <c r="N426" s="16"/>
+    </row>
+    <row r="427" spans="1:14">
       <c r="A427" s="10"/>
       <c r="B427" s="16"/>
       <c r="C427" s="10"/>
@@ -7994,14 +8438,15 @@
       <c r="E427" s="10"/>
       <c r="F427" s="10"/>
       <c r="G427" s="10"/>
-      <c r="H427" s="16"/>
+      <c r="H427" s="10"/>
       <c r="I427" s="16"/>
       <c r="J427" s="16"/>
       <c r="K427" s="16"/>
       <c r="L427" s="16"/>
       <c r="M427" s="16"/>
-    </row>
-    <row r="428" spans="1:13">
+      <c r="N427" s="16"/>
+    </row>
+    <row r="428" spans="1:14">
       <c r="A428" s="10"/>
       <c r="B428" s="16"/>
       <c r="C428" s="10"/>
@@ -8009,14 +8454,15 @@
       <c r="E428" s="10"/>
       <c r="F428" s="10"/>
       <c r="G428" s="10"/>
-      <c r="H428" s="16"/>
+      <c r="H428" s="10"/>
       <c r="I428" s="16"/>
       <c r="J428" s="16"/>
       <c r="K428" s="16"/>
       <c r="L428" s="16"/>
       <c r="M428" s="16"/>
-    </row>
-    <row r="429" spans="1:13">
+      <c r="N428" s="16"/>
+    </row>
+    <row r="429" spans="1:14">
       <c r="A429" s="10"/>
       <c r="B429" s="16"/>
       <c r="C429" s="10"/>
@@ -8024,14 +8470,15 @@
       <c r="E429" s="10"/>
       <c r="F429" s="10"/>
       <c r="G429" s="10"/>
-      <c r="H429" s="16"/>
+      <c r="H429" s="10"/>
       <c r="I429" s="16"/>
       <c r="J429" s="16"/>
       <c r="K429" s="16"/>
       <c r="L429" s="16"/>
       <c r="M429" s="16"/>
-    </row>
-    <row r="430" spans="1:13">
+      <c r="N429" s="16"/>
+    </row>
+    <row r="430" spans="1:14">
       <c r="A430" s="10"/>
       <c r="B430" s="16"/>
       <c r="C430" s="10"/>
@@ -8039,14 +8486,15 @@
       <c r="E430" s="10"/>
       <c r="F430" s="10"/>
       <c r="G430" s="10"/>
-      <c r="H430" s="16"/>
+      <c r="H430" s="10"/>
       <c r="I430" s="16"/>
       <c r="J430" s="16"/>
       <c r="K430" s="16"/>
       <c r="L430" s="16"/>
       <c r="M430" s="16"/>
-    </row>
-    <row r="431" spans="1:13">
+      <c r="N430" s="16"/>
+    </row>
+    <row r="431" spans="1:14">
       <c r="A431" s="10"/>
       <c r="B431" s="16"/>
       <c r="C431" s="10"/>
@@ -8054,14 +8502,15 @@
       <c r="E431" s="10"/>
       <c r="F431" s="10"/>
       <c r="G431" s="10"/>
-      <c r="H431" s="16"/>
+      <c r="H431" s="10"/>
       <c r="I431" s="16"/>
       <c r="J431" s="16"/>
       <c r="K431" s="16"/>
       <c r="L431" s="16"/>
       <c r="M431" s="16"/>
-    </row>
-    <row r="432" spans="1:13">
+      <c r="N431" s="16"/>
+    </row>
+    <row r="432" spans="1:14">
       <c r="A432" s="10"/>
       <c r="B432" s="16"/>
       <c r="C432" s="10"/>
@@ -8069,14 +8518,15 @@
       <c r="E432" s="10"/>
       <c r="F432" s="10"/>
       <c r="G432" s="10"/>
-      <c r="H432" s="16"/>
+      <c r="H432" s="10"/>
       <c r="I432" s="16"/>
       <c r="J432" s="16"/>
       <c r="K432" s="16"/>
       <c r="L432" s="16"/>
       <c r="M432" s="16"/>
-    </row>
-    <row r="433" spans="1:13">
+      <c r="N432" s="16"/>
+    </row>
+    <row r="433" spans="1:14">
       <c r="A433" s="10"/>
       <c r="B433" s="16"/>
       <c r="C433" s="10"/>
@@ -8084,14 +8534,15 @@
       <c r="E433" s="10"/>
       <c r="F433" s="10"/>
       <c r="G433" s="10"/>
-      <c r="H433" s="16"/>
+      <c r="H433" s="10"/>
       <c r="I433" s="16"/>
       <c r="J433" s="16"/>
       <c r="K433" s="16"/>
       <c r="L433" s="16"/>
       <c r="M433" s="16"/>
-    </row>
-    <row r="434" spans="1:13">
+      <c r="N433" s="16"/>
+    </row>
+    <row r="434" spans="1:14">
       <c r="A434" s="10"/>
       <c r="B434" s="16"/>
       <c r="C434" s="10"/>
@@ -8099,14 +8550,15 @@
       <c r="E434" s="10"/>
       <c r="F434" s="10"/>
       <c r="G434" s="10"/>
-      <c r="H434" s="16"/>
+      <c r="H434" s="10"/>
       <c r="I434" s="16"/>
       <c r="J434" s="16"/>
       <c r="K434" s="16"/>
       <c r="L434" s="16"/>
       <c r="M434" s="16"/>
-    </row>
-    <row r="435" spans="1:13">
+      <c r="N434" s="16"/>
+    </row>
+    <row r="435" spans="1:14">
       <c r="A435" s="10"/>
       <c r="B435" s="16"/>
       <c r="C435" s="10"/>
@@ -8114,14 +8566,15 @@
       <c r="E435" s="10"/>
       <c r="F435" s="10"/>
       <c r="G435" s="10"/>
-      <c r="H435" s="16"/>
+      <c r="H435" s="10"/>
       <c r="I435" s="16"/>
       <c r="J435" s="16"/>
       <c r="K435" s="16"/>
       <c r="L435" s="16"/>
       <c r="M435" s="16"/>
-    </row>
-    <row r="436" spans="1:13">
+      <c r="N435" s="16"/>
+    </row>
+    <row r="436" spans="1:14">
       <c r="A436" s="10"/>
       <c r="B436" s="16"/>
       <c r="C436" s="10"/>
@@ -8129,14 +8582,15 @@
       <c r="E436" s="10"/>
       <c r="F436" s="10"/>
       <c r="G436" s="10"/>
-      <c r="H436" s="16"/>
+      <c r="H436" s="10"/>
       <c r="I436" s="16"/>
       <c r="J436" s="16"/>
       <c r="K436" s="16"/>
       <c r="L436" s="16"/>
       <c r="M436" s="16"/>
-    </row>
-    <row r="437" spans="1:13">
+      <c r="N436" s="16"/>
+    </row>
+    <row r="437" spans="1:14">
       <c r="A437" s="10"/>
       <c r="B437" s="16"/>
       <c r="C437" s="10"/>
@@ -8144,14 +8598,15 @@
       <c r="E437" s="10"/>
       <c r="F437" s="10"/>
       <c r="G437" s="10"/>
-      <c r="H437" s="16"/>
+      <c r="H437" s="10"/>
       <c r="I437" s="16"/>
       <c r="J437" s="16"/>
       <c r="K437" s="16"/>
       <c r="L437" s="16"/>
       <c r="M437" s="16"/>
-    </row>
-    <row r="438" spans="1:13">
+      <c r="N437" s="16"/>
+    </row>
+    <row r="438" spans="1:14">
       <c r="A438" s="10"/>
       <c r="B438" s="16"/>
       <c r="C438" s="10"/>
@@ -8159,14 +8614,15 @@
       <c r="E438" s="10"/>
       <c r="F438" s="10"/>
       <c r="G438" s="10"/>
-      <c r="H438" s="16"/>
+      <c r="H438" s="10"/>
       <c r="I438" s="16"/>
       <c r="J438" s="16"/>
       <c r="K438" s="16"/>
       <c r="L438" s="16"/>
       <c r="M438" s="16"/>
-    </row>
-    <row r="439" spans="1:13">
+      <c r="N438" s="16"/>
+    </row>
+    <row r="439" spans="1:14">
       <c r="A439" s="10"/>
       <c r="B439" s="16"/>
       <c r="C439" s="10"/>
@@ -8174,14 +8630,15 @@
       <c r="E439" s="10"/>
       <c r="F439" s="10"/>
       <c r="G439" s="10"/>
-      <c r="H439" s="16"/>
+      <c r="H439" s="10"/>
       <c r="I439" s="16"/>
       <c r="J439" s="16"/>
       <c r="K439" s="16"/>
       <c r="L439" s="16"/>
       <c r="M439" s="16"/>
-    </row>
-    <row r="440" spans="1:13">
+      <c r="N439" s="16"/>
+    </row>
+    <row r="440" spans="1:14">
       <c r="A440" s="10"/>
       <c r="B440" s="16"/>
       <c r="C440" s="10"/>
@@ -8189,14 +8646,15 @@
       <c r="E440" s="10"/>
       <c r="F440" s="10"/>
       <c r="G440" s="10"/>
-      <c r="H440" s="16"/>
+      <c r="H440" s="10"/>
       <c r="I440" s="16"/>
       <c r="J440" s="16"/>
       <c r="K440" s="16"/>
       <c r="L440" s="16"/>
       <c r="M440" s="16"/>
-    </row>
-    <row r="441" spans="1:13">
+      <c r="N440" s="16"/>
+    </row>
+    <row r="441" spans="1:14">
       <c r="A441" s="10"/>
       <c r="B441" s="16"/>
       <c r="C441" s="10"/>
@@ -8204,14 +8662,15 @@
       <c r="E441" s="10"/>
       <c r="F441" s="10"/>
       <c r="G441" s="10"/>
-      <c r="H441" s="16"/>
+      <c r="H441" s="10"/>
       <c r="I441" s="16"/>
       <c r="J441" s="16"/>
       <c r="K441" s="16"/>
       <c r="L441" s="16"/>
       <c r="M441" s="16"/>
-    </row>
-    <row r="442" spans="1:13">
+      <c r="N441" s="16"/>
+    </row>
+    <row r="442" spans="1:14">
       <c r="A442" s="10"/>
       <c r="B442" s="16"/>
       <c r="C442" s="10"/>
@@ -8219,14 +8678,15 @@
       <c r="E442" s="10"/>
       <c r="F442" s="10"/>
       <c r="G442" s="10"/>
-      <c r="H442" s="16"/>
+      <c r="H442" s="10"/>
       <c r="I442" s="16"/>
       <c r="J442" s="16"/>
       <c r="K442" s="16"/>
       <c r="L442" s="16"/>
       <c r="M442" s="16"/>
-    </row>
-    <row r="443" spans="1:13">
+      <c r="N442" s="16"/>
+    </row>
+    <row r="443" spans="1:14">
       <c r="A443" s="10"/>
       <c r="B443" s="16"/>
       <c r="C443" s="10"/>
@@ -8234,14 +8694,15 @@
       <c r="E443" s="10"/>
       <c r="F443" s="10"/>
       <c r="G443" s="10"/>
-      <c r="H443" s="16"/>
+      <c r="H443" s="10"/>
       <c r="I443" s="16"/>
       <c r="J443" s="16"/>
       <c r="K443" s="16"/>
       <c r="L443" s="16"/>
       <c r="M443" s="16"/>
-    </row>
-    <row r="444" spans="1:13">
+      <c r="N443" s="16"/>
+    </row>
+    <row r="444" spans="1:14">
       <c r="A444" s="10"/>
       <c r="B444" s="16"/>
       <c r="C444" s="10"/>
@@ -8249,14 +8710,15 @@
       <c r="E444" s="10"/>
       <c r="F444" s="10"/>
       <c r="G444" s="10"/>
-      <c r="H444" s="16"/>
+      <c r="H444" s="10"/>
       <c r="I444" s="16"/>
       <c r="J444" s="16"/>
       <c r="K444" s="16"/>
       <c r="L444" s="16"/>
       <c r="M444" s="16"/>
-    </row>
-    <row r="445" spans="1:13">
+      <c r="N444" s="16"/>
+    </row>
+    <row r="445" spans="1:14">
       <c r="A445" s="10"/>
       <c r="B445" s="16"/>
       <c r="C445" s="10"/>
@@ -8264,14 +8726,15 @@
       <c r="E445" s="10"/>
       <c r="F445" s="10"/>
       <c r="G445" s="10"/>
-      <c r="H445" s="16"/>
+      <c r="H445" s="10"/>
       <c r="I445" s="16"/>
       <c r="J445" s="16"/>
       <c r="K445" s="16"/>
       <c r="L445" s="16"/>
       <c r="M445" s="16"/>
-    </row>
-    <row r="446" spans="1:13">
+      <c r="N445" s="16"/>
+    </row>
+    <row r="446" spans="1:14">
       <c r="A446" s="10"/>
       <c r="B446" s="16"/>
       <c r="C446" s="10"/>
@@ -8279,14 +8742,15 @@
       <c r="E446" s="10"/>
       <c r="F446" s="10"/>
       <c r="G446" s="10"/>
-      <c r="H446" s="16"/>
+      <c r="H446" s="10"/>
       <c r="I446" s="16"/>
       <c r="J446" s="16"/>
       <c r="K446" s="16"/>
       <c r="L446" s="16"/>
       <c r="M446" s="16"/>
-    </row>
-    <row r="447" spans="1:13">
+      <c r="N446" s="16"/>
+    </row>
+    <row r="447" spans="1:14">
       <c r="A447" s="10"/>
       <c r="B447" s="16"/>
       <c r="C447" s="10"/>
@@ -8294,14 +8758,15 @@
       <c r="E447" s="10"/>
       <c r="F447" s="10"/>
       <c r="G447" s="10"/>
-      <c r="H447" s="16"/>
+      <c r="H447" s="10"/>
       <c r="I447" s="16"/>
       <c r="J447" s="16"/>
       <c r="K447" s="16"/>
       <c r="L447" s="16"/>
       <c r="M447" s="16"/>
-    </row>
-    <row r="448" spans="1:13">
+      <c r="N447" s="16"/>
+    </row>
+    <row r="448" spans="1:14">
       <c r="A448" s="10"/>
       <c r="B448" s="16"/>
       <c r="C448" s="10"/>
@@ -8309,14 +8774,15 @@
       <c r="E448" s="10"/>
       <c r="F448" s="10"/>
       <c r="G448" s="10"/>
-      <c r="H448" s="16"/>
+      <c r="H448" s="10"/>
       <c r="I448" s="16"/>
       <c r="J448" s="16"/>
       <c r="K448" s="16"/>
       <c r="L448" s="16"/>
       <c r="M448" s="16"/>
-    </row>
-    <row r="449" spans="1:13">
+      <c r="N448" s="16"/>
+    </row>
+    <row r="449" spans="1:14">
       <c r="A449" s="10"/>
       <c r="B449" s="16"/>
       <c r="C449" s="10"/>
@@ -8324,14 +8790,15 @@
       <c r="E449" s="10"/>
       <c r="F449" s="10"/>
       <c r="G449" s="10"/>
-      <c r="H449" s="16"/>
+      <c r="H449" s="10"/>
       <c r="I449" s="16"/>
       <c r="J449" s="16"/>
       <c r="K449" s="16"/>
       <c r="L449" s="16"/>
       <c r="M449" s="16"/>
-    </row>
-    <row r="450" spans="1:13">
+      <c r="N449" s="16"/>
+    </row>
+    <row r="450" spans="1:14">
       <c r="A450" s="10"/>
       <c r="B450" s="16"/>
       <c r="C450" s="10"/>
@@ -8339,14 +8806,15 @@
       <c r="E450" s="10"/>
       <c r="F450" s="10"/>
       <c r="G450" s="10"/>
-      <c r="H450" s="16"/>
+      <c r="H450" s="10"/>
       <c r="I450" s="16"/>
       <c r="J450" s="16"/>
       <c r="K450" s="16"/>
       <c r="L450" s="16"/>
       <c r="M450" s="16"/>
-    </row>
-    <row r="451" spans="1:13">
+      <c r="N450" s="16"/>
+    </row>
+    <row r="451" spans="1:14">
       <c r="A451" s="10"/>
       <c r="B451" s="16"/>
       <c r="C451" s="10"/>
@@ -8354,14 +8822,15 @@
       <c r="E451" s="10"/>
       <c r="F451" s="10"/>
       <c r="G451" s="10"/>
-      <c r="H451" s="16"/>
+      <c r="H451" s="10"/>
       <c r="I451" s="16"/>
       <c r="J451" s="16"/>
       <c r="K451" s="16"/>
       <c r="L451" s="16"/>
       <c r="M451" s="16"/>
-    </row>
-    <row r="452" spans="1:13">
+      <c r="N451" s="16"/>
+    </row>
+    <row r="452" spans="1:14">
       <c r="A452" s="10"/>
       <c r="B452" s="16"/>
       <c r="C452" s="10"/>
@@ -8369,14 +8838,15 @@
       <c r="E452" s="10"/>
       <c r="F452" s="10"/>
       <c r="G452" s="10"/>
-      <c r="H452" s="16"/>
+      <c r="H452" s="10"/>
       <c r="I452" s="16"/>
       <c r="J452" s="16"/>
       <c r="K452" s="16"/>
       <c r="L452" s="16"/>
       <c r="M452" s="16"/>
-    </row>
-    <row r="453" spans="1:13">
+      <c r="N452" s="16"/>
+    </row>
+    <row r="453" spans="1:14">
       <c r="A453" s="10"/>
       <c r="B453" s="16"/>
       <c r="C453" s="10"/>
@@ -8384,14 +8854,15 @@
       <c r="E453" s="10"/>
       <c r="F453" s="10"/>
       <c r="G453" s="10"/>
-      <c r="H453" s="16"/>
+      <c r="H453" s="10"/>
       <c r="I453" s="16"/>
       <c r="J453" s="16"/>
       <c r="K453" s="16"/>
       <c r="L453" s="16"/>
       <c r="M453" s="16"/>
-    </row>
-    <row r="454" spans="1:13">
+      <c r="N453" s="16"/>
+    </row>
+    <row r="454" spans="1:14">
       <c r="A454" s="10"/>
       <c r="B454" s="16"/>
       <c r="C454" s="10"/>
@@ -8399,14 +8870,15 @@
       <c r="E454" s="10"/>
       <c r="F454" s="10"/>
       <c r="G454" s="10"/>
-      <c r="H454" s="16"/>
+      <c r="H454" s="10"/>
       <c r="I454" s="16"/>
       <c r="J454" s="16"/>
       <c r="K454" s="16"/>
       <c r="L454" s="16"/>
       <c r="M454" s="16"/>
-    </row>
-    <row r="455" spans="1:13">
+      <c r="N454" s="16"/>
+    </row>
+    <row r="455" spans="1:14">
       <c r="A455" s="10"/>
       <c r="B455" s="16"/>
       <c r="C455" s="10"/>
@@ -8414,14 +8886,15 @@
       <c r="E455" s="10"/>
       <c r="F455" s="10"/>
       <c r="G455" s="10"/>
-      <c r="H455" s="16"/>
+      <c r="H455" s="10"/>
       <c r="I455" s="16"/>
       <c r="J455" s="16"/>
       <c r="K455" s="16"/>
       <c r="L455" s="16"/>
       <c r="M455" s="16"/>
-    </row>
-    <row r="456" spans="1:13">
+      <c r="N455" s="16"/>
+    </row>
+    <row r="456" spans="1:14">
       <c r="A456" s="10"/>
       <c r="B456" s="16"/>
       <c r="C456" s="10"/>
@@ -8429,14 +8902,15 @@
       <c r="E456" s="10"/>
       <c r="F456" s="10"/>
       <c r="G456" s="10"/>
-      <c r="H456" s="16"/>
+      <c r="H456" s="10"/>
       <c r="I456" s="16"/>
       <c r="J456" s="16"/>
       <c r="K456" s="16"/>
       <c r="L456" s="16"/>
       <c r="M456" s="16"/>
-    </row>
-    <row r="457" spans="1:13">
+      <c r="N456" s="16"/>
+    </row>
+    <row r="457" spans="1:14">
       <c r="A457" s="10"/>
       <c r="B457" s="16"/>
       <c r="C457" s="10"/>
@@ -8444,14 +8918,15 @@
       <c r="E457" s="10"/>
       <c r="F457" s="10"/>
       <c r="G457" s="10"/>
-      <c r="H457" s="16"/>
+      <c r="H457" s="10"/>
       <c r="I457" s="16"/>
       <c r="J457" s="16"/>
       <c r="K457" s="16"/>
       <c r="L457" s="16"/>
       <c r="M457" s="16"/>
-    </row>
-    <row r="458" spans="1:13">
+      <c r="N457" s="16"/>
+    </row>
+    <row r="458" spans="1:14">
       <c r="A458" s="10"/>
       <c r="B458" s="16"/>
       <c r="C458" s="10"/>
@@ -8459,14 +8934,15 @@
       <c r="E458" s="10"/>
       <c r="F458" s="10"/>
       <c r="G458" s="10"/>
-      <c r="H458" s="16"/>
+      <c r="H458" s="10"/>
       <c r="I458" s="16"/>
       <c r="J458" s="16"/>
       <c r="K458" s="16"/>
       <c r="L458" s="16"/>
       <c r="M458" s="16"/>
-    </row>
-    <row r="459" spans="1:13">
+      <c r="N458" s="16"/>
+    </row>
+    <row r="459" spans="1:14">
       <c r="A459" s="10"/>
       <c r="B459" s="16"/>
       <c r="C459" s="10"/>
@@ -8474,14 +8950,15 @@
       <c r="E459" s="10"/>
       <c r="F459" s="10"/>
       <c r="G459" s="10"/>
-      <c r="H459" s="16"/>
+      <c r="H459" s="10"/>
       <c r="I459" s="16"/>
       <c r="J459" s="16"/>
       <c r="K459" s="16"/>
       <c r="L459" s="16"/>
       <c r="M459" s="16"/>
-    </row>
-    <row r="460" spans="1:13">
+      <c r="N459" s="16"/>
+    </row>
+    <row r="460" spans="1:14">
       <c r="A460" s="10"/>
       <c r="B460" s="16"/>
       <c r="C460" s="10"/>
@@ -8489,14 +8966,15 @@
       <c r="E460" s="10"/>
       <c r="F460" s="10"/>
       <c r="G460" s="10"/>
-      <c r="H460" s="16"/>
+      <c r="H460" s="10"/>
       <c r="I460" s="16"/>
       <c r="J460" s="16"/>
       <c r="K460" s="16"/>
       <c r="L460" s="16"/>
       <c r="M460" s="16"/>
-    </row>
-    <row r="461" spans="1:13">
+      <c r="N460" s="16"/>
+    </row>
+    <row r="461" spans="1:14">
       <c r="A461" s="10"/>
       <c r="B461" s="16"/>
       <c r="C461" s="10"/>
@@ -8504,14 +8982,15 @@
       <c r="E461" s="10"/>
       <c r="F461" s="10"/>
       <c r="G461" s="10"/>
-      <c r="H461" s="16"/>
+      <c r="H461" s="10"/>
       <c r="I461" s="16"/>
       <c r="J461" s="16"/>
       <c r="K461" s="16"/>
       <c r="L461" s="16"/>
       <c r="M461" s="16"/>
-    </row>
-    <row r="462" spans="1:13">
+      <c r="N461" s="16"/>
+    </row>
+    <row r="462" spans="1:14">
       <c r="A462" s="10"/>
       <c r="B462" s="16"/>
       <c r="C462" s="10"/>
@@ -8519,14 +8998,15 @@
       <c r="E462" s="10"/>
       <c r="F462" s="10"/>
       <c r="G462" s="10"/>
-      <c r="H462" s="16"/>
+      <c r="H462" s="10"/>
       <c r="I462" s="16"/>
       <c r="J462" s="16"/>
       <c r="K462" s="16"/>
       <c r="L462" s="16"/>
       <c r="M462" s="16"/>
-    </row>
-    <row r="463" spans="1:13">
+      <c r="N462" s="16"/>
+    </row>
+    <row r="463" spans="1:14">
       <c r="A463" s="10"/>
       <c r="B463" s="16"/>
       <c r="C463" s="10"/>
@@ -8534,14 +9014,15 @@
       <c r="E463" s="10"/>
       <c r="F463" s="10"/>
       <c r="G463" s="10"/>
-      <c r="H463" s="16"/>
+      <c r="H463" s="10"/>
       <c r="I463" s="16"/>
       <c r="J463" s="16"/>
       <c r="K463" s="16"/>
       <c r="L463" s="16"/>
       <c r="M463" s="16"/>
-    </row>
-    <row r="464" spans="1:13">
+      <c r="N463" s="16"/>
+    </row>
+    <row r="464" spans="1:14">
       <c r="A464" s="10"/>
       <c r="B464" s="16"/>
       <c r="C464" s="10"/>
@@ -8549,14 +9030,15 @@
       <c r="E464" s="10"/>
       <c r="F464" s="10"/>
       <c r="G464" s="10"/>
-      <c r="H464" s="16"/>
+      <c r="H464" s="10"/>
       <c r="I464" s="16"/>
       <c r="J464" s="16"/>
       <c r="K464" s="16"/>
       <c r="L464" s="16"/>
       <c r="M464" s="16"/>
-    </row>
-    <row r="465" spans="1:13">
+      <c r="N464" s="16"/>
+    </row>
+    <row r="465" spans="1:14">
       <c r="A465" s="10"/>
       <c r="B465" s="16"/>
       <c r="C465" s="10"/>
@@ -8564,14 +9046,15 @@
       <c r="E465" s="10"/>
       <c r="F465" s="10"/>
       <c r="G465" s="10"/>
-      <c r="H465" s="16"/>
+      <c r="H465" s="10"/>
       <c r="I465" s="16"/>
       <c r="J465" s="16"/>
       <c r="K465" s="16"/>
       <c r="L465" s="16"/>
       <c r="M465" s="16"/>
-    </row>
-    <row r="466" spans="1:13">
+      <c r="N465" s="16"/>
+    </row>
+    <row r="466" spans="1:14">
       <c r="A466" s="10"/>
       <c r="B466" s="16"/>
       <c r="C466" s="10"/>
@@ -8579,14 +9062,15 @@
       <c r="E466" s="10"/>
       <c r="F466" s="10"/>
       <c r="G466" s="10"/>
-      <c r="H466" s="16"/>
+      <c r="H466" s="10"/>
       <c r="I466" s="16"/>
       <c r="J466" s="16"/>
       <c r="K466" s="16"/>
       <c r="L466" s="16"/>
       <c r="M466" s="16"/>
-    </row>
-    <row r="467" spans="1:13">
+      <c r="N466" s="16"/>
+    </row>
+    <row r="467" spans="1:14">
       <c r="A467" s="10"/>
       <c r="B467" s="16"/>
       <c r="C467" s="10"/>
@@ -8594,14 +9078,15 @@
       <c r="E467" s="10"/>
       <c r="F467" s="10"/>
       <c r="G467" s="10"/>
-      <c r="H467" s="16"/>
+      <c r="H467" s="10"/>
       <c r="I467" s="16"/>
       <c r="J467" s="16"/>
       <c r="K467" s="16"/>
       <c r="L467" s="16"/>
       <c r="M467" s="16"/>
-    </row>
-    <row r="468" spans="1:13">
+      <c r="N467" s="16"/>
+    </row>
+    <row r="468" spans="1:14">
       <c r="A468" s="10"/>
       <c r="B468" s="16"/>
       <c r="C468" s="10"/>
@@ -8609,14 +9094,15 @@
       <c r="E468" s="10"/>
       <c r="F468" s="10"/>
       <c r="G468" s="10"/>
-      <c r="H468" s="16"/>
+      <c r="H468" s="10"/>
       <c r="I468" s="16"/>
       <c r="J468" s="16"/>
       <c r="K468" s="16"/>
       <c r="L468" s="16"/>
       <c r="M468" s="16"/>
-    </row>
-    <row r="469" spans="1:13">
+      <c r="N468" s="16"/>
+    </row>
+    <row r="469" spans="1:14">
       <c r="A469" s="10"/>
       <c r="B469" s="16"/>
       <c r="C469" s="10"/>
@@ -8624,14 +9110,15 @@
       <c r="E469" s="10"/>
       <c r="F469" s="10"/>
       <c r="G469" s="10"/>
-      <c r="H469" s="16"/>
+      <c r="H469" s="10"/>
       <c r="I469" s="16"/>
       <c r="J469" s="16"/>
       <c r="K469" s="16"/>
       <c r="L469" s="16"/>
       <c r="M469" s="16"/>
-    </row>
-    <row r="470" spans="1:13">
+      <c r="N469" s="16"/>
+    </row>
+    <row r="470" spans="1:14">
       <c r="A470" s="10"/>
       <c r="B470" s="16"/>
       <c r="C470" s="10"/>
@@ -8639,14 +9126,15 @@
       <c r="E470" s="10"/>
       <c r="F470" s="10"/>
       <c r="G470" s="10"/>
-      <c r="H470" s="16"/>
+      <c r="H470" s="10"/>
       <c r="I470" s="16"/>
       <c r="J470" s="16"/>
       <c r="K470" s="16"/>
       <c r="L470" s="16"/>
       <c r="M470" s="16"/>
-    </row>
-    <row r="471" spans="1:13">
+      <c r="N470" s="16"/>
+    </row>
+    <row r="471" spans="1:14">
       <c r="A471" s="10"/>
       <c r="B471" s="16"/>
       <c r="C471" s="10"/>
@@ -8654,14 +9142,15 @@
       <c r="E471" s="10"/>
       <c r="F471" s="10"/>
       <c r="G471" s="10"/>
-      <c r="H471" s="16"/>
+      <c r="H471" s="10"/>
       <c r="I471" s="16"/>
       <c r="J471" s="16"/>
       <c r="K471" s="16"/>
       <c r="L471" s="16"/>
       <c r="M471" s="16"/>
-    </row>
-    <row r="472" spans="1:13">
+      <c r="N471" s="16"/>
+    </row>
+    <row r="472" spans="1:14">
       <c r="A472" s="10"/>
       <c r="B472" s="16"/>
       <c r="C472" s="10"/>
@@ -8669,14 +9158,15 @@
       <c r="E472" s="10"/>
       <c r="F472" s="10"/>
       <c r="G472" s="10"/>
-      <c r="H472" s="16"/>
+      <c r="H472" s="10"/>
       <c r="I472" s="16"/>
       <c r="J472" s="16"/>
       <c r="K472" s="16"/>
       <c r="L472" s="16"/>
       <c r="M472" s="16"/>
-    </row>
-    <row r="473" spans="1:13">
+      <c r="N472" s="16"/>
+    </row>
+    <row r="473" spans="1:14">
       <c r="A473" s="10"/>
       <c r="B473" s="16"/>
       <c r="C473" s="10"/>
@@ -8684,14 +9174,15 @@
       <c r="E473" s="10"/>
       <c r="F473" s="10"/>
       <c r="G473" s="10"/>
-      <c r="H473" s="16"/>
+      <c r="H473" s="10"/>
       <c r="I473" s="16"/>
       <c r="J473" s="16"/>
       <c r="K473" s="16"/>
       <c r="L473" s="16"/>
       <c r="M473" s="16"/>
-    </row>
-    <row r="474" spans="1:13">
+      <c r="N473" s="16"/>
+    </row>
+    <row r="474" spans="1:14">
       <c r="A474" s="10"/>
       <c r="B474" s="16"/>
       <c r="C474" s="10"/>
@@ -8699,14 +9190,15 @@
       <c r="E474" s="10"/>
       <c r="F474" s="10"/>
       <c r="G474" s="10"/>
-      <c r="H474" s="16"/>
+      <c r="H474" s="10"/>
       <c r="I474" s="16"/>
       <c r="J474" s="16"/>
       <c r="K474" s="16"/>
       <c r="L474" s="16"/>
       <c r="M474" s="16"/>
-    </row>
-    <row r="475" spans="1:13">
+      <c r="N474" s="16"/>
+    </row>
+    <row r="475" spans="1:14">
       <c r="A475" s="10"/>
       <c r="B475" s="16"/>
       <c r="C475" s="10"/>
@@ -8714,14 +9206,15 @@
       <c r="E475" s="10"/>
       <c r="F475" s="10"/>
       <c r="G475" s="10"/>
-      <c r="H475" s="16"/>
+      <c r="H475" s="10"/>
       <c r="I475" s="16"/>
       <c r="J475" s="16"/>
       <c r="K475" s="16"/>
       <c r="L475" s="16"/>
       <c r="M475" s="16"/>
-    </row>
-    <row r="476" spans="1:13">
+      <c r="N475" s="16"/>
+    </row>
+    <row r="476" spans="1:14">
       <c r="A476" s="10"/>
       <c r="B476" s="16"/>
       <c r="C476" s="10"/>
@@ -8729,14 +9222,15 @@
       <c r="E476" s="10"/>
       <c r="F476" s="10"/>
       <c r="G476" s="10"/>
-      <c r="H476" s="16"/>
+      <c r="H476" s="10"/>
       <c r="I476" s="16"/>
       <c r="J476" s="16"/>
       <c r="K476" s="16"/>
       <c r="L476" s="16"/>
       <c r="M476" s="16"/>
-    </row>
-    <row r="477" spans="1:13">
+      <c r="N476" s="16"/>
+    </row>
+    <row r="477" spans="1:14">
       <c r="A477" s="10"/>
       <c r="B477" s="16"/>
       <c r="C477" s="10"/>
@@ -8744,14 +9238,15 @@
       <c r="E477" s="10"/>
       <c r="F477" s="10"/>
       <c r="G477" s="10"/>
-      <c r="H477" s="16"/>
+      <c r="H477" s="10"/>
       <c r="I477" s="16"/>
       <c r="J477" s="16"/>
       <c r="K477" s="16"/>
       <c r="L477" s="16"/>
       <c r="M477" s="16"/>
-    </row>
-    <row r="478" spans="1:13">
+      <c r="N477" s="16"/>
+    </row>
+    <row r="478" spans="1:14">
       <c r="A478" s="10"/>
       <c r="B478" s="16"/>
       <c r="C478" s="10"/>
@@ -8759,14 +9254,15 @@
       <c r="E478" s="10"/>
       <c r="F478" s="10"/>
       <c r="G478" s="10"/>
-      <c r="H478" s="16"/>
+      <c r="H478" s="10"/>
       <c r="I478" s="16"/>
       <c r="J478" s="16"/>
       <c r="K478" s="16"/>
       <c r="L478" s="16"/>
       <c r="M478" s="16"/>
-    </row>
-    <row r="479" spans="1:13">
+      <c r="N478" s="16"/>
+    </row>
+    <row r="479" spans="1:14">
       <c r="A479" s="10"/>
       <c r="B479" s="16"/>
       <c r="C479" s="10"/>
@@ -8774,14 +9270,15 @@
       <c r="E479" s="10"/>
       <c r="F479" s="10"/>
       <c r="G479" s="10"/>
-      <c r="H479" s="16"/>
+      <c r="H479" s="10"/>
       <c r="I479" s="16"/>
       <c r="J479" s="16"/>
       <c r="K479" s="16"/>
       <c r="L479" s="16"/>
       <c r="M479" s="16"/>
-    </row>
-    <row r="480" spans="1:13">
+      <c r="N479" s="16"/>
+    </row>
+    <row r="480" spans="1:14">
       <c r="A480" s="10"/>
       <c r="B480" s="16"/>
       <c r="C480" s="10"/>
@@ -8789,14 +9286,15 @@
       <c r="E480" s="10"/>
       <c r="F480" s="10"/>
       <c r="G480" s="10"/>
-      <c r="H480" s="16"/>
+      <c r="H480" s="10"/>
       <c r="I480" s="16"/>
       <c r="J480" s="16"/>
       <c r="K480" s="16"/>
       <c r="L480" s="16"/>
       <c r="M480" s="16"/>
-    </row>
-    <row r="481" spans="1:13">
+      <c r="N480" s="16"/>
+    </row>
+    <row r="481" spans="1:14">
       <c r="A481" s="10"/>
       <c r="B481" s="16"/>
       <c r="C481" s="10"/>
@@ -8804,14 +9302,15 @@
       <c r="E481" s="10"/>
       <c r="F481" s="10"/>
       <c r="G481" s="10"/>
-      <c r="H481" s="16"/>
+      <c r="H481" s="10"/>
       <c r="I481" s="16"/>
       <c r="J481" s="16"/>
       <c r="K481" s="16"/>
       <c r="L481" s="16"/>
       <c r="M481" s="16"/>
-    </row>
-    <row r="482" spans="1:13">
+      <c r="N481" s="16"/>
+    </row>
+    <row r="482" spans="1:14">
       <c r="A482" s="10"/>
       <c r="B482" s="16"/>
       <c r="C482" s="10"/>
@@ -8819,14 +9318,15 @@
       <c r="E482" s="10"/>
       <c r="F482" s="10"/>
       <c r="G482" s="10"/>
-      <c r="H482" s="16"/>
+      <c r="H482" s="10"/>
       <c r="I482" s="16"/>
       <c r="J482" s="16"/>
       <c r="K482" s="16"/>
       <c r="L482" s="16"/>
       <c r="M482" s="16"/>
-    </row>
-    <row r="483" spans="1:13">
+      <c r="N482" s="16"/>
+    </row>
+    <row r="483" spans="1:14">
       <c r="A483" s="10"/>
       <c r="B483" s="16"/>
       <c r="C483" s="10"/>
@@ -8834,14 +9334,15 @@
       <c r="E483" s="10"/>
       <c r="F483" s="10"/>
       <c r="G483" s="10"/>
-      <c r="H483" s="16"/>
+      <c r="H483" s="10"/>
       <c r="I483" s="16"/>
       <c r="J483" s="16"/>
       <c r="K483" s="16"/>
       <c r="L483" s="16"/>
       <c r="M483" s="16"/>
-    </row>
-    <row r="484" spans="1:13">
+      <c r="N483" s="16"/>
+    </row>
+    <row r="484" spans="1:14">
       <c r="A484" s="10"/>
       <c r="B484" s="16"/>
       <c r="C484" s="10"/>
@@ -8849,14 +9350,15 @@
       <c r="E484" s="10"/>
       <c r="F484" s="10"/>
       <c r="G484" s="10"/>
-      <c r="H484" s="16"/>
+      <c r="H484" s="10"/>
       <c r="I484" s="16"/>
       <c r="J484" s="16"/>
       <c r="K484" s="16"/>
       <c r="L484" s="16"/>
       <c r="M484" s="16"/>
-    </row>
-    <row r="485" spans="1:13">
+      <c r="N484" s="16"/>
+    </row>
+    <row r="485" spans="1:14">
       <c r="A485" s="10"/>
       <c r="B485" s="16"/>
       <c r="C485" s="10"/>
@@ -8864,14 +9366,15 @@
       <c r="E485" s="10"/>
       <c r="F485" s="10"/>
       <c r="G485" s="10"/>
-      <c r="H485" s="16"/>
+      <c r="H485" s="10"/>
       <c r="I485" s="16"/>
       <c r="J485" s="16"/>
       <c r="K485" s="16"/>
       <c r="L485" s="16"/>
       <c r="M485" s="16"/>
-    </row>
-    <row r="486" spans="1:13">
+      <c r="N485" s="16"/>
+    </row>
+    <row r="486" spans="1:14">
       <c r="A486" s="10"/>
       <c r="B486" s="16"/>
       <c r="C486" s="10"/>
@@ -8879,14 +9382,15 @@
       <c r="E486" s="10"/>
       <c r="F486" s="10"/>
       <c r="G486" s="10"/>
-      <c r="H486" s="16"/>
+      <c r="H486" s="10"/>
       <c r="I486" s="16"/>
       <c r="J486" s="16"/>
       <c r="K486" s="16"/>
       <c r="L486" s="16"/>
       <c r="M486" s="16"/>
-    </row>
-    <row r="487" spans="1:13">
+      <c r="N486" s="16"/>
+    </row>
+    <row r="487" spans="1:14">
       <c r="A487" s="10"/>
       <c r="B487" s="16"/>
       <c r="C487" s="10"/>
@@ -8894,14 +9398,15 @@
       <c r="E487" s="10"/>
       <c r="F487" s="10"/>
       <c r="G487" s="10"/>
-      <c r="H487" s="16"/>
+      <c r="H487" s="10"/>
       <c r="I487" s="16"/>
       <c r="J487" s="16"/>
       <c r="K487" s="16"/>
       <c r="L487" s="16"/>
       <c r="M487" s="16"/>
-    </row>
-    <row r="488" spans="1:13">
+      <c r="N487" s="16"/>
+    </row>
+    <row r="488" spans="1:14">
       <c r="A488" s="10"/>
       <c r="B488" s="16"/>
       <c r="C488" s="10"/>
@@ -8909,14 +9414,15 @@
       <c r="E488" s="10"/>
       <c r="F488" s="10"/>
       <c r="G488" s="10"/>
-      <c r="H488" s="16"/>
+      <c r="H488" s="10"/>
       <c r="I488" s="16"/>
       <c r="J488" s="16"/>
       <c r="K488" s="16"/>
       <c r="L488" s="16"/>
       <c r="M488" s="16"/>
-    </row>
-    <row r="489" spans="1:13">
+      <c r="N488" s="16"/>
+    </row>
+    <row r="489" spans="1:14">
       <c r="A489" s="10"/>
       <c r="B489" s="16"/>
       <c r="C489" s="10"/>
@@ -8924,14 +9430,15 @@
       <c r="E489" s="10"/>
       <c r="F489" s="10"/>
       <c r="G489" s="10"/>
-      <c r="H489" s="16"/>
+      <c r="H489" s="10"/>
       <c r="I489" s="16"/>
       <c r="J489" s="16"/>
       <c r="K489" s="16"/>
       <c r="L489" s="16"/>
       <c r="M489" s="16"/>
-    </row>
-    <row r="490" spans="1:13">
+      <c r="N489" s="16"/>
+    </row>
+    <row r="490" spans="1:14">
       <c r="A490" s="10"/>
       <c r="B490" s="16"/>
       <c r="C490" s="10"/>
@@ -8939,14 +9446,15 @@
       <c r="E490" s="10"/>
       <c r="F490" s="10"/>
       <c r="G490" s="10"/>
-      <c r="H490" s="16"/>
+      <c r="H490" s="10"/>
       <c r="I490" s="16"/>
       <c r="J490" s="16"/>
       <c r="K490" s="16"/>
       <c r="L490" s="16"/>
       <c r="M490" s="16"/>
-    </row>
-    <row r="491" spans="1:13">
+      <c r="N490" s="16"/>
+    </row>
+    <row r="491" spans="1:14">
       <c r="A491" s="10"/>
       <c r="B491" s="16"/>
       <c r="C491" s="10"/>
@@ -8954,14 +9462,15 @@
       <c r="E491" s="10"/>
       <c r="F491" s="10"/>
       <c r="G491" s="10"/>
-      <c r="H491" s="16"/>
+      <c r="H491" s="10"/>
       <c r="I491" s="16"/>
       <c r="J491" s="16"/>
       <c r="K491" s="16"/>
       <c r="L491" s="16"/>
       <c r="M491" s="16"/>
-    </row>
-    <row r="492" spans="1:13">
+      <c r="N491" s="16"/>
+    </row>
+    <row r="492" spans="1:14">
       <c r="A492" s="10"/>
       <c r="B492" s="16"/>
       <c r="C492" s="10"/>
@@ -8969,14 +9478,15 @@
       <c r="E492" s="10"/>
       <c r="F492" s="10"/>
       <c r="G492" s="10"/>
-      <c r="H492" s="16"/>
+      <c r="H492" s="10"/>
       <c r="I492" s="16"/>
       <c r="J492" s="16"/>
       <c r="K492" s="16"/>
       <c r="L492" s="16"/>
       <c r="M492" s="16"/>
-    </row>
-    <row r="493" spans="1:13">
+      <c r="N492" s="16"/>
+    </row>
+    <row r="493" spans="1:14">
       <c r="A493" s="10"/>
       <c r="B493" s="16"/>
       <c r="C493" s="10"/>
@@ -8984,14 +9494,15 @@
       <c r="E493" s="10"/>
       <c r="F493" s="10"/>
       <c r="G493" s="10"/>
-      <c r="H493" s="16"/>
+      <c r="H493" s="10"/>
       <c r="I493" s="16"/>
       <c r="J493" s="16"/>
       <c r="K493" s="16"/>
       <c r="L493" s="16"/>
       <c r="M493" s="16"/>
-    </row>
-    <row r="494" spans="1:13">
+      <c r="N493" s="16"/>
+    </row>
+    <row r="494" spans="1:14">
       <c r="A494" s="10"/>
       <c r="B494" s="16"/>
       <c r="C494" s="10"/>
@@ -8999,14 +9510,15 @@
       <c r="E494" s="10"/>
       <c r="F494" s="10"/>
       <c r="G494" s="10"/>
-      <c r="H494" s="16"/>
+      <c r="H494" s="10"/>
       <c r="I494" s="16"/>
       <c r="J494" s="16"/>
       <c r="K494" s="16"/>
       <c r="L494" s="16"/>
       <c r="M494" s="16"/>
-    </row>
-    <row r="495" spans="1:13">
+      <c r="N494" s="16"/>
+    </row>
+    <row r="495" spans="1:14">
       <c r="A495" s="10"/>
       <c r="B495" s="16"/>
       <c r="C495" s="10"/>
@@ -9014,14 +9526,15 @@
       <c r="E495" s="10"/>
       <c r="F495" s="10"/>
       <c r="G495" s="10"/>
-      <c r="H495" s="16"/>
+      <c r="H495" s="10"/>
       <c r="I495" s="16"/>
       <c r="J495" s="16"/>
       <c r="K495" s="16"/>
       <c r="L495" s="16"/>
       <c r="M495" s="16"/>
-    </row>
-    <row r="496" spans="1:13">
+      <c r="N495" s="16"/>
+    </row>
+    <row r="496" spans="1:14">
       <c r="A496" s="10"/>
       <c r="B496" s="16"/>
       <c r="C496" s="10"/>
@@ -9029,14 +9542,15 @@
       <c r="E496" s="10"/>
       <c r="F496" s="10"/>
       <c r="G496" s="10"/>
-      <c r="H496" s="16"/>
+      <c r="H496" s="10"/>
       <c r="I496" s="16"/>
       <c r="J496" s="16"/>
       <c r="K496" s="16"/>
       <c r="L496" s="16"/>
       <c r="M496" s="16"/>
-    </row>
-    <row r="497" spans="1:13">
+      <c r="N496" s="16"/>
+    </row>
+    <row r="497" spans="1:14">
       <c r="A497" s="10"/>
       <c r="B497" s="16"/>
       <c r="C497" s="10"/>
@@ -9044,14 +9558,15 @@
       <c r="E497" s="10"/>
       <c r="F497" s="10"/>
       <c r="G497" s="10"/>
-      <c r="H497" s="16"/>
+      <c r="H497" s="10"/>
       <c r="I497" s="16"/>
       <c r="J497" s="16"/>
       <c r="K497" s="16"/>
       <c r="L497" s="16"/>
       <c r="M497" s="16"/>
-    </row>
-    <row r="498" spans="1:13">
+      <c r="N497" s="16"/>
+    </row>
+    <row r="498" spans="1:14">
       <c r="A498" s="10"/>
       <c r="B498" s="16"/>
       <c r="C498" s="10"/>
@@ -9059,14 +9574,15 @@
       <c r="E498" s="10"/>
       <c r="F498" s="10"/>
       <c r="G498" s="10"/>
-      <c r="H498" s="16"/>
+      <c r="H498" s="10"/>
       <c r="I498" s="16"/>
       <c r="J498" s="16"/>
       <c r="K498" s="16"/>
       <c r="L498" s="16"/>
       <c r="M498" s="16"/>
-    </row>
-    <row r="499" spans="1:13">
+      <c r="N498" s="16"/>
+    </row>
+    <row r="499" spans="1:14">
       <c r="A499" s="10"/>
       <c r="B499" s="16"/>
       <c r="C499" s="10"/>
@@ -9074,14 +9590,15 @@
       <c r="E499" s="10"/>
       <c r="F499" s="10"/>
       <c r="G499" s="10"/>
-      <c r="H499" s="16"/>
+      <c r="H499" s="10"/>
       <c r="I499" s="16"/>
       <c r="J499" s="16"/>
       <c r="K499" s="16"/>
       <c r="L499" s="16"/>
       <c r="M499" s="16"/>
-    </row>
-    <row r="500" spans="1:13">
+      <c r="N499" s="16"/>
+    </row>
+    <row r="500" spans="1:14">
       <c r="A500" s="10"/>
       <c r="B500" s="16"/>
       <c r="C500" s="10"/>
@@ -9089,14 +9606,15 @@
       <c r="E500" s="10"/>
       <c r="F500" s="10"/>
       <c r="G500" s="10"/>
-      <c r="H500" s="16"/>
+      <c r="H500" s="10"/>
       <c r="I500" s="16"/>
       <c r="J500" s="16"/>
       <c r="K500" s="16"/>
       <c r="L500" s="16"/>
       <c r="M500" s="16"/>
-    </row>
-    <row r="501" spans="1:13">
+      <c r="N500" s="16"/>
+    </row>
+    <row r="501" spans="1:14">
       <c r="A501" s="10"/>
       <c r="B501" s="16"/>
       <c r="C501" s="10"/>
@@ -9104,14 +9622,15 @@
       <c r="E501" s="10"/>
       <c r="F501" s="10"/>
       <c r="G501" s="10"/>
-      <c r="H501" s="16"/>
+      <c r="H501" s="10"/>
       <c r="I501" s="16"/>
       <c r="J501" s="16"/>
       <c r="K501" s="16"/>
       <c r="L501" s="16"/>
       <c r="M501" s="16"/>
-    </row>
-    <row r="502" spans="1:13">
+      <c r="N501" s="16"/>
+    </row>
+    <row r="502" spans="1:14">
       <c r="A502" s="10"/>
       <c r="B502" s="16"/>
       <c r="C502" s="10"/>
@@ -9119,14 +9638,15 @@
       <c r="E502" s="10"/>
       <c r="F502" s="10"/>
       <c r="G502" s="10"/>
-      <c r="H502" s="16"/>
+      <c r="H502" s="10"/>
       <c r="I502" s="16"/>
       <c r="J502" s="16"/>
       <c r="K502" s="16"/>
       <c r="L502" s="16"/>
       <c r="M502" s="16"/>
-    </row>
-    <row r="503" spans="1:13">
+      <c r="N502" s="16"/>
+    </row>
+    <row r="503" spans="1:14">
       <c r="A503" s="10"/>
       <c r="B503" s="16"/>
       <c r="C503" s="10"/>
@@ -9134,12 +9654,13 @@
       <c r="E503" s="10"/>
       <c r="F503" s="10"/>
       <c r="G503" s="10"/>
-      <c r="H503" s="16"/>
+      <c r="H503" s="10"/>
       <c r="I503" s="16"/>
       <c r="J503" s="16"/>
       <c r="K503" s="16"/>
       <c r="L503" s="16"/>
       <c r="M503" s="16"/>
+      <c r="N503" s="16"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -9163,7 +9684,7 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～1000。跨表引用及组合条件请对照填表说明。" promptTitle="跳跃速度（毫米/Tick）" prompt="整数 1～1000。起跳时的向上速度。" sqref="G5:G503">
+    <dataValidation type="whole" operator="between" showInputMessage="1" showErrorMessage="1" errorTitle="请输入合法配置值" error="整数 1～1000。跨表引用及组合条件请对照填表说明。" promptTitle="跳跃速度（毫米/Tick）" prompt="整数 1～1000。起跳时的向上速度。" sqref="G5:G503 H5:H503">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
@@ -9172,7 +9693,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A7:H503 N6:O6 C5:H5 C6:D6 F6:H6 A5:A6 A2:H4 A1:G1 M1:O1 M7:O503 J2:J503 L5:L6" numberStoredAsText="1"/>
+    <ignoredError sqref="H2:I6 H7:I503 H1 M5:M6 K2:K503 N7:P503 N1:P1 A1:E1 A2:F4 A5:A6 F6 C6:D6 C5:F5 O6:P6 A7:F503" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9192,65 +9713,65 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="29" customHeight="1" spans="1:6">
       <c r="A3" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" s="7"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4" s="7"/>
     </row>
@@ -9268,7 +9789,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:6">

--- a/design/角色表.xlsx
+++ b/design/角色表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12060"/>
+    <workbookView windowWidth="18345" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="玩家|Player" sheetId="1" r:id="rId1"/>
@@ -9226,7 +9226,7 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="I2:J503 M7:O503 M1:O1 A1:B3 A4:A6 G6 D6:E6 N6:O6 A7:B503 E1:F1 D7:G503 D2:G4 E5:G5" numberStoredAsText="1"/>
+    <ignoredError sqref="E5:G5 D2:G4 D7:G503 E1:F1 A7:B503 N6:O6 D6:E6 G6 A4:A6 A1:B3 M1:O1 M7:O503 I2:J503" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/design/角色表.xlsx
+++ b/design/角色表.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\聚光灯\Hunter\design\"/>
+      <x15ac:absPath url="E:\聚光灯\Hunter\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -217,14 +217,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="58">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -418,8 +418,175 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF12283F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202C3A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202020"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202020"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="73">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -636,8 +803,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9CEE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD3E7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -795,8 +1142,132 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -945,8 +1416,156 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="32" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="32" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="32" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="32" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="32" fillId="0" borderId="13" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="41" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="42" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="43" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="44" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="45" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="46" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="47" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="48" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="49" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="50" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="51" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="52" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="53" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="54" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="55" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="56" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="57" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="58" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="59" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="60" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="61" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="62" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="63" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="64" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="65" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="66" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="67" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="68" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="69" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="70" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="71" borderId="13" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1001,6 +1620,86 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="99"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="99" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="14" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="15" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="16" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="17" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="31" fillId="39" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="31" fillId="40" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="13" xfId="99" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="28" fillId="37" borderId="14" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="37" borderId="15" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="38" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="28" fillId="37" borderId="16" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="37" borderId="17" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="31" fillId="39" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="40" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="13" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="30" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="54" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="55" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="54" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="55" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="54" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="55" fillId="72" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="13" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1270,7 +1969,7 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
@@ -1474,7 +2173,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:O503"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" style="11" customWidth="1"/>
@@ -1487,6 +2186,24 @@
     <col min="14" max="14" width="9" style="12"/>
     <col min="15" max="15" width="55" style="12" customWidth="1"/>
     <col min="16" max="30" width="9" style="12"/>
+    <col min="14" max="14" width="22" style="12" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="22" style="12" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="9" style="12" customWidth="0"/>
+    <col min="17" max="17" width="9" style="12" customWidth="0"/>
+    <col min="18" max="18" width="9" style="12" customWidth="0"/>
+    <col min="19" max="19" width="9" style="12" customWidth="0"/>
+    <col min="20" max="20" width="9" style="12" customWidth="0"/>
+    <col min="21" max="21" width="9" style="12" customWidth="0"/>
+    <col min="22" max="22" width="9" style="12" customWidth="0"/>
+    <col min="23" max="23" width="9" style="12" customWidth="0"/>
+    <col min="16" max="16" width="22" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="22" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="22" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="22" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="22" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="22" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="22" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:15">
@@ -1529,8 +2246,38 @@
       <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="15" t="s">
-        <v>13</v>
+      <c r="N1" s="47" t="str">
+        <v>匍匐速度（毫米/Tick）</v>
+      </c>
+      <c r="O1" s="54" t="str">
+        <v>匍匐宽度（毫米）</v>
+      </c>
+      <c r="P1" s="47" t="str">
+        <v>匍匐高度（毫米）</v>
+      </c>
+      <c r="Q1" s="47" t="str">
+        <v>最大体力</v>
+      </c>
+      <c r="R1" s="47" t="str">
+        <v>体力恢复延迟（Tick）</v>
+      </c>
+      <c r="S1" s="47" t="str">
+        <v>体力每秒恢复</v>
+      </c>
+      <c r="T1" s="47" t="str">
+        <v>奔跑每秒体耗（本版0）</v>
+      </c>
+      <c r="U1" s="47" t="str">
+        <v>跳跃体耗（本版0）</v>
+      </c>
+      <c r="V1" s="47" t="str">
+        <v>生命恢复延迟（Tick）</v>
+      </c>
+      <c r="W1" s="47" t="str">
+        <v>生命每秒恢复</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>配置模板 · 待接入</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:15">
@@ -1573,8 +2320,38 @@
       <c r="M2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="18" t="s">
-        <v>16</v>
+      <c r="N2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="O2" s="55" t="str">
+        <v>int32</v>
+      </c>
+      <c r="P2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="Q2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="R2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="S2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="T2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="U2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="V2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="W2" s="47" t="str">
+        <v>int32</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>详见《配置表填写说明.md》</v>
       </c>
     </row>
     <row r="3" ht="29" customHeight="1" spans="1:15">
@@ -1617,7 +2394,36 @@
       <c r="M3" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="18"/>
+      <c r="N3" s="47" t="str">
+        <v>ProneSpeed</v>
+      </c>
+      <c r="O3" s="55" t="str">
+        <v>ProneWidth</v>
+      </c>
+      <c r="P3" s="47" t="str">
+        <v>ProneHeight</v>
+      </c>
+      <c r="Q3" s="47" t="str">
+        <v>Stamina</v>
+      </c>
+      <c r="R3" s="47" t="str">
+        <v>StaminaDelay</v>
+      </c>
+      <c r="S3" s="47" t="str">
+        <v>StaminaRate</v>
+      </c>
+      <c r="T3" s="47" t="str">
+        <v>RunCost</v>
+      </c>
+      <c r="U3" s="47" t="str">
+        <v>JumpCost</v>
+      </c>
+      <c r="V3" s="47" t="str">
+        <v>HealthDelay</v>
+      </c>
+      <c r="W3" s="47" t="str">
+        <v>HealthRate</v>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:15">
       <c r="A4" s="16" t="s">
@@ -1659,7 +2465,36 @@
       <c r="M4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="18"/>
+      <c r="N4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="O4" s="55" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="P4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="Q4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="R4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="S4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="T4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="U4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="V4" s="47" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="W4" s="47" t="str">
+        <v>server/client</v>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:15">
       <c r="A5" s="19">
@@ -1695,12 +2530,42 @@
       <c r="K5" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="19" t="s">
-        <v>38</v>
+      <c r="L5" s="41" t="str">
+        <v>50|50|25|25</v>
       </c>
       <c r="M5" s="19"/>
-      <c r="O5" s="18" t="s">
-        <v>39</v>
+      <c r="N5" s="56" t="n">
+        <v>50</v>
+      </c>
+      <c r="O5" s="57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P5" s="56" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q5" s="56" t="n">
+        <v>100</v>
+      </c>
+      <c r="R5" s="56" t="n">
+        <v>120</v>
+      </c>
+      <c r="S5" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="56" t="n">
+        <v>300</v>
+      </c>
+      <c r="W5" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>资源空值表示待美术交付；新增数值为示例。</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:15">
@@ -1710,7 +2575,7 @@
       <c r="B6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="42" t="str">
         <v>0</v>
       </c>
       <c r="D6" s="20">
@@ -1737,11 +2602,41 @@
       <c r="K6" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="20" t="s">
-        <v>38</v>
+      <c r="L6" s="42" t="str">
+        <v>50|50|25|25</v>
       </c>
       <c r="M6" s="20" t="s">
         <v>42</v>
+      </c>
+      <c r="N6" s="56" t="n">
+        <v>50</v>
+      </c>
+      <c r="O6" s="56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P6" s="56" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q6" s="56" t="n">
+        <v>100</v>
+      </c>
+      <c r="R6" s="56" t="n">
+        <v>120</v>
+      </c>
+      <c r="S6" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="56" t="n">
+        <v>300</v>
+      </c>
+      <c r="W6" s="56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:15">

--- a/design/角色表.xlsx
+++ b/design/角色表.xlsx
@@ -1,32 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\聚光灯\Hunter\design\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <ns1:AlternateContent>
+    <ns1:Choice Requires="x15">
+      <ns2:absPath url="E:\聚光灯\Hunter\design\"/>
+    </ns1:Choice>
+  </ns1:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="玩家|Player" sheetId="1" r:id="rId1"/>
     <sheet name="玩家技能|PlayerSkill" sheetId="2" r:id="rId2"/>
+    <sheet name="天赋配置说明" sheetId="3" r:id="rIdCfg3"/>
+    <sheet name="成长规则|Career" sheetId="4" r:id="rIdCfg4"/>
+    <sheet name="等级经验|CareerLevel" sheetId="5" r:id="rIdCfg5"/>
+    <sheet name="击杀经验|KillXp" sheetId="6" r:id="rIdCfg6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <ns4:calcFeatures>
+        <ns4:feature name="microsoft.com:RD"/>
+        <ns4:feature name="microsoft.com:Single"/>
+        <ns4:feature name="microsoft.com:FV"/>
+        <ns4:feature name="microsoft.com:CNMTM"/>
+        <ns4:feature name="microsoft.com:LET_WF"/>
+        <ns4:feature name="microsoft.com:LAMBDA_WF"/>
+        <ns4:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </ns4:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -597,14 +601,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ns1:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -836,8 +840,36 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF17344A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF17344A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1060,8 +1092,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CDE1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CDE1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1234,8 +1288,10 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border/>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1384,8 +1440,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="14"/>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="15"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1455,6 +1513,62 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="14" xfId="50"/>
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="38" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="40" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="38" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="38" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="40" borderId="14" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="15" xfId="51"/>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="43" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1702,7 +1816,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" ns2:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1711,7 +1825,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" ns2:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1725,8 +1839,8 @@
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1924,6 +2038,398 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/cfg3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="85" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="37" t="str">
+        <v>v5 玩家天赋</v>
+      </c>
+      <c r="B1" s="37" t="str">
+        <v>规则</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="36" t="str">
+        <v>技能点</v>
+      </c>
+      <c r="B2" s="36" t="str">
+        <v>Player.SkillPoints；选择技能总花费不得超过技能点。</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="36" t="str">
+        <v>局内选择</v>
+      </c>
+      <c r="B3" s="36" t="str">
+        <v>使用 Loadout.skills，不读取旧 PlayerSkill 主动槽草稿。</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="36" t="str">
+        <v>数值来源</v>
+      </c>
+      <c r="B4" s="36" t="str">
+        <v>技能表 Skill + SkillEffect，明确选择后才进入生产。</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="36" t="str">
+        <v>生产默认</v>
+      </c>
+      <c r="B5" s="36" t="str">
+        <v>当前没有选入天赋；不会将未填参数补零。</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="36" t="str">
+        <v>复活</v>
+      </c>
+      <c r="B6" s="36" t="str">
+        <v>生命与体力须填绝对值，手动确认后原地复活。</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="36" t="str">
+        <v>复活抑制</v>
+      </c>
+      <c r="B7" s="36" t="str">
+        <v>成功复活后 180 Tick 不获得新警戒目标，不代表无敌。</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="36" t="str">
+        <v>参考</v>
+      </c>
+      <c r="B8" s="36" t="str">
+        <v>配置v5填写说明.md</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/cfg4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="43" t="str">
+        <v>成长规则ID</v>
+      </c>
+      <c r="B1" s="43" t="str">
+        <v>撤离经验</v>
+      </c>
+      <c r="C1" s="43" t="str">
+        <v>赏金经验</v>
+      </c>
+      <c r="D1" s="43" t="str">
+        <v>赏金货币</v>
+      </c>
+      <c r="E1" s="43" t="str">
+        <v>退役账号经验</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="43" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="43" t="str">
+        <v>int32</v>
+      </c>
+      <c r="C2" s="43" t="str">
+        <v>int32</v>
+      </c>
+      <c r="D2" s="43" t="str">
+        <v>int32</v>
+      </c>
+      <c r="E2" s="43" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="43" t="str">
+        <v>CareerIdx</v>
+      </c>
+      <c r="B3" s="43" t="str">
+        <v>ExtractXp</v>
+      </c>
+      <c r="C3" s="43" t="str">
+        <v>BountyXp</v>
+      </c>
+      <c r="D3" s="43" t="str">
+        <v>BountyCurrency</v>
+      </c>
+      <c r="E3" s="43" t="str">
+        <v>RetireXp</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="43" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="43" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="43" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="43" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="43" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/cfg5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="43" t="str">
+        <v>等级ID 从1连续</v>
+      </c>
+      <c r="B1" s="43" t="str">
+        <v>累计经验 首项0</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="43" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="43" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="43" t="str">
+        <v>LevelIdx</v>
+      </c>
+      <c r="B3" s="43" t="str">
+        <v>Xp</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="43" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="43" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/cfg6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="43" t="str">
+        <v>奖励ID</v>
+      </c>
+      <c r="B1" s="43" t="str">
+        <v>怪物ID</v>
+      </c>
+      <c r="C1" s="43" t="str">
+        <v>击杀经验</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="43" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="43" t="str">
+        <v>int32</v>
+      </c>
+      <c r="C2" s="43" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="43" t="str">
+        <v>RewardIdx</v>
+      </c>
+      <c r="B3" s="43" t="str">
+        <v>MonsterIdx</v>
+      </c>
+      <c r="C3" s="43" t="str">
+        <v>Xp</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="43" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="43" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="43" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="44"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="44"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="44"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="44"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="44"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>

--- a/design/角色表.xlsx
+++ b/design/角色表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <ns1:AlternateContent>
-    <ns1:Choice Requires="x15">
-      <ns2:absPath url="E:\聚光灯\Hunter\design\"/>
-    </ns1:Choice>
-  </ns1:AlternateContent>
+  <mc:AlternateContent>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath url="E:\聚光灯\Hunter\design\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17655"/>
   </bookViews>
@@ -22,15 +22,15 @@
   <calcPr calcId="191029"/>
   <extLst>
     <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <ns4:calcFeatures>
-        <ns4:feature name="microsoft.com:RD"/>
-        <ns4:feature name="microsoft.com:Single"/>
-        <ns4:feature name="microsoft.com:FV"/>
-        <ns4:feature name="microsoft.com:CNMTM"/>
-        <ns4:feature name="microsoft.com:LET_WF"/>
-        <ns4:feature name="microsoft.com:LAMBDA_WF"/>
-        <ns4:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </ns4:calcFeatures>
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -601,14 +601,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ns1:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="70">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -868,8 +868,175 @@
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF12283F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF79511F"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202C3A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF20364D"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202020"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF202020"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+    </font>
   </fonts>
-  <fills count="44">
+  <fills count="80">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1114,8 +1281,188 @@
         <fgColor rgb="FFB8CDE1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9CEE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD3E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1290,8 +1637,145 @@
     </border>
     <border/>
     <border/>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7EFF7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7EFF7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7EFF7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7EFF7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color theme="4" tint="0.49998"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="52">
+  <cellStyleXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1442,8 +1926,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="33" fillId="38" borderId="14"/>
     <xf numFmtId="0" fontId="36" fillId="41" borderId="15"/>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="48" fillId="41" borderId="15" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="48" fillId="41" borderId="15" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="48" fillId="41" borderId="15" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="48" fillId="41" borderId="15" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="48" fillId="41" borderId="15" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="41" borderId="15" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="41" borderId="15" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="49" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="41" borderId="15" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="41" borderId="15" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="41" borderId="15" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="41" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="41" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="41" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="41" borderId="15" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="50" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="51" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="51" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="52" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="41" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="41" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="53" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="54" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="55" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="56" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="57" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="58" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="59" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="60" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="61" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="62" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="63" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="64" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="65" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="66" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="67" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="68" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="69" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="70" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="71" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="72" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="73" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="74" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="75" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="76" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="77" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="78" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="79" borderId="15" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1569,6 +2200,75 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="43" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="15" xfId="51" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="44" borderId="16" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="44" borderId="17" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="45" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="44" borderId="18" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="44" borderId="19" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="41" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="42" fillId="46" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="42" fillId="47" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="36" fillId="41" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="41" borderId="15" xfId="51" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="41" borderId="15" xfId="51" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="39" fillId="44" borderId="20" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="48" borderId="20" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="44" fillId="48" borderId="20" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="44" borderId="20" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="48" borderId="20" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="46" borderId="20" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="46" borderId="20" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="41" borderId="20" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="41" borderId="20" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="47" borderId="20" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="47" borderId="20" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="36" fillId="41" borderId="15" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="15" xfId="51" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1816,7 +2516,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" ns2:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1825,7 +2525,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" ns2:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1840,7 +2540,7 @@
   </tableStyles>
   <extLst>
     <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2195,11 +2895,21 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
+      <c r="A5" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="44" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="44"/>
@@ -2296,24 +3006,44 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
+      <c r="A5" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
+      <c r="A6" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="44" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44"/>
+      <c r="A7" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="44" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
+      <c r="A8" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="44" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="44"/>
-      <c r="B9" s="44"/>
+      <c r="A9" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="44" t="n">
+        <v>700</v>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="44"/>
@@ -2386,34 +3116,70 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="44"/>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
+      <c r="A5" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="44" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="44"/>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
+      <c r="A6" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="44" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="44"/>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
+      <c r="A7" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="44" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
+      <c r="A8" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="44"/>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
+      <c r="A9" s="44" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="44" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C9" s="44" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="44"/>
-      <c r="B10" s="44"/>
-      <c r="C10" s="44"/>
+      <c r="A10" s="44" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="44" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C10" s="44" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="44"/>
@@ -2435,7 +3201,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:AA503"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" style="11" customWidth="1"/>
@@ -2848,8 +3614,10 @@
       <c r="L6" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="M6" s="22" t="s">
-        <v>62</v>
+      <c r="M6" s="71" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
       </c>
       <c r="N6" s="20">
         <v>50</v>
@@ -15345,7 +16113,7 @@
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
-  <dimension ref="A1:F504"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="20" style="1" customWidth="1"/>
@@ -15421,11 +16189,11 @@
       <c r="A5" s="8">
         <v>1</v>
       </c>
-      <c r="B5" s="8">
-        <v>2</v>
-      </c>
-      <c r="C5" s="8">
-        <v>2</v>
+      <c r="B5" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="57" t="n">
+        <v>4</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
@@ -15435,32 +16203,16 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1" spans="1:6">
-      <c r="A6" s="9">
-        <v>2</v>
-      </c>
-      <c r="B6" s="9">
-        <v>2</v>
-      </c>
-      <c r="C6" s="9">
-        <v>4</v>
-      </c>
-      <c r="D6" s="9">
-        <v>2</v>
-      </c>
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:6">
-      <c r="A7" s="8">
-        <v>3</v>
-      </c>
-      <c r="B7" s="8">
-        <v>3</v>
-      </c>
-      <c r="C7" s="8">
-        <v>5</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1</v>
-      </c>
+      <c r="A7" s="57"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="10"/>
